--- a/Sensitivity_Output/Sensitivity_Analysis_Full.xlsx
+++ b/Sensitivity_Output/Sensitivity_Analysis_Full.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>alpha</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>lookahead_days</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total_assigned</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>avg_distance_km</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_avg_utilization</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_avg_utilization</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_avg_utilization</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_overcap_weeks</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_overcap_weeks</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_overcap_weeks</t>
         </is>
@@ -510,22 +522,22 @@
         <v>24.55</v>
       </c>
       <c r="G2" t="n">
-        <v>11.81</v>
+        <v>4.55</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>74.5</v>
+        <v>71.5</v>
       </c>
       <c r="J2" t="n">
-        <v>50.5</v>
+        <v>61</v>
       </c>
       <c r="K2" t="n">
-        <v>76.5</v>
+        <v>63</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -553,22 +565,22 @@
         <v>500</v>
       </c>
       <c r="F3" t="n">
-        <v>24.55</v>
+        <v>24.6</v>
       </c>
       <c r="G3" t="n">
-        <v>11.81</v>
+        <v>2.07</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J3" t="n">
-        <v>50.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>76.5</v>
+        <v>63.1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -599,22 +611,22 @@
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>24.55</v>
+        <v>24.6</v>
       </c>
       <c r="G4" t="n">
-        <v>11.81</v>
+        <v>2.07</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J4" t="n">
-        <v>50.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>76.5</v>
+        <v>63.1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -645,22 +657,22 @@
         <v>500</v>
       </c>
       <c r="F5" t="n">
-        <v>24.55</v>
+        <v>24.6</v>
       </c>
       <c r="G5" t="n">
-        <v>11.81</v>
+        <v>2.07</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J5" t="n">
-        <v>50.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>76.5</v>
+        <v>63.1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -691,22 +703,22 @@
         <v>500</v>
       </c>
       <c r="F6" t="n">
-        <v>24.55</v>
+        <v>24.6</v>
       </c>
       <c r="G6" t="n">
-        <v>11.81</v>
+        <v>2.07</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J6" t="n">
-        <v>50.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>76.5</v>
+        <v>63.1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -740,19 +752,19 @@
         <v>24.43</v>
       </c>
       <c r="G7" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J7" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K7" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -786,19 +798,19 @@
         <v>24.43</v>
       </c>
       <c r="G8" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J8" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K8" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -832,19 +844,19 @@
         <v>24.43</v>
       </c>
       <c r="G9" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J9" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K9" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -878,19 +890,19 @@
         <v>24.43</v>
       </c>
       <c r="G10" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J10" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K10" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -924,19 +936,19 @@
         <v>24.43</v>
       </c>
       <c r="G11" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J11" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K11" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -970,19 +982,19 @@
         <v>24.43</v>
       </c>
       <c r="G12" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J12" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K12" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1016,19 +1028,19 @@
         <v>24.43</v>
       </c>
       <c r="G13" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J13" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K13" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1062,19 +1074,19 @@
         <v>24.43</v>
       </c>
       <c r="G14" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J14" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K14" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1108,19 +1120,19 @@
         <v>24.43</v>
       </c>
       <c r="G15" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J15" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K15" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1154,19 +1166,19 @@
         <v>24.43</v>
       </c>
       <c r="G16" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J16" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K16" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1200,19 +1212,19 @@
         <v>24.43</v>
       </c>
       <c r="G17" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J17" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K17" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1246,19 +1258,19 @@
         <v>24.43</v>
       </c>
       <c r="G18" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J18" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K18" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1292,19 +1304,19 @@
         <v>24.43</v>
       </c>
       <c r="G19" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J19" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K19" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1338,19 +1350,19 @@
         <v>24.43</v>
       </c>
       <c r="G20" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J20" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K20" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1384,19 +1396,19 @@
         <v>24.43</v>
       </c>
       <c r="G21" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J21" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K21" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1430,19 +1442,19 @@
         <v>24.43</v>
       </c>
       <c r="G22" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J22" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K22" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1476,19 +1488,19 @@
         <v>24.43</v>
       </c>
       <c r="G23" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J23" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K23" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1522,19 +1534,19 @@
         <v>24.43</v>
       </c>
       <c r="G24" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J24" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K24" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1568,19 +1580,19 @@
         <v>24.43</v>
       </c>
       <c r="G25" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J25" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K25" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1614,19 +1626,19 @@
         <v>24.43</v>
       </c>
       <c r="G26" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J26" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K26" t="n">
-        <v>76.5</v>
+        <v>65.2</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1657,22 +1669,22 @@
         <v>500</v>
       </c>
       <c r="F27" t="n">
-        <v>24.39</v>
+        <v>24.43</v>
       </c>
       <c r="G27" t="n">
-        <v>8.98</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J27" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K27" t="n">
-        <v>76.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1703,22 +1715,22 @@
         <v>500</v>
       </c>
       <c r="F28" t="n">
-        <v>24.39</v>
+        <v>24.43</v>
       </c>
       <c r="G28" t="n">
-        <v>8.98</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J28" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K28" t="n">
-        <v>76.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1749,22 +1761,22 @@
         <v>500</v>
       </c>
       <c r="F29" t="n">
-        <v>24.39</v>
+        <v>24.43</v>
       </c>
       <c r="G29" t="n">
-        <v>8.98</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J29" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K29" t="n">
-        <v>76.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1795,22 +1807,22 @@
         <v>500</v>
       </c>
       <c r="F30" t="n">
-        <v>24.39</v>
+        <v>24.43</v>
       </c>
       <c r="G30" t="n">
-        <v>8.98</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J30" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K30" t="n">
-        <v>76.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1841,22 +1853,22 @@
         <v>500</v>
       </c>
       <c r="F31" t="n">
-        <v>24.39</v>
+        <v>24.43</v>
       </c>
       <c r="G31" t="n">
-        <v>8.98</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J31" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K31" t="n">
-        <v>76.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1887,22 +1899,22 @@
         <v>500</v>
       </c>
       <c r="F32" t="n">
-        <v>24.39</v>
+        <v>24.43</v>
       </c>
       <c r="G32" t="n">
-        <v>8.98</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J32" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K32" t="n">
-        <v>76.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1933,22 +1945,22 @@
         <v>500</v>
       </c>
       <c r="F33" t="n">
-        <v>24.39</v>
+        <v>24.43</v>
       </c>
       <c r="G33" t="n">
-        <v>8.98</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J33" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K33" t="n">
-        <v>76.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -1979,22 +1991,22 @@
         <v>500</v>
       </c>
       <c r="F34" t="n">
-        <v>24.39</v>
+        <v>24.43</v>
       </c>
       <c r="G34" t="n">
-        <v>8.98</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J34" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K34" t="n">
-        <v>76.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2025,22 +2037,22 @@
         <v>500</v>
       </c>
       <c r="F35" t="n">
-        <v>24.39</v>
+        <v>24.43</v>
       </c>
       <c r="G35" t="n">
-        <v>8.98</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J35" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K35" t="n">
-        <v>76.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2071,22 +2083,22 @@
         <v>500</v>
       </c>
       <c r="F36" t="n">
-        <v>24.39</v>
+        <v>24.43</v>
       </c>
       <c r="G36" t="n">
-        <v>8.98</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J36" t="n">
-        <v>55</v>
+        <v>65.2</v>
       </c>
       <c r="K36" t="n">
-        <v>76.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2117,22 +2129,22 @@
         <v>500</v>
       </c>
       <c r="F37" t="n">
-        <v>24.41</v>
+        <v>24.43</v>
       </c>
       <c r="G37" t="n">
-        <v>8.91</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>70.2</v>
+        <v>65.2</v>
       </c>
       <c r="J37" t="n">
-        <v>55.1</v>
+        <v>65.2</v>
       </c>
       <c r="K37" t="n">
-        <v>76.3</v>
+        <v>65.2</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2163,22 +2175,22 @@
         <v>500</v>
       </c>
       <c r="F38" t="n">
-        <v>24.41</v>
+        <v>24.43</v>
       </c>
       <c r="G38" t="n">
-        <v>8.91</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>70.2</v>
+        <v>65.2</v>
       </c>
       <c r="J38" t="n">
-        <v>55.1</v>
+        <v>65.2</v>
       </c>
       <c r="K38" t="n">
-        <v>76.3</v>
+        <v>65.2</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2209,22 +2221,22 @@
         <v>500</v>
       </c>
       <c r="F39" t="n">
-        <v>24.41</v>
+        <v>24.43</v>
       </c>
       <c r="G39" t="n">
-        <v>8.91</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>70.2</v>
+        <v>65.2</v>
       </c>
       <c r="J39" t="n">
-        <v>55.1</v>
+        <v>65.2</v>
       </c>
       <c r="K39" t="n">
-        <v>76.3</v>
+        <v>65.2</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2255,22 +2267,22 @@
         <v>500</v>
       </c>
       <c r="F40" t="n">
-        <v>24.41</v>
+        <v>24.43</v>
       </c>
       <c r="G40" t="n">
-        <v>8.91</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>70.2</v>
+        <v>65.2</v>
       </c>
       <c r="J40" t="n">
-        <v>55.1</v>
+        <v>65.2</v>
       </c>
       <c r="K40" t="n">
-        <v>76.3</v>
+        <v>65.2</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2301,22 +2313,22 @@
         <v>500</v>
       </c>
       <c r="F41" t="n">
-        <v>24.41</v>
+        <v>24.43</v>
       </c>
       <c r="G41" t="n">
-        <v>8.91</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>70.2</v>
+        <v>65.2</v>
       </c>
       <c r="J41" t="n">
-        <v>55.1</v>
+        <v>65.2</v>
       </c>
       <c r="K41" t="n">
-        <v>76.3</v>
+        <v>65.2</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2350,19 +2362,19 @@
         <v>24.43</v>
       </c>
       <c r="G42" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>70.3</v>
+        <v>65.2</v>
       </c>
       <c r="J42" t="n">
-        <v>55.3</v>
+        <v>65.2</v>
       </c>
       <c r="K42" t="n">
-        <v>75.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2396,19 +2408,19 @@
         <v>24.43</v>
       </c>
       <c r="G43" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>70.3</v>
+        <v>65.2</v>
       </c>
       <c r="J43" t="n">
-        <v>55.3</v>
+        <v>65.2</v>
       </c>
       <c r="K43" t="n">
-        <v>75.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2442,19 +2454,19 @@
         <v>24.43</v>
       </c>
       <c r="G44" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>70.3</v>
+        <v>65.2</v>
       </c>
       <c r="J44" t="n">
-        <v>55.3</v>
+        <v>65.2</v>
       </c>
       <c r="K44" t="n">
-        <v>75.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -2488,19 +2500,19 @@
         <v>24.43</v>
       </c>
       <c r="G45" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>70.3</v>
+        <v>65.2</v>
       </c>
       <c r="J45" t="n">
-        <v>55.3</v>
+        <v>65.2</v>
       </c>
       <c r="K45" t="n">
-        <v>75.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2534,19 +2546,19 @@
         <v>24.43</v>
       </c>
       <c r="G46" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>70.3</v>
+        <v>65.2</v>
       </c>
       <c r="J46" t="n">
-        <v>55.3</v>
+        <v>65.2</v>
       </c>
       <c r="K46" t="n">
-        <v>75.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2577,22 +2589,22 @@
         <v>500</v>
       </c>
       <c r="F47" t="n">
-        <v>24.55</v>
+        <v>24.43</v>
       </c>
       <c r="G47" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J47" t="n">
-        <v>55.4</v>
+        <v>65.2</v>
       </c>
       <c r="K47" t="n">
-        <v>75.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2623,22 +2635,22 @@
         <v>500</v>
       </c>
       <c r="F48" t="n">
-        <v>24.55</v>
+        <v>24.43</v>
       </c>
       <c r="G48" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J48" t="n">
-        <v>55.4</v>
+        <v>65.2</v>
       </c>
       <c r="K48" t="n">
-        <v>75.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2669,22 +2681,22 @@
         <v>500</v>
       </c>
       <c r="F49" t="n">
-        <v>24.55</v>
+        <v>24.43</v>
       </c>
       <c r="G49" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J49" t="n">
-        <v>55.4</v>
+        <v>65.2</v>
       </c>
       <c r="K49" t="n">
-        <v>75.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2715,22 +2727,22 @@
         <v>500</v>
       </c>
       <c r="F50" t="n">
-        <v>24.55</v>
+        <v>24.43</v>
       </c>
       <c r="G50" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J50" t="n">
-        <v>55.4</v>
+        <v>65.2</v>
       </c>
       <c r="K50" t="n">
-        <v>75.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2761,22 +2773,22 @@
         <v>500</v>
       </c>
       <c r="F51" t="n">
-        <v>24.55</v>
+        <v>24.43</v>
       </c>
       <c r="G51" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J51" t="n">
-        <v>55.4</v>
+        <v>65.2</v>
       </c>
       <c r="K51" t="n">
-        <v>75.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2807,22 +2819,22 @@
         <v>500</v>
       </c>
       <c r="F52" t="n">
-        <v>27.42</v>
+        <v>27.34</v>
       </c>
       <c r="G52" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J52" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K52" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2853,22 +2865,22 @@
         <v>500</v>
       </c>
       <c r="F53" t="n">
-        <v>27.42</v>
+        <v>27.34</v>
       </c>
       <c r="G53" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J53" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K53" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -2899,22 +2911,22 @@
         <v>500</v>
       </c>
       <c r="F54" t="n">
-        <v>27.42</v>
+        <v>27.34</v>
       </c>
       <c r="G54" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J54" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K54" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -2945,22 +2957,22 @@
         <v>500</v>
       </c>
       <c r="F55" t="n">
-        <v>27.42</v>
+        <v>27.34</v>
       </c>
       <c r="G55" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J55" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K55" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -2991,22 +3003,22 @@
         <v>500</v>
       </c>
       <c r="F56" t="n">
-        <v>27.42</v>
+        <v>27.34</v>
       </c>
       <c r="G56" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J56" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K56" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -3040,19 +3052,19 @@
         <v>20.23</v>
       </c>
       <c r="G57" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J57" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K57" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3086,19 +3098,19 @@
         <v>20.23</v>
       </c>
       <c r="G58" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J58" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K58" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -3132,19 +3144,19 @@
         <v>20.23</v>
       </c>
       <c r="G59" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J59" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K59" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -3178,19 +3190,19 @@
         <v>20.23</v>
       </c>
       <c r="G60" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J60" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K60" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -3224,19 +3236,19 @@
         <v>20.23</v>
       </c>
       <c r="G61" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J61" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K61" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -3270,19 +3282,19 @@
         <v>20.23</v>
       </c>
       <c r="G62" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J62" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K62" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3316,19 +3328,19 @@
         <v>20.23</v>
       </c>
       <c r="G63" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J63" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K63" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3362,19 +3374,19 @@
         <v>20.23</v>
       </c>
       <c r="G64" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J64" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K64" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3408,19 +3420,19 @@
         <v>20.23</v>
       </c>
       <c r="G65" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J65" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K65" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3454,19 +3466,19 @@
         <v>20.23</v>
       </c>
       <c r="G66" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J66" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K66" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3500,19 +3512,19 @@
         <v>20.23</v>
       </c>
       <c r="G67" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J67" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K67" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -3546,19 +3558,19 @@
         <v>20.23</v>
       </c>
       <c r="G68" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J68" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K68" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3592,19 +3604,19 @@
         <v>20.23</v>
       </c>
       <c r="G69" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J69" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K69" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3638,19 +3650,19 @@
         <v>20.23</v>
       </c>
       <c r="G70" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J70" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K70" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -3684,19 +3696,19 @@
         <v>20.23</v>
       </c>
       <c r="G71" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J71" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K71" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -3730,19 +3742,19 @@
         <v>20.23</v>
       </c>
       <c r="G72" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J72" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K72" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -3776,19 +3788,19 @@
         <v>20.23</v>
       </c>
       <c r="G73" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J73" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K73" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -3822,19 +3834,19 @@
         <v>20.23</v>
       </c>
       <c r="G74" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J74" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K74" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -3868,19 +3880,19 @@
         <v>20.23</v>
       </c>
       <c r="G75" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J75" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K75" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -3914,19 +3926,19 @@
         <v>20.23</v>
       </c>
       <c r="G76" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J76" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K76" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -3960,19 +3972,19 @@
         <v>20.23</v>
       </c>
       <c r="G77" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J77" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K77" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -4006,19 +4018,19 @@
         <v>20.23</v>
       </c>
       <c r="G78" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J78" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K78" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -4052,19 +4064,19 @@
         <v>20.23</v>
       </c>
       <c r="G79" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J79" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K79" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -4098,19 +4110,19 @@
         <v>20.23</v>
       </c>
       <c r="G80" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J80" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K80" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -4144,19 +4156,19 @@
         <v>20.23</v>
       </c>
       <c r="G81" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J81" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K81" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -4190,19 +4202,19 @@
         <v>20.23</v>
       </c>
       <c r="G82" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J82" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K82" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -4236,19 +4248,19 @@
         <v>20.23</v>
       </c>
       <c r="G83" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J83" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K83" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -4282,19 +4294,19 @@
         <v>20.23</v>
       </c>
       <c r="G84" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J84" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K84" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -4328,19 +4340,19 @@
         <v>20.23</v>
       </c>
       <c r="G85" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J85" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K85" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -4374,19 +4386,19 @@
         <v>20.23</v>
       </c>
       <c r="G86" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J86" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K86" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -4420,19 +4432,19 @@
         <v>20.23</v>
       </c>
       <c r="G87" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J87" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K87" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4466,19 +4478,19 @@
         <v>20.23</v>
       </c>
       <c r="G88" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J88" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K88" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4512,19 +4524,19 @@
         <v>20.23</v>
       </c>
       <c r="G89" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J89" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K89" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4558,19 +4570,19 @@
         <v>20.23</v>
       </c>
       <c r="G90" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J90" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K90" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -4604,19 +4616,19 @@
         <v>20.23</v>
       </c>
       <c r="G91" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J91" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K91" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -4650,19 +4662,19 @@
         <v>20.23</v>
       </c>
       <c r="G92" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J92" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K92" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -4696,19 +4708,19 @@
         <v>20.23</v>
       </c>
       <c r="G93" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J93" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K93" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -4742,19 +4754,19 @@
         <v>20.23</v>
       </c>
       <c r="G94" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J94" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K94" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -4788,19 +4800,19 @@
         <v>20.23</v>
       </c>
       <c r="G95" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J95" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K95" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -4834,19 +4846,19 @@
         <v>20.23</v>
       </c>
       <c r="G96" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J96" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K96" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -4880,19 +4892,19 @@
         <v>20.23</v>
       </c>
       <c r="G97" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J97" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K97" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -4926,19 +4938,19 @@
         <v>20.23</v>
       </c>
       <c r="G98" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J98" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K98" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -4972,19 +4984,19 @@
         <v>20.23</v>
       </c>
       <c r="G99" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J99" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K99" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -5018,19 +5030,19 @@
         <v>20.23</v>
       </c>
       <c r="G100" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J100" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K100" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -5064,19 +5076,19 @@
         <v>20.23</v>
       </c>
       <c r="G101" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J101" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K101" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -5110,19 +5122,19 @@
         <v>20.23</v>
       </c>
       <c r="G102" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J102" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K102" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -5156,19 +5168,19 @@
         <v>20.23</v>
       </c>
       <c r="G103" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J103" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K103" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -5202,19 +5214,19 @@
         <v>20.23</v>
       </c>
       <c r="G104" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J104" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K104" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -5248,19 +5260,19 @@
         <v>20.23</v>
       </c>
       <c r="G105" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J105" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K105" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -5294,19 +5306,19 @@
         <v>20.23</v>
       </c>
       <c r="G106" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J106" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K106" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -5340,19 +5352,19 @@
         <v>20.23</v>
       </c>
       <c r="G107" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J107" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K107" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -5386,19 +5398,19 @@
         <v>20.23</v>
       </c>
       <c r="G108" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J108" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K108" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -5432,19 +5444,19 @@
         <v>20.23</v>
       </c>
       <c r="G109" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J109" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K109" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -5478,19 +5490,19 @@
         <v>20.23</v>
       </c>
       <c r="G110" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J110" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K110" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -5524,19 +5536,19 @@
         <v>20.23</v>
       </c>
       <c r="G111" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J111" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K111" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -5570,19 +5582,19 @@
         <v>27.14</v>
       </c>
       <c r="G112" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J112" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K112" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -5616,19 +5628,19 @@
         <v>27.14</v>
       </c>
       <c r="G113" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J113" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K113" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -5662,19 +5674,19 @@
         <v>27.14</v>
       </c>
       <c r="G114" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J114" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K114" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -5708,19 +5720,19 @@
         <v>27.14</v>
       </c>
       <c r="G115" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J115" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K115" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -5754,19 +5766,19 @@
         <v>27.14</v>
       </c>
       <c r="G116" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J116" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K116" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -5800,19 +5812,19 @@
         <v>27.14</v>
       </c>
       <c r="G117" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J117" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K117" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -5846,19 +5858,19 @@
         <v>27.14</v>
       </c>
       <c r="G118" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J118" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K118" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -5892,19 +5904,19 @@
         <v>27.14</v>
       </c>
       <c r="G119" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J119" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K119" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -5938,19 +5950,19 @@
         <v>27.14</v>
       </c>
       <c r="G120" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J120" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K120" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -5984,19 +5996,19 @@
         <v>27.14</v>
       </c>
       <c r="G121" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J121" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K121" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -6030,19 +6042,19 @@
         <v>27.14</v>
       </c>
       <c r="G122" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J122" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K122" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -6076,19 +6088,19 @@
         <v>27.14</v>
       </c>
       <c r="G123" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J123" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K123" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -6122,19 +6134,19 @@
         <v>27.14</v>
       </c>
       <c r="G124" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J124" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K124" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -6168,19 +6180,19 @@
         <v>27.14</v>
       </c>
       <c r="G125" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J125" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K125" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -6214,19 +6226,19 @@
         <v>27.14</v>
       </c>
       <c r="G126" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J126" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K126" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -6260,19 +6272,19 @@
         <v>27.14</v>
       </c>
       <c r="G127" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J127" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K127" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -6306,19 +6318,19 @@
         <v>27.14</v>
       </c>
       <c r="G128" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J128" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K128" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -6352,19 +6364,19 @@
         <v>27.14</v>
       </c>
       <c r="G129" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J129" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K129" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -6398,19 +6410,19 @@
         <v>27.14</v>
       </c>
       <c r="G130" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J130" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K130" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -6444,19 +6456,19 @@
         <v>27.14</v>
       </c>
       <c r="G131" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J131" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K131" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -6490,19 +6502,19 @@
         <v>27.14</v>
       </c>
       <c r="G132" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J132" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K132" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -6536,19 +6548,19 @@
         <v>27.14</v>
       </c>
       <c r="G133" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J133" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K133" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -6582,19 +6594,19 @@
         <v>27.14</v>
       </c>
       <c r="G134" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J134" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K134" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -6628,19 +6640,19 @@
         <v>27.14</v>
       </c>
       <c r="G135" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J135" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K135" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -6674,19 +6686,19 @@
         <v>27.14</v>
       </c>
       <c r="G136" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J136" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K136" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -6720,19 +6732,19 @@
         <v>27.14</v>
       </c>
       <c r="G137" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J137" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K137" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -6766,19 +6778,19 @@
         <v>27.14</v>
       </c>
       <c r="G138" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J138" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K138" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -6812,19 +6824,19 @@
         <v>27.14</v>
       </c>
       <c r="G139" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J139" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K139" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -6858,19 +6870,19 @@
         <v>27.14</v>
       </c>
       <c r="G140" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J140" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K140" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -6904,19 +6916,19 @@
         <v>27.14</v>
       </c>
       <c r="G141" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J141" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K141" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -6950,19 +6962,19 @@
         <v>27.14</v>
       </c>
       <c r="G142" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J142" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K142" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -6996,19 +7008,19 @@
         <v>27.14</v>
       </c>
       <c r="G143" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J143" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K143" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -7042,19 +7054,19 @@
         <v>27.14</v>
       </c>
       <c r="G144" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J144" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K144" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -7088,19 +7100,19 @@
         <v>27.14</v>
       </c>
       <c r="G145" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J145" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K145" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -7134,19 +7146,19 @@
         <v>27.14</v>
       </c>
       <c r="G146" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J146" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K146" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -7180,19 +7192,19 @@
         <v>27.14</v>
       </c>
       <c r="G147" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J147" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K147" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -7226,19 +7238,19 @@
         <v>27.14</v>
       </c>
       <c r="G148" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J148" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K148" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -7272,19 +7284,19 @@
         <v>27.14</v>
       </c>
       <c r="G149" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J149" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K149" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -7318,19 +7330,19 @@
         <v>27.14</v>
       </c>
       <c r="G150" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J150" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K150" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -7364,19 +7376,19 @@
         <v>27.14</v>
       </c>
       <c r="G151" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J151" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K151" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -7410,19 +7422,19 @@
         <v>27.14</v>
       </c>
       <c r="G152" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J152" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K152" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -7456,19 +7468,19 @@
         <v>27.14</v>
       </c>
       <c r="G153" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J153" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K153" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -7502,19 +7514,19 @@
         <v>27.14</v>
       </c>
       <c r="G154" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J154" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K154" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -7548,19 +7560,19 @@
         <v>27.14</v>
       </c>
       <c r="G155" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J155" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K155" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -7594,19 +7606,19 @@
         <v>27.14</v>
       </c>
       <c r="G156" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J156" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K156" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -7640,19 +7652,19 @@
         <v>27.14</v>
       </c>
       <c r="G157" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J157" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K157" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -7686,19 +7698,19 @@
         <v>27.14</v>
       </c>
       <c r="G158" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J158" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K158" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -7732,19 +7744,19 @@
         <v>27.14</v>
       </c>
       <c r="G159" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J159" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K159" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -7778,19 +7790,19 @@
         <v>27.14</v>
       </c>
       <c r="G160" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
       </c>
       <c r="I160" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J160" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K160" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -7824,19 +7836,19 @@
         <v>27.14</v>
       </c>
       <c r="G161" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J161" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K161" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -7870,19 +7882,19 @@
         <v>27.14</v>
       </c>
       <c r="G162" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J162" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K162" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -7916,19 +7928,19 @@
         <v>27.14</v>
       </c>
       <c r="G163" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J163" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K163" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -7962,19 +7974,19 @@
         <v>27.14</v>
       </c>
       <c r="G164" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J164" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K164" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -8008,19 +8020,19 @@
         <v>27.14</v>
       </c>
       <c r="G165" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J165" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K165" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -8054,19 +8066,19 @@
         <v>27.14</v>
       </c>
       <c r="G166" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J166" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K166" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -8100,22 +8112,22 @@
         <v>24.55</v>
       </c>
       <c r="G167" t="n">
-        <v>11.81</v>
+        <v>4.55</v>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I167" t="n">
-        <v>74.5</v>
+        <v>71.5</v>
       </c>
       <c r="J167" t="n">
-        <v>50.5</v>
+        <v>61</v>
       </c>
       <c r="K167" t="n">
-        <v>76.5</v>
+        <v>63</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M167" t="n">
         <v>0</v>
@@ -8143,22 +8155,22 @@
         <v>500</v>
       </c>
       <c r="F168" t="n">
-        <v>24.55</v>
+        <v>24.61</v>
       </c>
       <c r="G168" t="n">
-        <v>11.81</v>
+        <v>2.04</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J168" t="n">
-        <v>50.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K168" t="n">
-        <v>76.5</v>
+        <v>63.2</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -8189,22 +8201,22 @@
         <v>500</v>
       </c>
       <c r="F169" t="n">
-        <v>24.55</v>
+        <v>24.61</v>
       </c>
       <c r="G169" t="n">
-        <v>11.81</v>
+        <v>2.04</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J169" t="n">
-        <v>50.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K169" t="n">
-        <v>76.5</v>
+        <v>63.2</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -8235,22 +8247,22 @@
         <v>500</v>
       </c>
       <c r="F170" t="n">
-        <v>24.55</v>
+        <v>24.61</v>
       </c>
       <c r="G170" t="n">
-        <v>11.81</v>
+        <v>2.04</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J170" t="n">
-        <v>50.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K170" t="n">
-        <v>76.5</v>
+        <v>63.2</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -8281,22 +8293,22 @@
         <v>500</v>
       </c>
       <c r="F171" t="n">
-        <v>24.55</v>
+        <v>24.61</v>
       </c>
       <c r="G171" t="n">
-        <v>11.81</v>
+        <v>2.04</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J171" t="n">
-        <v>50.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K171" t="n">
-        <v>76.5</v>
+        <v>63.2</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -8327,22 +8339,22 @@
         <v>500</v>
       </c>
       <c r="F172" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G172" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J172" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K172" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -8373,22 +8385,22 @@
         <v>500</v>
       </c>
       <c r="F173" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G173" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
       </c>
       <c r="I173" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J173" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K173" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -8419,22 +8431,22 @@
         <v>500</v>
       </c>
       <c r="F174" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G174" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J174" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K174" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -8465,22 +8477,22 @@
         <v>500</v>
       </c>
       <c r="F175" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G175" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
       </c>
       <c r="I175" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J175" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K175" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -8511,22 +8523,22 @@
         <v>500</v>
       </c>
       <c r="F176" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G176" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
       </c>
       <c r="I176" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J176" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K176" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -8557,22 +8569,22 @@
         <v>500</v>
       </c>
       <c r="F177" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G177" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
       </c>
       <c r="I177" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J177" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K177" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -8603,22 +8615,22 @@
         <v>500</v>
       </c>
       <c r="F178" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G178" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
       </c>
       <c r="I178" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J178" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K178" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -8649,22 +8661,22 @@
         <v>500</v>
       </c>
       <c r="F179" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G179" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
       </c>
       <c r="I179" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K179" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -8695,22 +8707,22 @@
         <v>500</v>
       </c>
       <c r="F180" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G180" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
       </c>
       <c r="I180" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J180" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K180" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -8741,22 +8753,22 @@
         <v>500</v>
       </c>
       <c r="F181" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G181" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J181" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K181" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -8787,22 +8799,22 @@
         <v>500</v>
       </c>
       <c r="F182" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G182" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
       </c>
       <c r="I182" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J182" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K182" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -8833,22 +8845,22 @@
         <v>500</v>
       </c>
       <c r="F183" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G183" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
       </c>
       <c r="I183" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J183" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K183" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -8879,22 +8891,22 @@
         <v>500</v>
       </c>
       <c r="F184" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G184" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J184" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K184" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -8925,22 +8937,22 @@
         <v>500</v>
       </c>
       <c r="F185" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G185" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
       </c>
       <c r="I185" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J185" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K185" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -8971,22 +8983,22 @@
         <v>500</v>
       </c>
       <c r="F186" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G186" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J186" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K186" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -9017,22 +9029,22 @@
         <v>500</v>
       </c>
       <c r="F187" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G187" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
       </c>
       <c r="I187" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J187" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K187" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -9063,22 +9075,22 @@
         <v>500</v>
       </c>
       <c r="F188" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G188" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J188" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K188" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -9109,22 +9121,22 @@
         <v>500</v>
       </c>
       <c r="F189" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G189" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J189" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K189" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -9155,22 +9167,22 @@
         <v>500</v>
       </c>
       <c r="F190" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G190" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J190" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K190" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -9201,22 +9213,22 @@
         <v>500</v>
       </c>
       <c r="F191" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G191" t="n">
-        <v>9.06</v>
+        <v>0.19</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>70.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J191" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K191" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -9247,22 +9259,22 @@
         <v>500</v>
       </c>
       <c r="F192" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G192" t="n">
-        <v>8.93</v>
+        <v>0.19</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>70.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J192" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K192" t="n">
-        <v>76.2</v>
+        <v>65</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -9293,22 +9305,22 @@
         <v>500</v>
       </c>
       <c r="F193" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G193" t="n">
-        <v>8.93</v>
+        <v>0.19</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>70.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J193" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K193" t="n">
-        <v>76.2</v>
+        <v>65</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -9339,22 +9351,22 @@
         <v>500</v>
       </c>
       <c r="F194" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G194" t="n">
-        <v>8.93</v>
+        <v>0.19</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>70.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J194" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K194" t="n">
-        <v>76.2</v>
+        <v>65</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -9385,22 +9397,22 @@
         <v>500</v>
       </c>
       <c r="F195" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G195" t="n">
-        <v>8.93</v>
+        <v>0.19</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
       </c>
       <c r="I195" t="n">
-        <v>70.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J195" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K195" t="n">
-        <v>76.2</v>
+        <v>65</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -9431,22 +9443,22 @@
         <v>500</v>
       </c>
       <c r="F196" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G196" t="n">
-        <v>8.93</v>
+        <v>0.19</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>70.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J196" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K196" t="n">
-        <v>76.2</v>
+        <v>65</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -9477,22 +9489,22 @@
         <v>500</v>
       </c>
       <c r="F197" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G197" t="n">
-        <v>8.93</v>
+        <v>0.19</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>70.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J197" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K197" t="n">
-        <v>76.2</v>
+        <v>65</v>
       </c>
       <c r="L197" t="n">
         <v>0</v>
@@ -9523,22 +9535,22 @@
         <v>500</v>
       </c>
       <c r="F198" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G198" t="n">
-        <v>8.93</v>
+        <v>0.19</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>70.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J198" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K198" t="n">
-        <v>76.2</v>
+        <v>65</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -9569,22 +9581,22 @@
         <v>500</v>
       </c>
       <c r="F199" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G199" t="n">
-        <v>8.93</v>
+        <v>0.19</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>70.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J199" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K199" t="n">
-        <v>76.2</v>
+        <v>65</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -9615,22 +9627,22 @@
         <v>500</v>
       </c>
       <c r="F200" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G200" t="n">
-        <v>8.93</v>
+        <v>0.19</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
       </c>
       <c r="I200" t="n">
-        <v>70.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J200" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K200" t="n">
-        <v>76.2</v>
+        <v>65</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -9661,22 +9673,22 @@
         <v>500</v>
       </c>
       <c r="F201" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G201" t="n">
-        <v>8.93</v>
+        <v>0.19</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>70.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J201" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K201" t="n">
-        <v>76.2</v>
+        <v>65</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -9707,22 +9719,22 @@
         <v>500</v>
       </c>
       <c r="F202" t="n">
-        <v>24.43</v>
+        <v>24.58</v>
       </c>
       <c r="G202" t="n">
-        <v>8.81</v>
+        <v>0.19</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
       </c>
       <c r="I202" t="n">
-        <v>70.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J202" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K202" t="n">
-        <v>76.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -9753,22 +9765,22 @@
         <v>500</v>
       </c>
       <c r="F203" t="n">
-        <v>24.43</v>
+        <v>24.58</v>
       </c>
       <c r="G203" t="n">
-        <v>8.81</v>
+        <v>0.19</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>70.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J203" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K203" t="n">
-        <v>76.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -9799,22 +9811,22 @@
         <v>500</v>
       </c>
       <c r="F204" t="n">
-        <v>24.43</v>
+        <v>24.58</v>
       </c>
       <c r="G204" t="n">
-        <v>8.81</v>
+        <v>0.19</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>70.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J204" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K204" t="n">
-        <v>76.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -9845,22 +9857,22 @@
         <v>500</v>
       </c>
       <c r="F205" t="n">
-        <v>24.43</v>
+        <v>24.58</v>
       </c>
       <c r="G205" t="n">
-        <v>8.81</v>
+        <v>0.19</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>70.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J205" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K205" t="n">
-        <v>76.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -9891,22 +9903,22 @@
         <v>500</v>
       </c>
       <c r="F206" t="n">
-        <v>24.43</v>
+        <v>24.58</v>
       </c>
       <c r="G206" t="n">
-        <v>8.81</v>
+        <v>0.19</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>70.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J206" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K206" t="n">
-        <v>76.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="L206" t="n">
         <v>0</v>
@@ -9937,22 +9949,22 @@
         <v>500</v>
       </c>
       <c r="F207" t="n">
-        <v>24.67</v>
+        <v>24.54</v>
       </c>
       <c r="G207" t="n">
-        <v>8.789999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
       </c>
       <c r="I207" t="n">
-        <v>70.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="J207" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K207" t="n">
-        <v>76</v>
+        <v>65.2</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
@@ -9983,22 +9995,22 @@
         <v>500</v>
       </c>
       <c r="F208" t="n">
-        <v>24.67</v>
+        <v>24.54</v>
       </c>
       <c r="G208" t="n">
-        <v>8.789999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>70.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="J208" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K208" t="n">
-        <v>76</v>
+        <v>65.2</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
@@ -10029,22 +10041,22 @@
         <v>500</v>
       </c>
       <c r="F209" t="n">
-        <v>24.67</v>
+        <v>24.54</v>
       </c>
       <c r="G209" t="n">
-        <v>8.789999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
       </c>
       <c r="I209" t="n">
-        <v>70.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="J209" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K209" t="n">
-        <v>76</v>
+        <v>65.2</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -10075,22 +10087,22 @@
         <v>500</v>
       </c>
       <c r="F210" t="n">
-        <v>24.67</v>
+        <v>24.54</v>
       </c>
       <c r="G210" t="n">
-        <v>8.789999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
       </c>
       <c r="I210" t="n">
-        <v>70.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="J210" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K210" t="n">
-        <v>76</v>
+        <v>65.2</v>
       </c>
       <c r="L210" t="n">
         <v>0</v>
@@ -10121,22 +10133,22 @@
         <v>500</v>
       </c>
       <c r="F211" t="n">
-        <v>24.67</v>
+        <v>24.54</v>
       </c>
       <c r="G211" t="n">
-        <v>8.789999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
       </c>
       <c r="I211" t="n">
-        <v>70.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="J211" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K211" t="n">
-        <v>76</v>
+        <v>65.2</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -10167,22 +10179,22 @@
         <v>500</v>
       </c>
       <c r="F212" t="n">
-        <v>24.58</v>
+        <v>24.36</v>
       </c>
       <c r="G212" t="n">
-        <v>8.59</v>
+        <v>0.12</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
       </c>
       <c r="I212" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J212" t="n">
-        <v>55.4</v>
+        <v>65</v>
       </c>
       <c r="K212" t="n">
-        <v>75.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L212" t="n">
         <v>0</v>
@@ -10213,22 +10225,22 @@
         <v>500</v>
       </c>
       <c r="F213" t="n">
-        <v>24.58</v>
+        <v>24.36</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59</v>
+        <v>0.12</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
       </c>
       <c r="I213" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J213" t="n">
-        <v>55.4</v>
+        <v>65</v>
       </c>
       <c r="K213" t="n">
-        <v>75.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L213" t="n">
         <v>0</v>
@@ -10259,22 +10271,22 @@
         <v>500</v>
       </c>
       <c r="F214" t="n">
-        <v>24.58</v>
+        <v>24.36</v>
       </c>
       <c r="G214" t="n">
-        <v>8.59</v>
+        <v>0.12</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J214" t="n">
-        <v>55.4</v>
+        <v>65</v>
       </c>
       <c r="K214" t="n">
-        <v>75.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L214" t="n">
         <v>0</v>
@@ -10305,22 +10317,22 @@
         <v>500</v>
       </c>
       <c r="F215" t="n">
-        <v>24.58</v>
+        <v>24.36</v>
       </c>
       <c r="G215" t="n">
-        <v>8.59</v>
+        <v>0.12</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
       </c>
       <c r="I215" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J215" t="n">
-        <v>55.4</v>
+        <v>65</v>
       </c>
       <c r="K215" t="n">
-        <v>75.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L215" t="n">
         <v>0</v>
@@ -10351,22 +10363,22 @@
         <v>500</v>
       </c>
       <c r="F216" t="n">
-        <v>24.58</v>
+        <v>24.36</v>
       </c>
       <c r="G216" t="n">
-        <v>8.59</v>
+        <v>0.12</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
       </c>
       <c r="I216" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J216" t="n">
-        <v>55.4</v>
+        <v>65</v>
       </c>
       <c r="K216" t="n">
-        <v>75.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -10397,22 +10409,22 @@
         <v>500</v>
       </c>
       <c r="F217" t="n">
-        <v>27.46</v>
+        <v>27.22</v>
       </c>
       <c r="G217" t="n">
-        <v>8.51</v>
+        <v>0.09</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
       </c>
       <c r="I217" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J217" t="n">
-        <v>55.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K217" t="n">
-        <v>75.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
@@ -10443,22 +10455,22 @@
         <v>500</v>
       </c>
       <c r="F218" t="n">
-        <v>27.46</v>
+        <v>27.22</v>
       </c>
       <c r="G218" t="n">
-        <v>8.51</v>
+        <v>0.09</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J218" t="n">
-        <v>55.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K218" t="n">
-        <v>75.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -10489,22 +10501,22 @@
         <v>500</v>
       </c>
       <c r="F219" t="n">
-        <v>27.46</v>
+        <v>27.22</v>
       </c>
       <c r="G219" t="n">
-        <v>8.51</v>
+        <v>0.09</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J219" t="n">
-        <v>55.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K219" t="n">
-        <v>75.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -10535,22 +10547,22 @@
         <v>500</v>
       </c>
       <c r="F220" t="n">
-        <v>27.46</v>
+        <v>27.22</v>
       </c>
       <c r="G220" t="n">
-        <v>8.51</v>
+        <v>0.09</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
       </c>
       <c r="I220" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J220" t="n">
-        <v>55.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K220" t="n">
-        <v>75.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -10581,22 +10593,22 @@
         <v>500</v>
       </c>
       <c r="F221" t="n">
-        <v>27.46</v>
+        <v>27.22</v>
       </c>
       <c r="G221" t="n">
-        <v>8.51</v>
+        <v>0.09</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
       </c>
       <c r="I221" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J221" t="n">
-        <v>55.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K221" t="n">
-        <v>75.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L221" t="n">
         <v>0</v>

--- a/Sensitivity_Output/Sensitivity_Analysis_Full.xlsx
+++ b/Sensitivity_Output/Sensitivity_Analysis_Full.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>alpha</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>lookahead_days</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total_assigned</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>avg_distance_km</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>avg_travel_hours</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_avg_utilization</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_avg_utilization</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_avg_utilization</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_overcap_weeks</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_overcap_weeks</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_overcap_weeks</t>
         </is>
@@ -507,25 +519,25 @@
         <v>500</v>
       </c>
       <c r="F2" t="n">
-        <v>24.55</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>11.81</v>
+        <v>2.76</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>74.5</v>
+        <v>68.8</v>
       </c>
       <c r="J2" t="n">
-        <v>50.5</v>
+        <v>62.1</v>
       </c>
       <c r="K2" t="n">
-        <v>76.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -553,22 +565,22 @@
         <v>500</v>
       </c>
       <c r="F3" t="n">
-        <v>24.55</v>
+        <v>1.01</v>
       </c>
       <c r="G3" t="n">
-        <v>11.81</v>
+        <v>2.18</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J3" t="n">
-        <v>50.5</v>
+        <v>62.7</v>
       </c>
       <c r="K3" t="n">
-        <v>76.5</v>
+        <v>64.8</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -599,22 +611,22 @@
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>24.55</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>11.81</v>
+        <v>2.18</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J4" t="n">
-        <v>50.5</v>
+        <v>62.7</v>
       </c>
       <c r="K4" t="n">
-        <v>76.5</v>
+        <v>64.8</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -645,22 +657,22 @@
         <v>500</v>
       </c>
       <c r="F5" t="n">
-        <v>24.55</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
-        <v>11.81</v>
+        <v>2.18</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J5" t="n">
-        <v>50.5</v>
+        <v>62.7</v>
       </c>
       <c r="K5" t="n">
-        <v>76.5</v>
+        <v>64.8</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -691,22 +703,22 @@
         <v>500</v>
       </c>
       <c r="F6" t="n">
-        <v>24.55</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
-        <v>11.81</v>
+        <v>2.18</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J6" t="n">
-        <v>50.5</v>
+        <v>62.7</v>
       </c>
       <c r="K6" t="n">
-        <v>76.5</v>
+        <v>64.8</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -737,22 +749,22 @@
         <v>500</v>
       </c>
       <c r="F7" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K7" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -783,22 +795,22 @@
         <v>500</v>
       </c>
       <c r="F8" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K8" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -829,22 +841,22 @@
         <v>500</v>
       </c>
       <c r="F9" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K9" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -875,22 +887,22 @@
         <v>500</v>
       </c>
       <c r="F10" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K10" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -921,22 +933,22 @@
         <v>500</v>
       </c>
       <c r="F11" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K11" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -967,22 +979,22 @@
         <v>500</v>
       </c>
       <c r="F12" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K12" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1013,22 +1025,22 @@
         <v>500</v>
       </c>
       <c r="F13" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K13" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1059,22 +1071,22 @@
         <v>500</v>
       </c>
       <c r="F14" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K14" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1105,22 +1117,22 @@
         <v>500</v>
       </c>
       <c r="F15" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K15" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1151,22 +1163,22 @@
         <v>500</v>
       </c>
       <c r="F16" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K16" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1197,22 +1209,22 @@
         <v>500</v>
       </c>
       <c r="F17" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K17" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1243,22 +1255,22 @@
         <v>500</v>
       </c>
       <c r="F18" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K18" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1289,22 +1301,22 @@
         <v>500</v>
       </c>
       <c r="F19" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K19" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1335,22 +1347,22 @@
         <v>500</v>
       </c>
       <c r="F20" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K20" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1381,22 +1393,22 @@
         <v>500</v>
       </c>
       <c r="F21" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K21" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1427,22 +1439,22 @@
         <v>500</v>
       </c>
       <c r="F22" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K22" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1473,22 +1485,22 @@
         <v>500</v>
       </c>
       <c r="F23" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K23" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1519,22 +1531,22 @@
         <v>500</v>
       </c>
       <c r="F24" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K24" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1565,22 +1577,22 @@
         <v>500</v>
       </c>
       <c r="F25" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K25" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1611,22 +1623,22 @@
         <v>500</v>
       </c>
       <c r="F26" t="n">
-        <v>24.43</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>9.01</v>
+        <v>0.17</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K26" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1657,22 +1669,22 @@
         <v>500</v>
       </c>
       <c r="F27" t="n">
-        <v>24.39</v>
+        <v>1.01</v>
       </c>
       <c r="G27" t="n">
-        <v>8.98</v>
+        <v>0.17</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K27" t="n">
-        <v>76.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1703,22 +1715,22 @@
         <v>500</v>
       </c>
       <c r="F28" t="n">
-        <v>24.39</v>
+        <v>1.01</v>
       </c>
       <c r="G28" t="n">
-        <v>8.98</v>
+        <v>0.17</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K28" t="n">
-        <v>76.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1749,22 +1761,22 @@
         <v>500</v>
       </c>
       <c r="F29" t="n">
-        <v>24.39</v>
+        <v>1.01</v>
       </c>
       <c r="G29" t="n">
-        <v>8.98</v>
+        <v>0.17</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K29" t="n">
-        <v>76.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1795,22 +1807,22 @@
         <v>500</v>
       </c>
       <c r="F30" t="n">
-        <v>24.39</v>
+        <v>1.01</v>
       </c>
       <c r="G30" t="n">
-        <v>8.98</v>
+        <v>0.17</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K30" t="n">
-        <v>76.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1841,22 +1853,22 @@
         <v>500</v>
       </c>
       <c r="F31" t="n">
-        <v>24.39</v>
+        <v>1.01</v>
       </c>
       <c r="G31" t="n">
-        <v>8.98</v>
+        <v>0.17</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K31" t="n">
-        <v>76.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1887,22 +1899,22 @@
         <v>500</v>
       </c>
       <c r="F32" t="n">
-        <v>24.39</v>
+        <v>1.01</v>
       </c>
       <c r="G32" t="n">
-        <v>8.98</v>
+        <v>0.16</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J32" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K32" t="n">
-        <v>76.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1933,22 +1945,22 @@
         <v>500</v>
       </c>
       <c r="F33" t="n">
-        <v>24.39</v>
+        <v>1.01</v>
       </c>
       <c r="G33" t="n">
-        <v>8.98</v>
+        <v>0.16</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J33" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K33" t="n">
-        <v>76.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -1979,22 +1991,22 @@
         <v>500</v>
       </c>
       <c r="F34" t="n">
-        <v>24.39</v>
+        <v>1.01</v>
       </c>
       <c r="G34" t="n">
-        <v>8.98</v>
+        <v>0.16</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J34" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K34" t="n">
-        <v>76.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2025,22 +2037,22 @@
         <v>500</v>
       </c>
       <c r="F35" t="n">
-        <v>24.39</v>
+        <v>1.01</v>
       </c>
       <c r="G35" t="n">
-        <v>8.98</v>
+        <v>0.16</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J35" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K35" t="n">
-        <v>76.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2071,22 +2083,22 @@
         <v>500</v>
       </c>
       <c r="F36" t="n">
-        <v>24.39</v>
+        <v>1.01</v>
       </c>
       <c r="G36" t="n">
-        <v>8.98</v>
+        <v>0.16</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>70.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J36" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K36" t="n">
-        <v>76.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2117,22 +2129,22 @@
         <v>500</v>
       </c>
       <c r="F37" t="n">
-        <v>24.41</v>
+        <v>1.01</v>
       </c>
       <c r="G37" t="n">
-        <v>8.91</v>
+        <v>0.16</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>70.2</v>
+        <v>65.2</v>
       </c>
       <c r="J37" t="n">
-        <v>55.1</v>
+        <v>65</v>
       </c>
       <c r="K37" t="n">
-        <v>76.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2163,22 +2175,22 @@
         <v>500</v>
       </c>
       <c r="F38" t="n">
-        <v>24.41</v>
+        <v>1.01</v>
       </c>
       <c r="G38" t="n">
-        <v>8.91</v>
+        <v>0.16</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>70.2</v>
+        <v>65.2</v>
       </c>
       <c r="J38" t="n">
-        <v>55.1</v>
+        <v>65</v>
       </c>
       <c r="K38" t="n">
-        <v>76.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2209,22 +2221,22 @@
         <v>500</v>
       </c>
       <c r="F39" t="n">
-        <v>24.41</v>
+        <v>1.01</v>
       </c>
       <c r="G39" t="n">
-        <v>8.91</v>
+        <v>0.16</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>70.2</v>
+        <v>65.2</v>
       </c>
       <c r="J39" t="n">
-        <v>55.1</v>
+        <v>65</v>
       </c>
       <c r="K39" t="n">
-        <v>76.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2255,22 +2267,22 @@
         <v>500</v>
       </c>
       <c r="F40" t="n">
-        <v>24.41</v>
+        <v>1.01</v>
       </c>
       <c r="G40" t="n">
-        <v>8.91</v>
+        <v>0.16</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>70.2</v>
+        <v>65.2</v>
       </c>
       <c r="J40" t="n">
-        <v>55.1</v>
+        <v>65</v>
       </c>
       <c r="K40" t="n">
-        <v>76.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2301,22 +2313,22 @@
         <v>500</v>
       </c>
       <c r="F41" t="n">
-        <v>24.41</v>
+        <v>1.01</v>
       </c>
       <c r="G41" t="n">
-        <v>8.91</v>
+        <v>0.16</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>70.2</v>
+        <v>65.2</v>
       </c>
       <c r="J41" t="n">
-        <v>55.1</v>
+        <v>65</v>
       </c>
       <c r="K41" t="n">
-        <v>76.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2347,22 +2359,22 @@
         <v>500</v>
       </c>
       <c r="F42" t="n">
-        <v>24.43</v>
+        <v>1.01</v>
       </c>
       <c r="G42" t="n">
-        <v>8.699999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>70.3</v>
+        <v>65.2</v>
       </c>
       <c r="J42" t="n">
-        <v>55.3</v>
+        <v>65</v>
       </c>
       <c r="K42" t="n">
-        <v>75.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2393,22 +2405,22 @@
         <v>500</v>
       </c>
       <c r="F43" t="n">
-        <v>24.43</v>
+        <v>1.01</v>
       </c>
       <c r="G43" t="n">
-        <v>8.699999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>70.3</v>
+        <v>65.2</v>
       </c>
       <c r="J43" t="n">
-        <v>55.3</v>
+        <v>65</v>
       </c>
       <c r="K43" t="n">
-        <v>75.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2439,22 +2451,22 @@
         <v>500</v>
       </c>
       <c r="F44" t="n">
-        <v>24.43</v>
+        <v>1.01</v>
       </c>
       <c r="G44" t="n">
-        <v>8.699999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>70.3</v>
+        <v>65.2</v>
       </c>
       <c r="J44" t="n">
-        <v>55.3</v>
+        <v>65</v>
       </c>
       <c r="K44" t="n">
-        <v>75.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -2485,22 +2497,22 @@
         <v>500</v>
       </c>
       <c r="F45" t="n">
-        <v>24.43</v>
+        <v>1.01</v>
       </c>
       <c r="G45" t="n">
-        <v>8.699999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>70.3</v>
+        <v>65.2</v>
       </c>
       <c r="J45" t="n">
-        <v>55.3</v>
+        <v>65</v>
       </c>
       <c r="K45" t="n">
-        <v>75.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2531,22 +2543,22 @@
         <v>500</v>
       </c>
       <c r="F46" t="n">
-        <v>24.43</v>
+        <v>1.01</v>
       </c>
       <c r="G46" t="n">
-        <v>8.699999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>70.3</v>
+        <v>65.2</v>
       </c>
       <c r="J46" t="n">
-        <v>55.3</v>
+        <v>65</v>
       </c>
       <c r="K46" t="n">
-        <v>75.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2577,22 +2589,22 @@
         <v>500</v>
       </c>
       <c r="F47" t="n">
-        <v>24.55</v>
+        <v>1.01</v>
       </c>
       <c r="G47" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J47" t="n">
-        <v>55.4</v>
+        <v>65.2</v>
       </c>
       <c r="K47" t="n">
-        <v>75.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2623,22 +2635,22 @@
         <v>500</v>
       </c>
       <c r="F48" t="n">
-        <v>24.55</v>
+        <v>1.01</v>
       </c>
       <c r="G48" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J48" t="n">
-        <v>55.4</v>
+        <v>65.2</v>
       </c>
       <c r="K48" t="n">
-        <v>75.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2669,22 +2681,22 @@
         <v>500</v>
       </c>
       <c r="F49" t="n">
-        <v>24.55</v>
+        <v>1.01</v>
       </c>
       <c r="G49" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J49" t="n">
-        <v>55.4</v>
+        <v>65.2</v>
       </c>
       <c r="K49" t="n">
-        <v>75.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2715,22 +2727,22 @@
         <v>500</v>
       </c>
       <c r="F50" t="n">
-        <v>24.55</v>
+        <v>1.01</v>
       </c>
       <c r="G50" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J50" t="n">
-        <v>55.4</v>
+        <v>65.2</v>
       </c>
       <c r="K50" t="n">
-        <v>75.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2761,22 +2773,22 @@
         <v>500</v>
       </c>
       <c r="F51" t="n">
-        <v>24.55</v>
+        <v>1.01</v>
       </c>
       <c r="G51" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J51" t="n">
-        <v>55.4</v>
+        <v>65.2</v>
       </c>
       <c r="K51" t="n">
-        <v>75.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2807,22 +2819,22 @@
         <v>500</v>
       </c>
       <c r="F52" t="n">
-        <v>27.42</v>
+        <v>1.18</v>
       </c>
       <c r="G52" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J52" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K52" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2853,22 +2865,22 @@
         <v>500</v>
       </c>
       <c r="F53" t="n">
-        <v>27.42</v>
+        <v>1.18</v>
       </c>
       <c r="G53" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J53" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K53" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -2899,22 +2911,22 @@
         <v>500</v>
       </c>
       <c r="F54" t="n">
-        <v>27.42</v>
+        <v>1.18</v>
       </c>
       <c r="G54" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J54" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K54" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -2945,22 +2957,22 @@
         <v>500</v>
       </c>
       <c r="F55" t="n">
-        <v>27.42</v>
+        <v>1.18</v>
       </c>
       <c r="G55" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J55" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K55" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -2991,22 +3003,22 @@
         <v>500</v>
       </c>
       <c r="F56" t="n">
-        <v>27.42</v>
+        <v>1.18</v>
       </c>
       <c r="G56" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J56" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K56" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -3037,22 +3049,22 @@
         <v>500</v>
       </c>
       <c r="F57" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G57" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J57" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K57" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3083,22 +3095,22 @@
         <v>500</v>
       </c>
       <c r="F58" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G58" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J58" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K58" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -3129,22 +3141,22 @@
         <v>500</v>
       </c>
       <c r="F59" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G59" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J59" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K59" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -3175,22 +3187,22 @@
         <v>500</v>
       </c>
       <c r="F60" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G60" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J60" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K60" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -3221,22 +3233,22 @@
         <v>500</v>
       </c>
       <c r="F61" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G61" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J61" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K61" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -3267,22 +3279,22 @@
         <v>500</v>
       </c>
       <c r="F62" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G62" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J62" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K62" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3313,22 +3325,22 @@
         <v>500</v>
       </c>
       <c r="F63" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G63" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J63" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K63" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3359,22 +3371,22 @@
         <v>500</v>
       </c>
       <c r="F64" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G64" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J64" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K64" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3405,22 +3417,22 @@
         <v>500</v>
       </c>
       <c r="F65" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G65" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J65" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K65" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3451,22 +3463,22 @@
         <v>500</v>
       </c>
       <c r="F66" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G66" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J66" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K66" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3497,22 +3509,22 @@
         <v>500</v>
       </c>
       <c r="F67" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G67" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J67" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K67" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -3543,22 +3555,22 @@
         <v>500</v>
       </c>
       <c r="F68" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G68" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J68" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K68" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3589,22 +3601,22 @@
         <v>500</v>
       </c>
       <c r="F69" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G69" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J69" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K69" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3635,22 +3647,22 @@
         <v>500</v>
       </c>
       <c r="F70" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G70" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J70" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K70" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -3681,22 +3693,22 @@
         <v>500</v>
       </c>
       <c r="F71" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G71" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J71" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K71" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -3727,22 +3739,22 @@
         <v>500</v>
       </c>
       <c r="F72" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G72" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J72" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K72" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -3773,22 +3785,22 @@
         <v>500</v>
       </c>
       <c r="F73" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G73" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J73" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K73" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -3819,22 +3831,22 @@
         <v>500</v>
       </c>
       <c r="F74" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G74" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J74" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K74" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -3865,22 +3877,22 @@
         <v>500</v>
       </c>
       <c r="F75" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G75" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J75" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K75" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -3911,22 +3923,22 @@
         <v>500</v>
       </c>
       <c r="F76" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G76" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J76" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K76" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -3957,22 +3969,22 @@
         <v>500</v>
       </c>
       <c r="F77" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G77" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J77" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K77" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -4003,22 +4015,22 @@
         <v>500</v>
       </c>
       <c r="F78" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G78" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J78" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K78" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -4049,22 +4061,22 @@
         <v>500</v>
       </c>
       <c r="F79" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G79" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J79" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K79" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -4095,22 +4107,22 @@
         <v>500</v>
       </c>
       <c r="F80" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G80" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J80" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K80" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -4141,22 +4153,22 @@
         <v>500</v>
       </c>
       <c r="F81" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G81" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J81" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K81" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -4187,22 +4199,22 @@
         <v>500</v>
       </c>
       <c r="F82" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G82" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J82" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K82" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -4233,22 +4245,22 @@
         <v>500</v>
       </c>
       <c r="F83" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G83" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J83" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K83" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -4279,22 +4291,22 @@
         <v>500</v>
       </c>
       <c r="F84" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G84" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J84" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K84" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -4325,22 +4337,22 @@
         <v>500</v>
       </c>
       <c r="F85" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G85" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J85" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K85" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -4371,22 +4383,22 @@
         <v>500</v>
       </c>
       <c r="F86" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G86" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J86" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K86" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -4417,22 +4429,22 @@
         <v>500</v>
       </c>
       <c r="F87" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G87" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J87" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K87" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4463,22 +4475,22 @@
         <v>500</v>
       </c>
       <c r="F88" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G88" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J88" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K88" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4509,22 +4521,22 @@
         <v>500</v>
       </c>
       <c r="F89" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G89" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J89" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K89" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4555,22 +4567,22 @@
         <v>500</v>
       </c>
       <c r="F90" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G90" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J90" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K90" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -4601,22 +4613,22 @@
         <v>500</v>
       </c>
       <c r="F91" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G91" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J91" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K91" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -4647,22 +4659,22 @@
         <v>500</v>
       </c>
       <c r="F92" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G92" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J92" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K92" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -4693,22 +4705,22 @@
         <v>500</v>
       </c>
       <c r="F93" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G93" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J93" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K93" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -4739,22 +4751,22 @@
         <v>500</v>
       </c>
       <c r="F94" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G94" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J94" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K94" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -4785,22 +4797,22 @@
         <v>500</v>
       </c>
       <c r="F95" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G95" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J95" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K95" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -4831,22 +4843,22 @@
         <v>500</v>
       </c>
       <c r="F96" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G96" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J96" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K96" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -4877,22 +4889,22 @@
         <v>500</v>
       </c>
       <c r="F97" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G97" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J97" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K97" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -4923,22 +4935,22 @@
         <v>500</v>
       </c>
       <c r="F98" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G98" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J98" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K98" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -4969,22 +4981,22 @@
         <v>500</v>
       </c>
       <c r="F99" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G99" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J99" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K99" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -5015,22 +5027,22 @@
         <v>500</v>
       </c>
       <c r="F100" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G100" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J100" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K100" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -5061,22 +5073,22 @@
         <v>500</v>
       </c>
       <c r="F101" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G101" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J101" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K101" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -5107,22 +5119,22 @@
         <v>500</v>
       </c>
       <c r="F102" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G102" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J102" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K102" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -5153,22 +5165,22 @@
         <v>500</v>
       </c>
       <c r="F103" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G103" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J103" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K103" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -5199,22 +5211,22 @@
         <v>500</v>
       </c>
       <c r="F104" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G104" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J104" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K104" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -5245,22 +5257,22 @@
         <v>500</v>
       </c>
       <c r="F105" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G105" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J105" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K105" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -5291,22 +5303,22 @@
         <v>500</v>
       </c>
       <c r="F106" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G106" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J106" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K106" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -5337,22 +5349,22 @@
         <v>500</v>
       </c>
       <c r="F107" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G107" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J107" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K107" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -5383,22 +5395,22 @@
         <v>500</v>
       </c>
       <c r="F108" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G108" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J108" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K108" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -5429,22 +5441,22 @@
         <v>500</v>
       </c>
       <c r="F109" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G109" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J109" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K109" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -5475,22 +5487,22 @@
         <v>500</v>
       </c>
       <c r="F110" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G110" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J110" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K110" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -5521,22 +5533,22 @@
         <v>500</v>
       </c>
       <c r="F111" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G111" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J111" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K111" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -5567,22 +5579,22 @@
         <v>500</v>
       </c>
       <c r="F112" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G112" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J112" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K112" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -5613,22 +5625,22 @@
         <v>500</v>
       </c>
       <c r="F113" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G113" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J113" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K113" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -5659,22 +5671,22 @@
         <v>500</v>
       </c>
       <c r="F114" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G114" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J114" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K114" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -5705,22 +5717,22 @@
         <v>500</v>
       </c>
       <c r="F115" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G115" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J115" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K115" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -5751,22 +5763,22 @@
         <v>500</v>
       </c>
       <c r="F116" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G116" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J116" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K116" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -5797,22 +5809,22 @@
         <v>500</v>
       </c>
       <c r="F117" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G117" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J117" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K117" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -5843,22 +5855,22 @@
         <v>500</v>
       </c>
       <c r="F118" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G118" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J118" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K118" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -5889,22 +5901,22 @@
         <v>500</v>
       </c>
       <c r="F119" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G119" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J119" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K119" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -5935,22 +5947,22 @@
         <v>500</v>
       </c>
       <c r="F120" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G120" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J120" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K120" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -5981,22 +5993,22 @@
         <v>500</v>
       </c>
       <c r="F121" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G121" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J121" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K121" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -6027,22 +6039,22 @@
         <v>500</v>
       </c>
       <c r="F122" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G122" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J122" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K122" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -6073,22 +6085,22 @@
         <v>500</v>
       </c>
       <c r="F123" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G123" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J123" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K123" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -6119,22 +6131,22 @@
         <v>500</v>
       </c>
       <c r="F124" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G124" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J124" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K124" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -6165,22 +6177,22 @@
         <v>500</v>
       </c>
       <c r="F125" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G125" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J125" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K125" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -6211,22 +6223,22 @@
         <v>500</v>
       </c>
       <c r="F126" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G126" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J126" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K126" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -6257,22 +6269,22 @@
         <v>500</v>
       </c>
       <c r="F127" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G127" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J127" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K127" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -6303,22 +6315,22 @@
         <v>500</v>
       </c>
       <c r="F128" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G128" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J128" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K128" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -6349,22 +6361,22 @@
         <v>500</v>
       </c>
       <c r="F129" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G129" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J129" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K129" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -6395,22 +6407,22 @@
         <v>500</v>
       </c>
       <c r="F130" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G130" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J130" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K130" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -6441,22 +6453,22 @@
         <v>500</v>
       </c>
       <c r="F131" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G131" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J131" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K131" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -6487,22 +6499,22 @@
         <v>500</v>
       </c>
       <c r="F132" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G132" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J132" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K132" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -6533,22 +6545,22 @@
         <v>500</v>
       </c>
       <c r="F133" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G133" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J133" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K133" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -6579,22 +6591,22 @@
         <v>500</v>
       </c>
       <c r="F134" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G134" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J134" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K134" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -6625,22 +6637,22 @@
         <v>500</v>
       </c>
       <c r="F135" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G135" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J135" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K135" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -6671,22 +6683,22 @@
         <v>500</v>
       </c>
       <c r="F136" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G136" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J136" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K136" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -6717,22 +6729,22 @@
         <v>500</v>
       </c>
       <c r="F137" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G137" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J137" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K137" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -6763,22 +6775,22 @@
         <v>500</v>
       </c>
       <c r="F138" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G138" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J138" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K138" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -6809,22 +6821,22 @@
         <v>500</v>
       </c>
       <c r="F139" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G139" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J139" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K139" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -6855,22 +6867,22 @@
         <v>500</v>
       </c>
       <c r="F140" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G140" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J140" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K140" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -6901,22 +6913,22 @@
         <v>500</v>
       </c>
       <c r="F141" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G141" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J141" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K141" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -6947,22 +6959,22 @@
         <v>500</v>
       </c>
       <c r="F142" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G142" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J142" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K142" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -6993,22 +7005,22 @@
         <v>500</v>
       </c>
       <c r="F143" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G143" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J143" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K143" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -7039,22 +7051,22 @@
         <v>500</v>
       </c>
       <c r="F144" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G144" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J144" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K144" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -7085,22 +7097,22 @@
         <v>500</v>
       </c>
       <c r="F145" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G145" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J145" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K145" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -7131,22 +7143,22 @@
         <v>500</v>
       </c>
       <c r="F146" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G146" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J146" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K146" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -7177,22 +7189,22 @@
         <v>500</v>
       </c>
       <c r="F147" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G147" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J147" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K147" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -7223,22 +7235,22 @@
         <v>500</v>
       </c>
       <c r="F148" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G148" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J148" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K148" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -7269,22 +7281,22 @@
         <v>500</v>
       </c>
       <c r="F149" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G149" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J149" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K149" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -7315,22 +7327,22 @@
         <v>500</v>
       </c>
       <c r="F150" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G150" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J150" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K150" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -7361,22 +7373,22 @@
         <v>500</v>
       </c>
       <c r="F151" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G151" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J151" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K151" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -7407,22 +7419,22 @@
         <v>500</v>
       </c>
       <c r="F152" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G152" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J152" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K152" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -7453,22 +7465,22 @@
         <v>500</v>
       </c>
       <c r="F153" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G153" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J153" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K153" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -7499,22 +7511,22 @@
         <v>500</v>
       </c>
       <c r="F154" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G154" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J154" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K154" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -7545,22 +7557,22 @@
         <v>500</v>
       </c>
       <c r="F155" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G155" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J155" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K155" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -7591,22 +7603,22 @@
         <v>500</v>
       </c>
       <c r="F156" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G156" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J156" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K156" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -7637,22 +7649,22 @@
         <v>500</v>
       </c>
       <c r="F157" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G157" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J157" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K157" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -7683,22 +7695,22 @@
         <v>500</v>
       </c>
       <c r="F158" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G158" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J158" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K158" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -7729,22 +7741,22 @@
         <v>500</v>
       </c>
       <c r="F159" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G159" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J159" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K159" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -7775,22 +7787,22 @@
         <v>500</v>
       </c>
       <c r="F160" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G160" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
       </c>
       <c r="I160" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J160" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K160" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -7821,22 +7833,22 @@
         <v>500</v>
       </c>
       <c r="F161" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G161" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J161" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K161" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -7867,22 +7879,22 @@
         <v>500</v>
       </c>
       <c r="F162" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G162" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J162" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K162" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -7913,22 +7925,22 @@
         <v>500</v>
       </c>
       <c r="F163" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G163" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J163" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K163" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -7959,22 +7971,22 @@
         <v>500</v>
       </c>
       <c r="F164" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G164" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J164" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K164" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -8005,22 +8017,22 @@
         <v>500</v>
       </c>
       <c r="F165" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G165" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J165" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K165" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -8051,22 +8063,22 @@
         <v>500</v>
       </c>
       <c r="F166" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G166" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J166" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K166" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -8097,25 +8109,25 @@
         <v>500</v>
       </c>
       <c r="F167" t="n">
-        <v>24.55</v>
+        <v>1.01</v>
       </c>
       <c r="G167" t="n">
-        <v>11.81</v>
+        <v>2.76</v>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I167" t="n">
-        <v>74.5</v>
+        <v>68.8</v>
       </c>
       <c r="J167" t="n">
-        <v>50.5</v>
+        <v>62.1</v>
       </c>
       <c r="K167" t="n">
-        <v>76.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M167" t="n">
         <v>0</v>
@@ -8143,22 +8155,22 @@
         <v>500</v>
       </c>
       <c r="F168" t="n">
-        <v>24.55</v>
+        <v>1.01</v>
       </c>
       <c r="G168" t="n">
-        <v>11.81</v>
+        <v>2.22</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J168" t="n">
-        <v>50.5</v>
+        <v>62.6</v>
       </c>
       <c r="K168" t="n">
-        <v>76.5</v>
+        <v>64.8</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -8189,22 +8201,22 @@
         <v>500</v>
       </c>
       <c r="F169" t="n">
-        <v>24.55</v>
+        <v>1.01</v>
       </c>
       <c r="G169" t="n">
-        <v>11.81</v>
+        <v>2.22</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J169" t="n">
-        <v>50.5</v>
+        <v>62.6</v>
       </c>
       <c r="K169" t="n">
-        <v>76.5</v>
+        <v>64.8</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -8235,22 +8247,22 @@
         <v>500</v>
       </c>
       <c r="F170" t="n">
-        <v>24.55</v>
+        <v>1.01</v>
       </c>
       <c r="G170" t="n">
-        <v>11.81</v>
+        <v>2.22</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J170" t="n">
-        <v>50.5</v>
+        <v>62.6</v>
       </c>
       <c r="K170" t="n">
-        <v>76.5</v>
+        <v>64.8</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -8281,22 +8293,22 @@
         <v>500</v>
       </c>
       <c r="F171" t="n">
-        <v>24.55</v>
+        <v>1.01</v>
       </c>
       <c r="G171" t="n">
-        <v>11.81</v>
+        <v>2.22</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="J171" t="n">
-        <v>50.5</v>
+        <v>62.6</v>
       </c>
       <c r="K171" t="n">
-        <v>76.5</v>
+        <v>64.8</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -8327,22 +8339,22 @@
         <v>500</v>
       </c>
       <c r="F172" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G172" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J172" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K172" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -8373,22 +8385,22 @@
         <v>500</v>
       </c>
       <c r="F173" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G173" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
       </c>
       <c r="I173" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J173" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K173" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -8419,22 +8431,22 @@
         <v>500</v>
       </c>
       <c r="F174" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G174" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J174" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K174" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -8465,22 +8477,22 @@
         <v>500</v>
       </c>
       <c r="F175" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G175" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
       </c>
       <c r="I175" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J175" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K175" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -8511,22 +8523,22 @@
         <v>500</v>
       </c>
       <c r="F176" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G176" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
       </c>
       <c r="I176" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J176" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K176" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -8557,22 +8569,22 @@
         <v>500</v>
       </c>
       <c r="F177" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G177" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
       </c>
       <c r="I177" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J177" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K177" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -8603,22 +8615,22 @@
         <v>500</v>
       </c>
       <c r="F178" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G178" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
       </c>
       <c r="I178" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J178" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K178" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -8649,22 +8661,22 @@
         <v>500</v>
       </c>
       <c r="F179" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G179" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
       </c>
       <c r="I179" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J179" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K179" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -8695,22 +8707,22 @@
         <v>500</v>
       </c>
       <c r="F180" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G180" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
       </c>
       <c r="I180" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J180" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K180" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -8741,22 +8753,22 @@
         <v>500</v>
       </c>
       <c r="F181" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G181" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J181" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K181" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -8787,22 +8799,22 @@
         <v>500</v>
       </c>
       <c r="F182" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G182" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
       </c>
       <c r="I182" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J182" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K182" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -8833,22 +8845,22 @@
         <v>500</v>
       </c>
       <c r="F183" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G183" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
       </c>
       <c r="I183" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J183" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K183" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -8879,22 +8891,22 @@
         <v>500</v>
       </c>
       <c r="F184" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G184" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J184" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K184" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -8925,22 +8937,22 @@
         <v>500</v>
       </c>
       <c r="F185" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G185" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
       </c>
       <c r="I185" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J185" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K185" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -8971,22 +8983,22 @@
         <v>500</v>
       </c>
       <c r="F186" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G186" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J186" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K186" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -9017,22 +9029,22 @@
         <v>500</v>
       </c>
       <c r="F187" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G187" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
       </c>
       <c r="I187" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J187" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K187" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -9063,22 +9075,22 @@
         <v>500</v>
       </c>
       <c r="F188" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G188" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J188" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K188" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -9109,22 +9121,22 @@
         <v>500</v>
       </c>
       <c r="F189" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G189" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J189" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K189" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -9155,22 +9167,22 @@
         <v>500</v>
       </c>
       <c r="F190" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G190" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J190" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K190" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -9201,22 +9213,22 @@
         <v>500</v>
       </c>
       <c r="F191" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G191" t="n">
-        <v>9.06</v>
+        <v>0.17</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J191" t="n">
-        <v>54.9</v>
+        <v>65</v>
       </c>
       <c r="K191" t="n">
-        <v>76.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -9247,22 +9259,22 @@
         <v>500</v>
       </c>
       <c r="F192" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G192" t="n">
-        <v>8.93</v>
+        <v>0.17</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>70.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J192" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K192" t="n">
-        <v>76.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -9293,22 +9305,22 @@
         <v>500</v>
       </c>
       <c r="F193" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G193" t="n">
-        <v>8.93</v>
+        <v>0.17</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>70.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J193" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K193" t="n">
-        <v>76.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -9339,22 +9351,22 @@
         <v>500</v>
       </c>
       <c r="F194" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G194" t="n">
-        <v>8.93</v>
+        <v>0.17</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>70.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J194" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K194" t="n">
-        <v>76.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -9385,22 +9397,22 @@
         <v>500</v>
       </c>
       <c r="F195" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G195" t="n">
-        <v>8.93</v>
+        <v>0.17</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
       </c>
       <c r="I195" t="n">
-        <v>70.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J195" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K195" t="n">
-        <v>76.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -9431,22 +9443,22 @@
         <v>500</v>
       </c>
       <c r="F196" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G196" t="n">
-        <v>8.93</v>
+        <v>0.17</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>70.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J196" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K196" t="n">
-        <v>76.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -9477,22 +9489,22 @@
         <v>500</v>
       </c>
       <c r="F197" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G197" t="n">
-        <v>8.93</v>
+        <v>0.17</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>70.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J197" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K197" t="n">
-        <v>76.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L197" t="n">
         <v>0</v>
@@ -9523,22 +9535,22 @@
         <v>500</v>
       </c>
       <c r="F198" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G198" t="n">
-        <v>8.93</v>
+        <v>0.17</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>70.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J198" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K198" t="n">
-        <v>76.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -9569,22 +9581,22 @@
         <v>500</v>
       </c>
       <c r="F199" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G199" t="n">
-        <v>8.93</v>
+        <v>0.17</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>70.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J199" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K199" t="n">
-        <v>76.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -9615,22 +9627,22 @@
         <v>500</v>
       </c>
       <c r="F200" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G200" t="n">
-        <v>8.93</v>
+        <v>0.17</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
       </c>
       <c r="I200" t="n">
-        <v>70.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J200" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K200" t="n">
-        <v>76.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -9661,22 +9673,22 @@
         <v>500</v>
       </c>
       <c r="F201" t="n">
-        <v>24.45</v>
+        <v>1.01</v>
       </c>
       <c r="G201" t="n">
-        <v>8.93</v>
+        <v>0.17</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>70.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J201" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K201" t="n">
-        <v>76.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -9707,22 +9719,22 @@
         <v>500</v>
       </c>
       <c r="F202" t="n">
-        <v>24.43</v>
+        <v>1.01</v>
       </c>
       <c r="G202" t="n">
-        <v>8.81</v>
+        <v>0.17</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
       </c>
       <c r="I202" t="n">
-        <v>70.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J202" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K202" t="n">
-        <v>76.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -9753,22 +9765,22 @@
         <v>500</v>
       </c>
       <c r="F203" t="n">
-        <v>24.43</v>
+        <v>1.01</v>
       </c>
       <c r="G203" t="n">
-        <v>8.81</v>
+        <v>0.17</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>70.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J203" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K203" t="n">
-        <v>76.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -9799,22 +9811,22 @@
         <v>500</v>
       </c>
       <c r="F204" t="n">
-        <v>24.43</v>
+        <v>1.01</v>
       </c>
       <c r="G204" t="n">
-        <v>8.81</v>
+        <v>0.17</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>70.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J204" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K204" t="n">
-        <v>76.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -9845,22 +9857,22 @@
         <v>500</v>
       </c>
       <c r="F205" t="n">
-        <v>24.43</v>
+        <v>1.01</v>
       </c>
       <c r="G205" t="n">
-        <v>8.81</v>
+        <v>0.17</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>70.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J205" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K205" t="n">
-        <v>76.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -9891,22 +9903,22 @@
         <v>500</v>
       </c>
       <c r="F206" t="n">
-        <v>24.43</v>
+        <v>1.01</v>
       </c>
       <c r="G206" t="n">
-        <v>8.81</v>
+        <v>0.17</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>70.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K206" t="n">
-        <v>76.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L206" t="n">
         <v>0</v>
@@ -9937,22 +9949,22 @@
         <v>500</v>
       </c>
       <c r="F207" t="n">
-        <v>24.67</v>
+        <v>1.01</v>
       </c>
       <c r="G207" t="n">
-        <v>8.789999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
       </c>
       <c r="I207" t="n">
-        <v>70.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J207" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K207" t="n">
-        <v>76</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
@@ -9983,22 +9995,22 @@
         <v>500</v>
       </c>
       <c r="F208" t="n">
-        <v>24.67</v>
+        <v>1.01</v>
       </c>
       <c r="G208" t="n">
-        <v>8.789999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>70.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J208" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K208" t="n">
-        <v>76</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
@@ -10029,22 +10041,22 @@
         <v>500</v>
       </c>
       <c r="F209" t="n">
-        <v>24.67</v>
+        <v>1.01</v>
       </c>
       <c r="G209" t="n">
-        <v>8.789999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
       </c>
       <c r="I209" t="n">
-        <v>70.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K209" t="n">
-        <v>76</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -10075,22 +10087,22 @@
         <v>500</v>
       </c>
       <c r="F210" t="n">
-        <v>24.67</v>
+        <v>1.01</v>
       </c>
       <c r="G210" t="n">
-        <v>8.789999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
       </c>
       <c r="I210" t="n">
-        <v>70.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J210" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K210" t="n">
-        <v>76</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L210" t="n">
         <v>0</v>
@@ -10121,22 +10133,22 @@
         <v>500</v>
       </c>
       <c r="F211" t="n">
-        <v>24.67</v>
+        <v>1.01</v>
       </c>
       <c r="G211" t="n">
-        <v>8.789999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
       </c>
       <c r="I211" t="n">
-        <v>70.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J211" t="n">
-        <v>55.2</v>
+        <v>65</v>
       </c>
       <c r="K211" t="n">
-        <v>76</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -10167,22 +10179,22 @@
         <v>500</v>
       </c>
       <c r="F212" t="n">
-        <v>24.58</v>
+        <v>1.01</v>
       </c>
       <c r="G212" t="n">
-        <v>8.59</v>
+        <v>0.17</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
       </c>
       <c r="I212" t="n">
-        <v>70.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J212" t="n">
-        <v>55.4</v>
+        <v>65</v>
       </c>
       <c r="K212" t="n">
-        <v>75.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L212" t="n">
         <v>0</v>
@@ -10213,22 +10225,22 @@
         <v>500</v>
       </c>
       <c r="F213" t="n">
-        <v>24.58</v>
+        <v>1.01</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59</v>
+        <v>0.17</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
       </c>
       <c r="I213" t="n">
-        <v>70.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J213" t="n">
-        <v>55.4</v>
+        <v>65</v>
       </c>
       <c r="K213" t="n">
-        <v>75.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L213" t="n">
         <v>0</v>
@@ -10259,22 +10271,22 @@
         <v>500</v>
       </c>
       <c r="F214" t="n">
-        <v>24.58</v>
+        <v>1.01</v>
       </c>
       <c r="G214" t="n">
-        <v>8.59</v>
+        <v>0.17</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>70.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J214" t="n">
-        <v>55.4</v>
+        <v>65</v>
       </c>
       <c r="K214" t="n">
-        <v>75.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L214" t="n">
         <v>0</v>
@@ -10305,22 +10317,22 @@
         <v>500</v>
       </c>
       <c r="F215" t="n">
-        <v>24.58</v>
+        <v>1.01</v>
       </c>
       <c r="G215" t="n">
-        <v>8.59</v>
+        <v>0.17</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
       </c>
       <c r="I215" t="n">
-        <v>70.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J215" t="n">
-        <v>55.4</v>
+        <v>65</v>
       </c>
       <c r="K215" t="n">
-        <v>75.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L215" t="n">
         <v>0</v>
@@ -10351,22 +10363,22 @@
         <v>500</v>
       </c>
       <c r="F216" t="n">
-        <v>24.58</v>
+        <v>1.01</v>
       </c>
       <c r="G216" t="n">
-        <v>8.59</v>
+        <v>0.17</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
       </c>
       <c r="I216" t="n">
-        <v>70.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J216" t="n">
-        <v>55.4</v>
+        <v>65</v>
       </c>
       <c r="K216" t="n">
-        <v>75.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -10397,22 +10409,22 @@
         <v>500</v>
       </c>
       <c r="F217" t="n">
-        <v>27.46</v>
+        <v>1.18</v>
       </c>
       <c r="G217" t="n">
-        <v>8.51</v>
+        <v>0.09</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
       </c>
       <c r="I217" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J217" t="n">
-        <v>55.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K217" t="n">
-        <v>75.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
@@ -10443,22 +10455,22 @@
         <v>500</v>
       </c>
       <c r="F218" t="n">
-        <v>27.46</v>
+        <v>1.18</v>
       </c>
       <c r="G218" t="n">
-        <v>8.51</v>
+        <v>0.09</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J218" t="n">
-        <v>55.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K218" t="n">
-        <v>75.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -10489,22 +10501,22 @@
         <v>500</v>
       </c>
       <c r="F219" t="n">
-        <v>27.46</v>
+        <v>1.18</v>
       </c>
       <c r="G219" t="n">
-        <v>8.51</v>
+        <v>0.09</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J219" t="n">
-        <v>55.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K219" t="n">
-        <v>75.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -10535,22 +10547,22 @@
         <v>500</v>
       </c>
       <c r="F220" t="n">
-        <v>27.46</v>
+        <v>1.18</v>
       </c>
       <c r="G220" t="n">
-        <v>8.51</v>
+        <v>0.09</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
       </c>
       <c r="I220" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J220" t="n">
-        <v>55.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K220" t="n">
-        <v>75.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -10581,22 +10593,22 @@
         <v>500</v>
       </c>
       <c r="F221" t="n">
-        <v>27.46</v>
+        <v>1.18</v>
       </c>
       <c r="G221" t="n">
-        <v>8.51</v>
+        <v>0.09</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
       </c>
       <c r="I221" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J221" t="n">
-        <v>55.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K221" t="n">
-        <v>75.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L221" t="n">
         <v>0</v>

--- a/Sensitivity_Output/Sensitivity_Analysis_Full.xlsx
+++ b/Sensitivity_Output/Sensitivity_Analysis_Full.xlsx
@@ -522,28 +522,28 @@
         <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>2.76</v>
+        <v>16.94</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>68.8</v>
+        <v>115.4</v>
       </c>
       <c r="J2" t="n">
-        <v>62.1</v>
+        <v>74.8</v>
       </c>
       <c r="K2" t="n">
-        <v>64.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -565,31 +565,31 @@
         <v>500</v>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G3" t="n">
-        <v>2.18</v>
+        <v>4.15</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>68</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>62.7</v>
+        <v>88.8</v>
       </c>
       <c r="K3" t="n">
-        <v>64.8</v>
+        <v>90.7</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -611,31 +611,31 @@
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G4" t="n">
-        <v>2.18</v>
+        <v>4.15</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>68</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>62.7</v>
+        <v>88.8</v>
       </c>
       <c r="K4" t="n">
-        <v>64.8</v>
+        <v>90.7</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -657,31 +657,31 @@
         <v>500</v>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G5" t="n">
-        <v>2.18</v>
+        <v>4.15</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>68</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>62.7</v>
+        <v>88.8</v>
       </c>
       <c r="K5" t="n">
-        <v>64.8</v>
+        <v>90.7</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -703,31 +703,31 @@
         <v>500</v>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G6" t="n">
-        <v>2.18</v>
+        <v>4.15</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>68</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>62.7</v>
+        <v>88.8</v>
       </c>
       <c r="K6" t="n">
-        <v>64.8</v>
+        <v>90.7</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -752,28 +752,28 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.17</v>
+        <v>0.78</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>65.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>65</v>
+        <v>93.5</v>
       </c>
       <c r="K7" t="n">
-        <v>65.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -795,31 +795,31 @@
         <v>500</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G8" t="n">
-        <v>0.17</v>
+        <v>0.87</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>65.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="J8" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K8" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -841,31 +841,31 @@
         <v>500</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G9" t="n">
-        <v>0.17</v>
+        <v>0.87</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>65.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="J9" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K9" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -887,31 +887,31 @@
         <v>500</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G10" t="n">
-        <v>0.17</v>
+        <v>0.87</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>65.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="J10" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K10" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -933,31 +933,31 @@
         <v>500</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G11" t="n">
-        <v>0.17</v>
+        <v>0.87</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>65.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="J11" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K11" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -982,28 +982,28 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.17</v>
+        <v>0.78</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>65.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>65</v>
+        <v>93.5</v>
       </c>
       <c r="K12" t="n">
-        <v>65.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1025,31 +1025,31 @@
         <v>500</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G13" t="n">
-        <v>0.17</v>
+        <v>0.87</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>65.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="J13" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K13" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1071,31 +1071,31 @@
         <v>500</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G14" t="n">
-        <v>0.17</v>
+        <v>0.87</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>65.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="J14" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K14" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1117,31 +1117,31 @@
         <v>500</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G15" t="n">
-        <v>0.17</v>
+        <v>0.87</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>65.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="J15" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K15" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1163,31 +1163,31 @@
         <v>500</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G16" t="n">
-        <v>0.17</v>
+        <v>0.87</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>65.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="J16" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K16" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1212,28 +1212,28 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.17</v>
+        <v>0.87</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>65.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="J17" t="n">
-        <v>65</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>65.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1255,31 +1255,31 @@
         <v>500</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G18" t="n">
-        <v>0.17</v>
+        <v>0.95</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>65.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>65</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1301,31 +1301,31 @@
         <v>500</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G19" t="n">
-        <v>0.17</v>
+        <v>0.95</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>65.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>65</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1347,31 +1347,31 @@
         <v>500</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G20" t="n">
-        <v>0.17</v>
+        <v>0.95</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>65.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>65</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1393,31 +1393,31 @@
         <v>500</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G21" t="n">
-        <v>0.17</v>
+        <v>0.95</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>65.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>65</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1442,28 +1442,28 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.17</v>
+        <v>0.84</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>65.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="J22" t="n">
-        <v>65</v>
+        <v>93.5</v>
       </c>
       <c r="K22" t="n">
-        <v>65.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1485,31 +1485,31 @@
         <v>500</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G23" t="n">
-        <v>0.17</v>
+        <v>0.9</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>65.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K23" t="n">
-        <v>65.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1531,31 +1531,31 @@
         <v>500</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G24" t="n">
-        <v>0.17</v>
+        <v>0.9</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>65.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K24" t="n">
-        <v>65.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1577,31 +1577,31 @@
         <v>500</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G25" t="n">
-        <v>0.17</v>
+        <v>0.9</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>65.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K25" t="n">
-        <v>65.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1623,31 +1623,31 @@
         <v>500</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G26" t="n">
-        <v>0.17</v>
+        <v>0.9</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>65.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K26" t="n">
-        <v>65.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1672,28 +1672,28 @@
         <v>1.01</v>
       </c>
       <c r="G27" t="n">
-        <v>0.17</v>
+        <v>0.92</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>65.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>65</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>65.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1715,31 +1715,31 @@
         <v>500</v>
       </c>
       <c r="F28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G28" t="n">
-        <v>0.17</v>
+        <v>0.98</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>65.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="J28" t="n">
-        <v>65</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>65.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1761,31 +1761,31 @@
         <v>500</v>
       </c>
       <c r="F29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G29" t="n">
-        <v>0.17</v>
+        <v>0.98</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>65.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="J29" t="n">
-        <v>65</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>65.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1807,31 +1807,31 @@
         <v>500</v>
       </c>
       <c r="F30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G30" t="n">
-        <v>0.17</v>
+        <v>0.98</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>65.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="J30" t="n">
-        <v>65</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>65.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1853,31 +1853,31 @@
         <v>500</v>
       </c>
       <c r="F31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G31" t="n">
-        <v>0.17</v>
+        <v>0.98</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>65.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="J31" t="n">
-        <v>65</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>65.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1902,28 +1902,28 @@
         <v>1.01</v>
       </c>
       <c r="G32" t="n">
-        <v>0.16</v>
+        <v>0.83</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>65.2</v>
+        <v>91.5</v>
       </c>
       <c r="J32" t="n">
-        <v>65</v>
+        <v>93.5</v>
       </c>
       <c r="K32" t="n">
-        <v>65.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1945,31 +1945,31 @@
         <v>500</v>
       </c>
       <c r="F33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G33" t="n">
-        <v>0.16</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>65.2</v>
+        <v>91.5</v>
       </c>
       <c r="J33" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K33" t="n">
-        <v>65.40000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1991,31 +1991,31 @@
         <v>500</v>
       </c>
       <c r="F34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G34" t="n">
-        <v>0.16</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>65.2</v>
+        <v>91.5</v>
       </c>
       <c r="J34" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K34" t="n">
-        <v>65.40000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2037,31 +2037,31 @@
         <v>500</v>
       </c>
       <c r="F35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G35" t="n">
-        <v>0.16</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>65.2</v>
+        <v>91.5</v>
       </c>
       <c r="J35" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K35" t="n">
-        <v>65.40000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2083,31 +2083,31 @@
         <v>500</v>
       </c>
       <c r="F36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G36" t="n">
-        <v>0.16</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>65.2</v>
+        <v>91.5</v>
       </c>
       <c r="J36" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K36" t="n">
-        <v>65.40000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2132,28 +2132,28 @@
         <v>1.01</v>
       </c>
       <c r="G37" t="n">
-        <v>0.16</v>
+        <v>0.86</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>65.2</v>
+        <v>91.5</v>
       </c>
       <c r="J37" t="n">
-        <v>65</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>65.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2175,31 +2175,31 @@
         <v>500</v>
       </c>
       <c r="F38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G38" t="n">
-        <v>0.16</v>
+        <v>0.99</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>65.2</v>
+        <v>91.5</v>
       </c>
       <c r="J38" t="n">
-        <v>65</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2221,31 +2221,31 @@
         <v>500</v>
       </c>
       <c r="F39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G39" t="n">
-        <v>0.16</v>
+        <v>0.99</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>65.2</v>
+        <v>91.5</v>
       </c>
       <c r="J39" t="n">
-        <v>65</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2267,31 +2267,31 @@
         <v>500</v>
       </c>
       <c r="F40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G40" t="n">
-        <v>0.16</v>
+        <v>0.99</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I40" t="n">
-        <v>65.2</v>
+        <v>91.5</v>
       </c>
       <c r="J40" t="n">
-        <v>65</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2313,31 +2313,31 @@
         <v>500</v>
       </c>
       <c r="F41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G41" t="n">
-        <v>0.16</v>
+        <v>0.99</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
-        <v>65.2</v>
+        <v>91.5</v>
       </c>
       <c r="J41" t="n">
-        <v>65</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2359,31 +2359,31 @@
         <v>500</v>
       </c>
       <c r="F42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G42" t="n">
-        <v>0.16</v>
+        <v>0.91</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
-        <v>65.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="K42" t="n">
-        <v>65.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2405,31 +2405,31 @@
         <v>500</v>
       </c>
       <c r="F43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G43" t="n">
-        <v>0.16</v>
+        <v>1.04</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>65.2</v>
+        <v>91.5</v>
       </c>
       <c r="J43" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="K43" t="n">
-        <v>65.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2451,31 +2451,31 @@
         <v>500</v>
       </c>
       <c r="F44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G44" t="n">
-        <v>0.16</v>
+        <v>1.04</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>65.2</v>
+        <v>91.5</v>
       </c>
       <c r="J44" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="K44" t="n">
-        <v>65.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2497,31 +2497,31 @@
         <v>500</v>
       </c>
       <c r="F45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G45" t="n">
-        <v>0.16</v>
+        <v>1.04</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>65.2</v>
+        <v>91.5</v>
       </c>
       <c r="J45" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="K45" t="n">
-        <v>65.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2543,31 +2543,31 @@
         <v>500</v>
       </c>
       <c r="F46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G46" t="n">
-        <v>0.16</v>
+        <v>1.04</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>65.2</v>
+        <v>91.5</v>
       </c>
       <c r="J46" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="K46" t="n">
-        <v>65.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2589,31 +2589,31 @@
         <v>500</v>
       </c>
       <c r="F47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>65.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>65.2</v>
+        <v>93.8</v>
       </c>
       <c r="K47" t="n">
-        <v>65.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2635,31 +2635,31 @@
         <v>500</v>
       </c>
       <c r="F48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>65.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>65.2</v>
+        <v>94.2</v>
       </c>
       <c r="K48" t="n">
-        <v>65.2</v>
+        <v>92</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2681,31 +2681,31 @@
         <v>500</v>
       </c>
       <c r="F49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>65.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>65.2</v>
+        <v>94.2</v>
       </c>
       <c r="K49" t="n">
-        <v>65.2</v>
+        <v>92</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2727,31 +2727,31 @@
         <v>500</v>
       </c>
       <c r="F50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>65.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>65.2</v>
+        <v>94.2</v>
       </c>
       <c r="K50" t="n">
-        <v>65.2</v>
+        <v>92</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2773,31 +2773,31 @@
         <v>500</v>
       </c>
       <c r="F51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>65.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>65.2</v>
+        <v>94.2</v>
       </c>
       <c r="K51" t="n">
-        <v>65.2</v>
+        <v>92</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -2822,28 +2822,28 @@
         <v>1.18</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>65.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>65.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>65.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2868,28 +2868,28 @@
         <v>1.18</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>65.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>65.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>65.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2914,28 +2914,28 @@
         <v>1.18</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>65.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>65.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>65.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2960,28 +2960,28 @@
         <v>1.18</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>65.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>65.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>65.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3006,28 +3006,28 @@
         <v>1.18</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I56" t="n">
-        <v>65.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>65.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>65.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3049,31 +3049,31 @@
         <v>500</v>
       </c>
       <c r="F57" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G57" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I57" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J57" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3095,31 +3095,31 @@
         <v>500</v>
       </c>
       <c r="F58" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G58" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I58" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J58" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3141,31 +3141,31 @@
         <v>500</v>
       </c>
       <c r="F59" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G59" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I59" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J59" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3187,31 +3187,31 @@
         <v>500</v>
       </c>
       <c r="F60" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G60" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I60" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J60" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3233,31 +3233,31 @@
         <v>500</v>
       </c>
       <c r="F61" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G61" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I61" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J61" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3279,31 +3279,31 @@
         <v>500</v>
       </c>
       <c r="F62" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G62" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I62" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J62" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -3325,31 +3325,31 @@
         <v>500</v>
       </c>
       <c r="F63" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G63" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I63" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J63" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -3371,31 +3371,31 @@
         <v>500</v>
       </c>
       <c r="F64" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G64" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I64" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J64" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -3417,31 +3417,31 @@
         <v>500</v>
       </c>
       <c r="F65" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G65" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I65" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J65" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -3463,31 +3463,31 @@
         <v>500</v>
       </c>
       <c r="F66" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G66" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I66" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J66" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -3509,31 +3509,31 @@
         <v>500</v>
       </c>
       <c r="F67" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G67" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I67" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J67" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -3555,31 +3555,31 @@
         <v>500</v>
       </c>
       <c r="F68" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G68" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I68" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J68" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -3601,31 +3601,31 @@
         <v>500</v>
       </c>
       <c r="F69" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G69" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I69" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J69" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -3647,31 +3647,31 @@
         <v>500</v>
       </c>
       <c r="F70" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G70" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I70" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J70" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -3693,31 +3693,31 @@
         <v>500</v>
       </c>
       <c r="F71" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G71" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I71" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J71" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -3739,31 +3739,31 @@
         <v>500</v>
       </c>
       <c r="F72" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G72" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I72" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J72" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -3785,31 +3785,31 @@
         <v>500</v>
       </c>
       <c r="F73" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G73" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I73" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J73" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -3831,31 +3831,31 @@
         <v>500</v>
       </c>
       <c r="F74" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G74" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I74" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J74" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -3877,31 +3877,31 @@
         <v>500</v>
       </c>
       <c r="F75" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G75" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I75" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J75" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -3923,31 +3923,31 @@
         <v>500</v>
       </c>
       <c r="F76" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G76" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I76" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J76" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -3969,31 +3969,31 @@
         <v>500</v>
       </c>
       <c r="F77" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G77" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I77" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J77" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -4015,31 +4015,31 @@
         <v>500</v>
       </c>
       <c r="F78" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G78" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I78" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J78" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -4061,31 +4061,31 @@
         <v>500</v>
       </c>
       <c r="F79" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G79" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I79" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J79" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -4107,31 +4107,31 @@
         <v>500</v>
       </c>
       <c r="F80" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G80" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I80" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J80" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -4153,31 +4153,31 @@
         <v>500</v>
       </c>
       <c r="F81" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G81" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I81" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J81" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -4199,31 +4199,31 @@
         <v>500</v>
       </c>
       <c r="F82" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G82" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I82" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J82" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -4245,31 +4245,31 @@
         <v>500</v>
       </c>
       <c r="F83" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G83" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I83" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J83" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -4291,31 +4291,31 @@
         <v>500</v>
       </c>
       <c r="F84" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G84" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I84" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J84" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -4337,31 +4337,31 @@
         <v>500</v>
       </c>
       <c r="F85" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G85" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I85" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J85" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -4383,31 +4383,31 @@
         <v>500</v>
       </c>
       <c r="F86" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G86" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I86" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J86" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -4429,31 +4429,31 @@
         <v>500</v>
       </c>
       <c r="F87" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G87" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I87" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J87" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
@@ -4475,31 +4475,31 @@
         <v>500</v>
       </c>
       <c r="F88" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G88" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I88" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J88" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -4521,31 +4521,31 @@
         <v>500</v>
       </c>
       <c r="F89" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G89" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I89" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J89" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K89" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -4567,31 +4567,31 @@
         <v>500</v>
       </c>
       <c r="F90" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G90" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I90" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J90" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K90" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -4613,31 +4613,31 @@
         <v>500</v>
       </c>
       <c r="F91" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G91" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I91" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J91" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K91" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -4659,31 +4659,31 @@
         <v>500</v>
       </c>
       <c r="F92" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G92" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I92" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J92" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K92" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -4705,31 +4705,31 @@
         <v>500</v>
       </c>
       <c r="F93" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G93" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I93" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J93" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K93" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -4751,31 +4751,31 @@
         <v>500</v>
       </c>
       <c r="F94" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G94" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I94" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J94" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K94" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -4797,31 +4797,31 @@
         <v>500</v>
       </c>
       <c r="F95" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G95" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I95" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J95" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K95" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
@@ -4843,31 +4843,31 @@
         <v>500</v>
       </c>
       <c r="F96" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G96" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I96" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J96" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K96" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
@@ -4889,31 +4889,31 @@
         <v>500</v>
       </c>
       <c r="F97" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G97" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I97" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J97" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K97" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -4935,31 +4935,31 @@
         <v>500</v>
       </c>
       <c r="F98" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G98" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I98" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J98" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K98" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -4981,31 +4981,31 @@
         <v>500</v>
       </c>
       <c r="F99" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G99" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I99" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J99" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K99" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -5027,31 +5027,31 @@
         <v>500</v>
       </c>
       <c r="F100" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G100" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I100" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J100" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K100" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -5073,31 +5073,31 @@
         <v>500</v>
       </c>
       <c r="F101" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G101" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I101" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J101" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K101" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -5119,31 +5119,31 @@
         <v>500</v>
       </c>
       <c r="F102" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G102" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I102" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J102" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K102" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -5165,31 +5165,31 @@
         <v>500</v>
       </c>
       <c r="F103" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G103" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I103" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J103" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K103" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -5211,31 +5211,31 @@
         <v>500</v>
       </c>
       <c r="F104" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G104" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I104" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J104" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K104" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -5257,31 +5257,31 @@
         <v>500</v>
       </c>
       <c r="F105" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G105" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I105" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J105" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K105" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -5303,31 +5303,31 @@
         <v>500</v>
       </c>
       <c r="F106" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G106" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I106" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J106" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K106" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -5349,31 +5349,31 @@
         <v>500</v>
       </c>
       <c r="F107" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G107" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I107" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J107" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K107" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -5395,31 +5395,31 @@
         <v>500</v>
       </c>
       <c r="F108" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G108" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I108" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J108" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K108" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -5441,31 +5441,31 @@
         <v>500</v>
       </c>
       <c r="F109" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G109" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I109" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J109" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K109" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -5487,31 +5487,31 @@
         <v>500</v>
       </c>
       <c r="F110" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G110" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I110" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J110" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K110" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -5533,31 +5533,31 @@
         <v>500</v>
       </c>
       <c r="F111" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G111" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I111" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J111" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K111" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -5582,28 +5582,28 @@
         <v>1.18</v>
       </c>
       <c r="G112" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I112" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J112" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K112" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -5628,28 +5628,28 @@
         <v>1.18</v>
       </c>
       <c r="G113" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I113" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J113" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K113" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -5674,28 +5674,28 @@
         <v>1.18</v>
       </c>
       <c r="G114" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I114" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J114" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K114" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -5720,28 +5720,28 @@
         <v>1.18</v>
       </c>
       <c r="G115" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I115" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J115" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K115" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -5766,28 +5766,28 @@
         <v>1.18</v>
       </c>
       <c r="G116" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I116" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J116" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K116" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -5812,28 +5812,28 @@
         <v>1.18</v>
       </c>
       <c r="G117" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I117" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J117" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K117" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -5858,28 +5858,28 @@
         <v>1.18</v>
       </c>
       <c r="G118" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I118" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K118" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -5904,28 +5904,28 @@
         <v>1.18</v>
       </c>
       <c r="G119" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I119" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K119" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -5950,28 +5950,28 @@
         <v>1.18</v>
       </c>
       <c r="G120" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I120" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J120" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K120" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -5996,28 +5996,28 @@
         <v>1.18</v>
       </c>
       <c r="G121" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I121" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J121" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K121" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -6042,28 +6042,28 @@
         <v>1.18</v>
       </c>
       <c r="G122" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I122" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J122" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K122" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -6088,28 +6088,28 @@
         <v>1.18</v>
       </c>
       <c r="G123" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I123" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J123" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K123" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -6134,28 +6134,28 @@
         <v>1.18</v>
       </c>
       <c r="G124" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I124" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J124" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K124" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -6180,28 +6180,28 @@
         <v>1.18</v>
       </c>
       <c r="G125" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I125" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J125" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K125" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -6226,28 +6226,28 @@
         <v>1.18</v>
       </c>
       <c r="G126" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I126" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J126" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K126" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -6272,28 +6272,28 @@
         <v>1.18</v>
       </c>
       <c r="G127" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I127" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J127" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K127" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -6318,28 +6318,28 @@
         <v>1.18</v>
       </c>
       <c r="G128" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I128" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J128" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K128" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -6364,28 +6364,28 @@
         <v>1.18</v>
       </c>
       <c r="G129" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I129" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J129" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K129" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -6410,28 +6410,28 @@
         <v>1.18</v>
       </c>
       <c r="G130" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I130" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J130" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K130" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -6456,28 +6456,28 @@
         <v>1.18</v>
       </c>
       <c r="G131" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I131" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J131" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K131" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -6502,28 +6502,28 @@
         <v>1.18</v>
       </c>
       <c r="G132" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I132" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J132" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K132" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -6548,28 +6548,28 @@
         <v>1.18</v>
       </c>
       <c r="G133" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I133" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J133" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K133" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -6594,28 +6594,28 @@
         <v>1.18</v>
       </c>
       <c r="G134" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I134" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J134" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K134" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -6640,28 +6640,28 @@
         <v>1.18</v>
       </c>
       <c r="G135" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I135" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J135" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K135" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -6686,28 +6686,28 @@
         <v>1.18</v>
       </c>
       <c r="G136" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I136" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J136" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K136" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -6732,28 +6732,28 @@
         <v>1.18</v>
       </c>
       <c r="G137" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I137" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J137" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K137" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -6778,28 +6778,28 @@
         <v>1.18</v>
       </c>
       <c r="G138" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I138" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J138" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K138" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -6824,28 +6824,28 @@
         <v>1.18</v>
       </c>
       <c r="G139" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I139" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J139" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K139" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -6870,28 +6870,28 @@
         <v>1.18</v>
       </c>
       <c r="G140" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I140" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J140" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K140" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -6916,28 +6916,28 @@
         <v>1.18</v>
       </c>
       <c r="G141" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I141" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J141" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K141" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -6962,28 +6962,28 @@
         <v>1.18</v>
       </c>
       <c r="G142" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I142" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K142" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -7008,28 +7008,28 @@
         <v>1.18</v>
       </c>
       <c r="G143" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I143" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K143" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -7054,28 +7054,28 @@
         <v>1.18</v>
       </c>
       <c r="G144" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I144" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J144" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K144" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -7100,28 +7100,28 @@
         <v>1.18</v>
       </c>
       <c r="G145" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I145" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J145" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K145" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -7146,28 +7146,28 @@
         <v>1.18</v>
       </c>
       <c r="G146" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I146" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J146" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K146" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -7192,28 +7192,28 @@
         <v>1.18</v>
       </c>
       <c r="G147" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I147" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K147" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -7238,28 +7238,28 @@
         <v>1.18</v>
       </c>
       <c r="G148" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I148" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J148" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K148" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -7284,28 +7284,28 @@
         <v>1.18</v>
       </c>
       <c r="G149" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I149" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J149" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K149" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -7330,28 +7330,28 @@
         <v>1.18</v>
       </c>
       <c r="G150" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I150" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J150" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K150" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -7376,28 +7376,28 @@
         <v>1.18</v>
       </c>
       <c r="G151" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I151" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J151" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K151" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -7422,28 +7422,28 @@
         <v>1.18</v>
       </c>
       <c r="G152" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I152" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J152" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K152" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -7468,28 +7468,28 @@
         <v>1.18</v>
       </c>
       <c r="G153" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I153" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K153" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -7514,28 +7514,28 @@
         <v>1.18</v>
       </c>
       <c r="G154" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I154" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J154" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K154" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -7560,28 +7560,28 @@
         <v>1.18</v>
       </c>
       <c r="G155" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H155" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I155" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J155" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K155" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -7606,28 +7606,28 @@
         <v>1.18</v>
       </c>
       <c r="G156" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I156" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J156" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K156" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -7652,28 +7652,28 @@
         <v>1.18</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I157" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J157" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K157" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -7698,28 +7698,28 @@
         <v>1.18</v>
       </c>
       <c r="G158" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I158" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K158" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -7744,28 +7744,28 @@
         <v>1.18</v>
       </c>
       <c r="G159" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I159" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J159" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K159" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -7790,28 +7790,28 @@
         <v>1.18</v>
       </c>
       <c r="G160" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I160" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K160" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -7836,28 +7836,28 @@
         <v>1.18</v>
       </c>
       <c r="G161" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I161" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J161" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K161" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -7882,28 +7882,28 @@
         <v>1.18</v>
       </c>
       <c r="G162" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I162" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J162" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K162" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -7928,28 +7928,28 @@
         <v>1.18</v>
       </c>
       <c r="G163" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I163" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J163" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K163" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -7974,28 +7974,28 @@
         <v>1.18</v>
       </c>
       <c r="G164" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H164" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I164" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J164" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K164" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -8020,28 +8020,28 @@
         <v>1.18</v>
       </c>
       <c r="G165" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I165" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J165" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K165" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -8066,28 +8066,28 @@
         <v>1.18</v>
       </c>
       <c r="G166" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H166" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I166" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J166" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K166" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -8112,28 +8112,28 @@
         <v>1.01</v>
       </c>
       <c r="G167" t="n">
-        <v>2.76</v>
+        <v>16.94</v>
       </c>
       <c r="H167" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I167" t="n">
-        <v>68.8</v>
+        <v>115.4</v>
       </c>
       <c r="J167" t="n">
-        <v>62.1</v>
+        <v>74.8</v>
       </c>
       <c r="K167" t="n">
-        <v>64.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="L167" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M167" t="n">
         <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -8155,31 +8155,31 @@
         <v>500</v>
       </c>
       <c r="F168" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G168" t="n">
-        <v>2.22</v>
+        <v>6.76</v>
       </c>
       <c r="H168" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I168" t="n">
-        <v>68</v>
+        <v>101.9</v>
       </c>
       <c r="J168" t="n">
-        <v>62.6</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K168" t="n">
-        <v>64.8</v>
+        <v>90.2</v>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -8201,31 +8201,31 @@
         <v>500</v>
       </c>
       <c r="F169" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G169" t="n">
-        <v>2.22</v>
+        <v>6.76</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I169" t="n">
-        <v>68</v>
+        <v>101.9</v>
       </c>
       <c r="J169" t="n">
-        <v>62.6</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K169" t="n">
-        <v>64.8</v>
+        <v>90.2</v>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -8247,31 +8247,31 @@
         <v>500</v>
       </c>
       <c r="F170" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G170" t="n">
-        <v>2.22</v>
+        <v>6.76</v>
       </c>
       <c r="H170" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I170" t="n">
-        <v>68</v>
+        <v>101.9</v>
       </c>
       <c r="J170" t="n">
-        <v>62.6</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K170" t="n">
-        <v>64.8</v>
+        <v>90.2</v>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -8293,31 +8293,31 @@
         <v>500</v>
       </c>
       <c r="F171" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G171" t="n">
-        <v>2.22</v>
+        <v>6.76</v>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I171" t="n">
-        <v>68</v>
+        <v>101.9</v>
       </c>
       <c r="J171" t="n">
-        <v>62.6</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K171" t="n">
-        <v>64.8</v>
+        <v>90.2</v>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -8342,28 +8342,28 @@
         <v>1.01</v>
       </c>
       <c r="G172" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I172" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J172" t="n">
-        <v>65</v>
+        <v>92.5</v>
       </c>
       <c r="K172" t="n">
-        <v>65.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -8385,31 +8385,31 @@
         <v>500</v>
       </c>
       <c r="F173" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G173" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H173" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I173" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J173" t="n">
-        <v>65</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K173" t="n">
-        <v>65.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -8431,31 +8431,31 @@
         <v>500</v>
       </c>
       <c r="F174" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G174" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H174" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I174" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J174" t="n">
-        <v>65</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K174" t="n">
-        <v>65.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -8477,31 +8477,31 @@
         <v>500</v>
       </c>
       <c r="F175" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G175" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H175" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I175" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J175" t="n">
-        <v>65</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K175" t="n">
-        <v>65.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -8523,31 +8523,31 @@
         <v>500</v>
       </c>
       <c r="F176" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G176" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H176" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I176" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J176" t="n">
-        <v>65</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K176" t="n">
-        <v>65.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -8572,28 +8572,28 @@
         <v>1.01</v>
       </c>
       <c r="G177" t="n">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="H177" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I177" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J177" t="n">
-        <v>65</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K177" t="n">
-        <v>65.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
@@ -8615,31 +8615,31 @@
         <v>500</v>
       </c>
       <c r="F178" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G178" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H178" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I178" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J178" t="n">
-        <v>65</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K178" t="n">
-        <v>65.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -8661,31 +8661,31 @@
         <v>500</v>
       </c>
       <c r="F179" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G179" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H179" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I179" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J179" t="n">
-        <v>65</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K179" t="n">
-        <v>65.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -8707,31 +8707,31 @@
         <v>500</v>
       </c>
       <c r="F180" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G180" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H180" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I180" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J180" t="n">
-        <v>65</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K180" t="n">
-        <v>65.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -8753,31 +8753,31 @@
         <v>500</v>
       </c>
       <c r="F181" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G181" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I181" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J181" t="n">
-        <v>65</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K181" t="n">
-        <v>65.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -8802,28 +8802,28 @@
         <v>1.01</v>
       </c>
       <c r="G182" t="n">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I182" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J182" t="n">
-        <v>65</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K182" t="n">
-        <v>65.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -8845,31 +8845,31 @@
         <v>500</v>
       </c>
       <c r="F183" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G183" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I183" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J183" t="n">
-        <v>65</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K183" t="n">
-        <v>65.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -8891,31 +8891,31 @@
         <v>500</v>
       </c>
       <c r="F184" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G184" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I184" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J184" t="n">
-        <v>65</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K184" t="n">
-        <v>65.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -8937,31 +8937,31 @@
         <v>500</v>
       </c>
       <c r="F185" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G185" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H185" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I185" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J185" t="n">
-        <v>65</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K185" t="n">
-        <v>65.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -8983,31 +8983,31 @@
         <v>500</v>
       </c>
       <c r="F186" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G186" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H186" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I186" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J186" t="n">
-        <v>65</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K186" t="n">
-        <v>65.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -9032,28 +9032,28 @@
         <v>1.01</v>
       </c>
       <c r="G187" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="H187" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I187" t="n">
-        <v>65.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J187" t="n">
-        <v>65</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K187" t="n">
-        <v>65.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -9075,31 +9075,31 @@
         <v>500</v>
       </c>
       <c r="F188" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G188" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
       <c r="H188" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I188" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J188" t="n">
-        <v>65</v>
+        <v>92.5</v>
       </c>
       <c r="K188" t="n">
-        <v>65.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -9121,31 +9121,31 @@
         <v>500</v>
       </c>
       <c r="F189" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G189" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
       <c r="H189" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I189" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J189" t="n">
-        <v>65</v>
+        <v>92.5</v>
       </c>
       <c r="K189" t="n">
-        <v>65.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -9167,31 +9167,31 @@
         <v>500</v>
       </c>
       <c r="F190" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G190" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
       <c r="H190" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I190" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J190" t="n">
-        <v>65</v>
+        <v>92.5</v>
       </c>
       <c r="K190" t="n">
-        <v>65.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -9213,31 +9213,31 @@
         <v>500</v>
       </c>
       <c r="F191" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G191" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
       <c r="H191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I191" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J191" t="n">
-        <v>65</v>
+        <v>92.5</v>
       </c>
       <c r="K191" t="n">
-        <v>65.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -9259,31 +9259,31 @@
         <v>500</v>
       </c>
       <c r="F192" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G192" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="H192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I192" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J192" t="n">
-        <v>65</v>
+        <v>92.8</v>
       </c>
       <c r="K192" t="n">
-        <v>65.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -9305,31 +9305,31 @@
         <v>500</v>
       </c>
       <c r="F193" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G193" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="H193" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I193" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J193" t="n">
-        <v>65</v>
+        <v>92.7</v>
       </c>
       <c r="K193" t="n">
-        <v>65.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -9351,31 +9351,31 @@
         <v>500</v>
       </c>
       <c r="F194" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G194" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="H194" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I194" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J194" t="n">
-        <v>65</v>
+        <v>92.7</v>
       </c>
       <c r="K194" t="n">
-        <v>65.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -9397,31 +9397,31 @@
         <v>500</v>
       </c>
       <c r="F195" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G195" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="H195" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I195" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J195" t="n">
-        <v>65</v>
+        <v>92.7</v>
       </c>
       <c r="K195" t="n">
-        <v>65.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -9443,31 +9443,31 @@
         <v>500</v>
       </c>
       <c r="F196" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G196" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="H196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I196" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J196" t="n">
-        <v>65</v>
+        <v>92.7</v>
       </c>
       <c r="K196" t="n">
-        <v>65.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -9489,31 +9489,31 @@
         <v>500</v>
       </c>
       <c r="F197" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G197" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H197" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I197" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J197" t="n">
-        <v>65</v>
+        <v>92.8</v>
       </c>
       <c r="K197" t="n">
-        <v>65.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -9535,31 +9535,31 @@
         <v>500</v>
       </c>
       <c r="F198" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G198" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="H198" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I198" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J198" t="n">
-        <v>65</v>
+        <v>92.8</v>
       </c>
       <c r="K198" t="n">
-        <v>65.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -9581,31 +9581,31 @@
         <v>500</v>
       </c>
       <c r="F199" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G199" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="H199" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I199" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J199" t="n">
-        <v>65</v>
+        <v>92.8</v>
       </c>
       <c r="K199" t="n">
-        <v>65.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -9627,31 +9627,31 @@
         <v>500</v>
       </c>
       <c r="F200" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G200" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="H200" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I200" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J200" t="n">
-        <v>65</v>
+        <v>92.8</v>
       </c>
       <c r="K200" t="n">
-        <v>65.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -9673,31 +9673,31 @@
         <v>500</v>
       </c>
       <c r="F201" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G201" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="H201" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I201" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J201" t="n">
-        <v>65</v>
+        <v>92.8</v>
       </c>
       <c r="K201" t="n">
-        <v>65.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202">
@@ -9719,31 +9719,31 @@
         <v>500</v>
       </c>
       <c r="F202" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G202" t="n">
         <v>0.17</v>
       </c>
       <c r="H202" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I202" t="n">
-        <v>65.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J202" t="n">
-        <v>65</v>
+        <v>92.7</v>
       </c>
       <c r="K202" t="n">
-        <v>65.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203">
@@ -9765,31 +9765,31 @@
         <v>500</v>
       </c>
       <c r="F203" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G203" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H203" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I203" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J203" t="n">
-        <v>65</v>
+        <v>92.7</v>
       </c>
       <c r="K203" t="n">
-        <v>65.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -9811,31 +9811,31 @@
         <v>500</v>
       </c>
       <c r="F204" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G204" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H204" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I204" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J204" t="n">
-        <v>65</v>
+        <v>92.7</v>
       </c>
       <c r="K204" t="n">
-        <v>65.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -9857,31 +9857,31 @@
         <v>500</v>
       </c>
       <c r="F205" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G205" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H205" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I205" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J205" t="n">
-        <v>65</v>
+        <v>92.7</v>
       </c>
       <c r="K205" t="n">
-        <v>65.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -9903,31 +9903,31 @@
         <v>500</v>
       </c>
       <c r="F206" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G206" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I206" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J206" t="n">
-        <v>65</v>
+        <v>92.7</v>
       </c>
       <c r="K206" t="n">
-        <v>65.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -9949,31 +9949,31 @@
         <v>500</v>
       </c>
       <c r="F207" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G207" t="n">
         <v>0.17</v>
       </c>
       <c r="H207" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I207" t="n">
-        <v>65.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J207" t="n">
-        <v>65</v>
+        <v>92.7</v>
       </c>
       <c r="K207" t="n">
-        <v>65.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -9995,31 +9995,31 @@
         <v>500</v>
       </c>
       <c r="F208" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G208" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H208" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I208" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J208" t="n">
-        <v>65</v>
+        <v>92.7</v>
       </c>
       <c r="K208" t="n">
-        <v>65.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -10041,31 +10041,31 @@
         <v>500</v>
       </c>
       <c r="F209" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G209" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H209" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I209" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J209" t="n">
-        <v>65</v>
+        <v>92.7</v>
       </c>
       <c r="K209" t="n">
-        <v>65.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -10087,31 +10087,31 @@
         <v>500</v>
       </c>
       <c r="F210" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G210" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H210" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I210" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J210" t="n">
-        <v>65</v>
+        <v>92.7</v>
       </c>
       <c r="K210" t="n">
-        <v>65.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -10133,31 +10133,31 @@
         <v>500</v>
       </c>
       <c r="F211" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G211" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H211" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I211" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J211" t="n">
-        <v>65</v>
+        <v>92.7</v>
       </c>
       <c r="K211" t="n">
-        <v>65.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
@@ -10179,31 +10179,31 @@
         <v>500</v>
       </c>
       <c r="F212" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G212" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H212" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I212" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J212" t="n">
-        <v>65</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K212" t="n">
-        <v>65.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
@@ -10225,31 +10225,31 @@
         <v>500</v>
       </c>
       <c r="F213" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G213" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H213" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I213" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J213" t="n">
-        <v>65</v>
+        <v>92.8</v>
       </c>
       <c r="K213" t="n">
-        <v>65.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214">
@@ -10271,31 +10271,31 @@
         <v>500</v>
       </c>
       <c r="F214" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G214" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H214" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I214" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J214" t="n">
-        <v>65</v>
+        <v>92.8</v>
       </c>
       <c r="K214" t="n">
-        <v>65.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -10317,31 +10317,31 @@
         <v>500</v>
       </c>
       <c r="F215" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G215" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H215" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I215" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J215" t="n">
-        <v>65</v>
+        <v>92.8</v>
       </c>
       <c r="K215" t="n">
-        <v>65.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
@@ -10363,31 +10363,31 @@
         <v>500</v>
       </c>
       <c r="F216" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G216" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H216" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I216" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J216" t="n">
-        <v>65</v>
+        <v>92.8</v>
       </c>
       <c r="K216" t="n">
-        <v>65.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -10409,31 +10409,31 @@
         <v>500</v>
       </c>
       <c r="F217" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G217" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="H217" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I217" t="n">
-        <v>65.3</v>
+        <v>92.8</v>
       </c>
       <c r="J217" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="K217" t="n">
-        <v>65.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -10455,31 +10455,31 @@
         <v>500</v>
       </c>
       <c r="F218" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G218" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="H218" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I218" t="n">
-        <v>65.3</v>
+        <v>92.8</v>
       </c>
       <c r="J218" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="K218" t="n">
-        <v>65.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
@@ -10501,31 +10501,31 @@
         <v>500</v>
       </c>
       <c r="F219" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G219" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="H219" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I219" t="n">
-        <v>65.3</v>
+        <v>92.8</v>
       </c>
       <c r="J219" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="K219" t="n">
-        <v>65.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
@@ -10547,31 +10547,31 @@
         <v>500</v>
       </c>
       <c r="F220" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G220" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="H220" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I220" t="n">
-        <v>65.3</v>
+        <v>92.8</v>
       </c>
       <c r="J220" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="K220" t="n">
-        <v>65.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -10593,31 +10593,31 @@
         <v>500</v>
       </c>
       <c r="F221" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G221" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="H221" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I221" t="n">
-        <v>65.3</v>
+        <v>92.8</v>
       </c>
       <c r="J221" t="n">
-        <v>65.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="K221" t="n">
-        <v>65.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Sensitivity_Output/Sensitivity_Analysis_Full.xlsx
+++ b/Sensitivity_Output/Sensitivity_Analysis_Full.xlsx
@@ -519,31 +519,31 @@
         <v>500</v>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>0.26</v>
       </c>
       <c r="G2" t="n">
-        <v>16.94</v>
+        <v>10.21</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>115.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>74.8</v>
+        <v>65.8</v>
       </c>
       <c r="K2" t="n">
-        <v>87.7</v>
+        <v>88.3</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -565,31 +565,31 @@
         <v>500</v>
       </c>
       <c r="F3" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G3" t="n">
-        <v>4.15</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>98.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>88.8</v>
+        <v>65.8</v>
       </c>
       <c r="K3" t="n">
-        <v>90.7</v>
+        <v>87.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -611,31 +611,31 @@
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G4" t="n">
-        <v>4.15</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>98.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>88.8</v>
+        <v>65.8</v>
       </c>
       <c r="K4" t="n">
-        <v>90.7</v>
+        <v>87.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -657,31 +657,31 @@
         <v>500</v>
       </c>
       <c r="F5" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G5" t="n">
-        <v>4.15</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>98.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>88.8</v>
+        <v>65.8</v>
       </c>
       <c r="K5" t="n">
-        <v>90.7</v>
+        <v>87.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -703,31 +703,31 @@
         <v>500</v>
       </c>
       <c r="F6" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G6" t="n">
-        <v>4.15</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>98.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>88.8</v>
+        <v>65.8</v>
       </c>
       <c r="K6" t="n">
-        <v>90.7</v>
+        <v>87.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -749,31 +749,31 @@
         <v>500</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.26</v>
       </c>
       <c r="G7" t="n">
-        <v>0.78</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>91.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="J7" t="n">
-        <v>93.5</v>
+        <v>66</v>
       </c>
       <c r="K7" t="n">
-        <v>92.8</v>
+        <v>88</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -795,31 +795,31 @@
         <v>500</v>
       </c>
       <c r="F8" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G8" t="n">
-        <v>0.87</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>91.7</v>
+        <v>68.3</v>
       </c>
       <c r="J8" t="n">
-        <v>93.8</v>
+        <v>66</v>
       </c>
       <c r="K8" t="n">
-        <v>92.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -841,31 +841,31 @@
         <v>500</v>
       </c>
       <c r="F9" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G9" t="n">
-        <v>0.87</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>91.7</v>
+        <v>68.3</v>
       </c>
       <c r="J9" t="n">
-        <v>93.8</v>
+        <v>66</v>
       </c>
       <c r="K9" t="n">
-        <v>92.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -887,31 +887,31 @@
         <v>500</v>
       </c>
       <c r="F10" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G10" t="n">
-        <v>0.87</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>91.7</v>
+        <v>68.3</v>
       </c>
       <c r="J10" t="n">
-        <v>93.8</v>
+        <v>66</v>
       </c>
       <c r="K10" t="n">
-        <v>92.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -933,31 +933,31 @@
         <v>500</v>
       </c>
       <c r="F11" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G11" t="n">
-        <v>0.87</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>91.7</v>
+        <v>68.3</v>
       </c>
       <c r="J11" t="n">
-        <v>93.8</v>
+        <v>66</v>
       </c>
       <c r="K11" t="n">
-        <v>92.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -979,31 +979,31 @@
         <v>500</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.26</v>
       </c>
       <c r="G12" t="n">
-        <v>0.78</v>
+        <v>9.16</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>91.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="J12" t="n">
-        <v>93.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>92.8</v>
+        <v>86.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1025,31 +1025,31 @@
         <v>500</v>
       </c>
       <c r="F13" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G13" t="n">
-        <v>0.87</v>
+        <v>9.01</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>91.7</v>
+        <v>68.8</v>
       </c>
       <c r="J13" t="n">
-        <v>93.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>92.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1071,31 +1071,31 @@
         <v>500</v>
       </c>
       <c r="F14" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G14" t="n">
-        <v>0.87</v>
+        <v>9.01</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>91.7</v>
+        <v>68.8</v>
       </c>
       <c r="J14" t="n">
-        <v>93.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>92.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1117,31 +1117,31 @@
         <v>500</v>
       </c>
       <c r="F15" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G15" t="n">
-        <v>0.87</v>
+        <v>9.01</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>91.7</v>
+        <v>68.8</v>
       </c>
       <c r="J15" t="n">
-        <v>93.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>92.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1163,31 +1163,31 @@
         <v>500</v>
       </c>
       <c r="F16" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G16" t="n">
-        <v>0.87</v>
+        <v>9.01</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>91.7</v>
+        <v>68.8</v>
       </c>
       <c r="J16" t="n">
-        <v>93.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>92.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1209,28 +1209,28 @@
         <v>500</v>
       </c>
       <c r="F17" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="H17" t="n">
         <v>1</v>
       </c>
-      <c r="G17" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H17" t="n">
-        <v>3</v>
-      </c>
       <c r="I17" t="n">
-        <v>91.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>93.59999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>92.8</v>
+        <v>86</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
@@ -1255,31 +1255,31 @@
         <v>500</v>
       </c>
       <c r="F18" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G18" t="n">
-        <v>0.95</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>91.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="J18" t="n">
-        <v>93.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>92.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1301,31 +1301,31 @@
         <v>500</v>
       </c>
       <c r="F19" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.95</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>91.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="J19" t="n">
-        <v>93.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>92.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1347,31 +1347,31 @@
         <v>500</v>
       </c>
       <c r="F20" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G20" t="n">
-        <v>0.95</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>91.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="J20" t="n">
-        <v>93.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>92.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1393,31 +1393,31 @@
         <v>500</v>
       </c>
       <c r="F21" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G21" t="n">
-        <v>0.95</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>91.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="J21" t="n">
-        <v>93.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>92.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1439,31 +1439,31 @@
         <v>500</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0.26</v>
       </c>
       <c r="G22" t="n">
-        <v>0.84</v>
+        <v>7.71</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>91.5</v>
+        <v>69.8</v>
       </c>
       <c r="J22" t="n">
-        <v>93.5</v>
+        <v>67.2</v>
       </c>
       <c r="K22" t="n">
-        <v>92.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1485,31 +1485,31 @@
         <v>500</v>
       </c>
       <c r="F23" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9</v>
+        <v>7.71</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>91.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="J23" t="n">
-        <v>93.8</v>
+        <v>67.2</v>
       </c>
       <c r="K23" t="n">
-        <v>92.5</v>
+        <v>84.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1531,31 +1531,31 @@
         <v>500</v>
       </c>
       <c r="F24" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9</v>
+        <v>7.71</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>91.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="J24" t="n">
-        <v>93.8</v>
+        <v>67.2</v>
       </c>
       <c r="K24" t="n">
-        <v>92.5</v>
+        <v>84.7</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1577,31 +1577,31 @@
         <v>500</v>
       </c>
       <c r="F25" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9</v>
+        <v>7.71</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>91.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="J25" t="n">
-        <v>93.8</v>
+        <v>67.2</v>
       </c>
       <c r="K25" t="n">
-        <v>92.5</v>
+        <v>84.7</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1623,31 +1623,31 @@
         <v>500</v>
       </c>
       <c r="F26" t="n">
-        <v>1.02</v>
+        <v>0.26</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9</v>
+        <v>7.71</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>91.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="J26" t="n">
-        <v>93.8</v>
+        <v>67.2</v>
       </c>
       <c r="K26" t="n">
-        <v>92.5</v>
+        <v>84.7</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1669,31 +1669,31 @@
         <v>500</v>
       </c>
       <c r="F27" t="n">
-        <v>1.01</v>
+        <v>0.27</v>
       </c>
       <c r="G27" t="n">
-        <v>0.92</v>
+        <v>7.02</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>91.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>93.59999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>92.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1715,31 +1715,31 @@
         <v>500</v>
       </c>
       <c r="F28" t="n">
-        <v>1.02</v>
+        <v>0.27</v>
       </c>
       <c r="G28" t="n">
-        <v>0.98</v>
+        <v>7.02</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>91.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>93.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>92.5</v>
+        <v>83.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1761,31 +1761,31 @@
         <v>500</v>
       </c>
       <c r="F29" t="n">
-        <v>1.02</v>
+        <v>0.27</v>
       </c>
       <c r="G29" t="n">
-        <v>0.98</v>
+        <v>7.02</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>91.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>93.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>92.5</v>
+        <v>83.7</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1807,31 +1807,31 @@
         <v>500</v>
       </c>
       <c r="F30" t="n">
-        <v>1.02</v>
+        <v>0.27</v>
       </c>
       <c r="G30" t="n">
-        <v>0.98</v>
+        <v>7.02</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>91.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>93.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>92.5</v>
+        <v>83.7</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1853,31 +1853,31 @@
         <v>500</v>
       </c>
       <c r="F31" t="n">
-        <v>1.02</v>
+        <v>0.27</v>
       </c>
       <c r="G31" t="n">
-        <v>0.98</v>
+        <v>7.02</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>91.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>93.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>92.5</v>
+        <v>83.7</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1899,31 +1899,31 @@
         <v>500</v>
       </c>
       <c r="F32" t="n">
-        <v>1.01</v>
+        <v>0.28</v>
       </c>
       <c r="G32" t="n">
-        <v>0.83</v>
+        <v>5.99</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>91.5</v>
+        <v>71.2</v>
       </c>
       <c r="J32" t="n">
-        <v>93.5</v>
+        <v>68.3</v>
       </c>
       <c r="K32" t="n">
-        <v>92.8</v>
+        <v>82.2</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1945,31 +1945,31 @@
         <v>500</v>
       </c>
       <c r="F33" t="n">
-        <v>1.03</v>
+        <v>0.28</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9399999999999999</v>
+        <v>5.99</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>91.5</v>
+        <v>71.2</v>
       </c>
       <c r="J33" t="n">
-        <v>93.8</v>
+        <v>68.3</v>
       </c>
       <c r="K33" t="n">
-        <v>92.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1991,31 +1991,31 @@
         <v>500</v>
       </c>
       <c r="F34" t="n">
-        <v>1.03</v>
+        <v>0.28</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9399999999999999</v>
+        <v>5.99</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>91.5</v>
+        <v>71.2</v>
       </c>
       <c r="J34" t="n">
-        <v>93.8</v>
+        <v>68.3</v>
       </c>
       <c r="K34" t="n">
-        <v>92.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2037,31 +2037,31 @@
         <v>500</v>
       </c>
       <c r="F35" t="n">
-        <v>1.03</v>
+        <v>0.28</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9399999999999999</v>
+        <v>5.99</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>91.5</v>
+        <v>71.2</v>
       </c>
       <c r="J35" t="n">
-        <v>93.8</v>
+        <v>68.3</v>
       </c>
       <c r="K35" t="n">
-        <v>92.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2083,31 +2083,31 @@
         <v>500</v>
       </c>
       <c r="F36" t="n">
-        <v>1.03</v>
+        <v>0.28</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9399999999999999</v>
+        <v>5.99</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>91.5</v>
+        <v>71.2</v>
       </c>
       <c r="J36" t="n">
-        <v>93.8</v>
+        <v>68.3</v>
       </c>
       <c r="K36" t="n">
-        <v>92.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2129,31 +2129,31 @@
         <v>500</v>
       </c>
       <c r="F37" t="n">
-        <v>1.01</v>
+        <v>0.29</v>
       </c>
       <c r="G37" t="n">
-        <v>0.86</v>
+        <v>4.67</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>91.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>93.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="K37" t="n">
-        <v>92.7</v>
+        <v>80.3</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2175,31 +2175,31 @@
         <v>500</v>
       </c>
       <c r="F38" t="n">
-        <v>1.03</v>
+        <v>0.29</v>
       </c>
       <c r="G38" t="n">
-        <v>0.99</v>
+        <v>4.67</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>91.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>93.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="K38" t="n">
-        <v>92.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2221,31 +2221,31 @@
         <v>500</v>
       </c>
       <c r="F39" t="n">
-        <v>1.03</v>
+        <v>0.29</v>
       </c>
       <c r="G39" t="n">
-        <v>0.99</v>
+        <v>4.67</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>91.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>93.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="K39" t="n">
-        <v>92.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2267,31 +2267,31 @@
         <v>500</v>
       </c>
       <c r="F40" t="n">
-        <v>1.03</v>
+        <v>0.29</v>
       </c>
       <c r="G40" t="n">
-        <v>0.99</v>
+        <v>4.67</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>91.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>93.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="K40" t="n">
-        <v>92.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2313,31 +2313,31 @@
         <v>500</v>
       </c>
       <c r="F41" t="n">
-        <v>1.03</v>
+        <v>0.29</v>
       </c>
       <c r="G41" t="n">
-        <v>0.99</v>
+        <v>4.67</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>91.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>93.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="K41" t="n">
-        <v>92.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2359,31 +2359,31 @@
         <v>500</v>
       </c>
       <c r="F42" t="n">
-        <v>1.02</v>
+        <v>0.3</v>
       </c>
       <c r="G42" t="n">
-        <v>0.91</v>
+        <v>3.1</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>91.59999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>93.8</v>
+        <v>70.7</v>
       </c>
       <c r="K42" t="n">
-        <v>92.40000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2405,31 +2405,31 @@
         <v>500</v>
       </c>
       <c r="F43" t="n">
-        <v>1.03</v>
+        <v>0.3</v>
       </c>
       <c r="G43" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>91.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>94</v>
+        <v>70.7</v>
       </c>
       <c r="K43" t="n">
-        <v>92.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2451,31 +2451,31 @@
         <v>500</v>
       </c>
       <c r="F44" t="n">
-        <v>1.03</v>
+        <v>0.3</v>
       </c>
       <c r="G44" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>91.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>94</v>
+        <v>70.7</v>
       </c>
       <c r="K44" t="n">
-        <v>92.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2497,31 +2497,31 @@
         <v>500</v>
       </c>
       <c r="F45" t="n">
-        <v>1.03</v>
+        <v>0.3</v>
       </c>
       <c r="G45" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>91.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>94</v>
+        <v>70.7</v>
       </c>
       <c r="K45" t="n">
-        <v>92.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2543,31 +2543,31 @@
         <v>500</v>
       </c>
       <c r="F46" t="n">
-        <v>1.03</v>
+        <v>0.3</v>
       </c>
       <c r="G46" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>91.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>94</v>
+        <v>70.7</v>
       </c>
       <c r="K46" t="n">
-        <v>92.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2589,31 +2589,31 @@
         <v>500</v>
       </c>
       <c r="F47" t="n">
-        <v>1.03</v>
+        <v>0.34</v>
       </c>
       <c r="G47" t="n">
-        <v>0.85</v>
+        <v>1.6</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>91.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>93.8</v>
+        <v>72.3</v>
       </c>
       <c r="K47" t="n">
-        <v>92.09999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2635,31 +2635,31 @@
         <v>500</v>
       </c>
       <c r="F48" t="n">
-        <v>1.04</v>
+        <v>0.34</v>
       </c>
       <c r="G48" t="n">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>91.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>94.2</v>
+        <v>72.3</v>
       </c>
       <c r="K48" t="n">
-        <v>92</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2681,31 +2681,31 @@
         <v>500</v>
       </c>
       <c r="F49" t="n">
-        <v>1.04</v>
+        <v>0.34</v>
       </c>
       <c r="G49" t="n">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>91.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>94.2</v>
+        <v>72.3</v>
       </c>
       <c r="K49" t="n">
-        <v>92</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2727,31 +2727,31 @@
         <v>500</v>
       </c>
       <c r="F50" t="n">
-        <v>1.04</v>
+        <v>0.34</v>
       </c>
       <c r="G50" t="n">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>91.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>94.2</v>
+        <v>72.3</v>
       </c>
       <c r="K50" t="n">
-        <v>92</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2773,31 +2773,31 @@
         <v>500</v>
       </c>
       <c r="F51" t="n">
-        <v>1.04</v>
+        <v>0.34</v>
       </c>
       <c r="G51" t="n">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>91.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>94.2</v>
+        <v>72.3</v>
       </c>
       <c r="K51" t="n">
-        <v>92</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2819,31 +2819,31 @@
         <v>500</v>
       </c>
       <c r="F52" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G52" t="n">
-        <v>0.33</v>
+        <v>0.09</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>93.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="J52" t="n">
-        <v>92.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="K52" t="n">
-        <v>92.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2865,31 +2865,31 @@
         <v>500</v>
       </c>
       <c r="F53" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G53" t="n">
-        <v>0.33</v>
+        <v>0.09</v>
       </c>
       <c r="H53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>93.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="J53" t="n">
-        <v>92.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="K53" t="n">
-        <v>92.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2911,31 +2911,31 @@
         <v>500</v>
       </c>
       <c r="F54" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G54" t="n">
-        <v>0.33</v>
+        <v>0.09</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>93.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="J54" t="n">
-        <v>92.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="K54" t="n">
-        <v>92.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2957,31 +2957,31 @@
         <v>500</v>
       </c>
       <c r="F55" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G55" t="n">
-        <v>0.33</v>
+        <v>0.09</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>93.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="J55" t="n">
-        <v>92.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="K55" t="n">
-        <v>92.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3003,31 +3003,31 @@
         <v>500</v>
       </c>
       <c r="F56" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G56" t="n">
-        <v>0.33</v>
+        <v>0.09</v>
       </c>
       <c r="H56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>93.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="J56" t="n">
-        <v>92.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="K56" t="n">
-        <v>92.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3049,31 +3049,31 @@
         <v>500</v>
       </c>
       <c r="F57" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G57" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I57" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J57" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K57" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K57" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3095,31 +3095,31 @@
         <v>500</v>
       </c>
       <c r="F58" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G58" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I58" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J58" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K58" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K58" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3141,31 +3141,31 @@
         <v>500</v>
       </c>
       <c r="F59" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G59" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I59" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J59" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K59" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K59" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3187,31 +3187,31 @@
         <v>500</v>
       </c>
       <c r="F60" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G60" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H60" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J60" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K60" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K60" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3233,31 +3233,31 @@
         <v>500</v>
       </c>
       <c r="F61" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G61" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J61" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K61" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K61" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3279,31 +3279,31 @@
         <v>500</v>
       </c>
       <c r="F62" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G62" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I62" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J62" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K62" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K62" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -3325,31 +3325,31 @@
         <v>500</v>
       </c>
       <c r="F63" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G63" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H63" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J63" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K63" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K63" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -3371,31 +3371,31 @@
         <v>500</v>
       </c>
       <c r="F64" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G64" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I64" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J64" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K64" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K64" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -3417,31 +3417,31 @@
         <v>500</v>
       </c>
       <c r="F65" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G65" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I65" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J65" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K65" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K65" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -3463,31 +3463,31 @@
         <v>500</v>
       </c>
       <c r="F66" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G66" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I66" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J66" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K66" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K66" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -3509,31 +3509,31 @@
         <v>500</v>
       </c>
       <c r="F67" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G67" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I67" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J67" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K67" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K67" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -3555,31 +3555,31 @@
         <v>500</v>
       </c>
       <c r="F68" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G68" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J68" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K68" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K68" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -3601,31 +3601,31 @@
         <v>500</v>
       </c>
       <c r="F69" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G69" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I69" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J69" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K69" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K69" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -3647,31 +3647,31 @@
         <v>500</v>
       </c>
       <c r="F70" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G70" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I70" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J70" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K70" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K70" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -3693,31 +3693,31 @@
         <v>500</v>
       </c>
       <c r="F71" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G71" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J71" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K71" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K71" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -3739,31 +3739,31 @@
         <v>500</v>
       </c>
       <c r="F72" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G72" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H72" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J72" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K72" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K72" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -3785,31 +3785,31 @@
         <v>500</v>
       </c>
       <c r="F73" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G73" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J73" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K73" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K73" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -3831,31 +3831,31 @@
         <v>500</v>
       </c>
       <c r="F74" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G74" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H74" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J74" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K74" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K74" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -3877,31 +3877,31 @@
         <v>500</v>
       </c>
       <c r="F75" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G75" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H75" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I75" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J75" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K75" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K75" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -3923,31 +3923,31 @@
         <v>500</v>
       </c>
       <c r="F76" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G76" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J76" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K76" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K76" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -3969,31 +3969,31 @@
         <v>500</v>
       </c>
       <c r="F77" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G77" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H77" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I77" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J77" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K77" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K77" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4015,31 +4015,31 @@
         <v>500</v>
       </c>
       <c r="F78" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G78" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H78" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I78" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J78" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K78" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K78" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -4061,31 +4061,31 @@
         <v>500</v>
       </c>
       <c r="F79" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G79" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H79" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J79" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K79" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K79" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4107,31 +4107,31 @@
         <v>500</v>
       </c>
       <c r="F80" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G80" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I80" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J80" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K80" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K80" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -4153,31 +4153,31 @@
         <v>500</v>
       </c>
       <c r="F81" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G81" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H81" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I81" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J81" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K81" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K81" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -4199,31 +4199,31 @@
         <v>500</v>
       </c>
       <c r="F82" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G82" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I82" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J82" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K82" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K82" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -4245,31 +4245,31 @@
         <v>500</v>
       </c>
       <c r="F83" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G83" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H83" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I83" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J83" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K83" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K83" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -4291,31 +4291,31 @@
         <v>500</v>
       </c>
       <c r="F84" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G84" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I84" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J84" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K84" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K84" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -4337,31 +4337,31 @@
         <v>500</v>
       </c>
       <c r="F85" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G85" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I85" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J85" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K85" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K85" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -4383,31 +4383,31 @@
         <v>500</v>
       </c>
       <c r="F86" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G86" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I86" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J86" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K86" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K86" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -4429,31 +4429,31 @@
         <v>500</v>
       </c>
       <c r="F87" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G87" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H87" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I87" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J87" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K87" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K87" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -4475,31 +4475,31 @@
         <v>500</v>
       </c>
       <c r="F88" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G88" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H88" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J88" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K88" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K88" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -4521,31 +4521,31 @@
         <v>500</v>
       </c>
       <c r="F89" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G89" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H89" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I89" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J89" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K89" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K89" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -4567,31 +4567,31 @@
         <v>500</v>
       </c>
       <c r="F90" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G90" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H90" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I90" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J90" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K90" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K90" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -4613,31 +4613,31 @@
         <v>500</v>
       </c>
       <c r="F91" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G91" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I91" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J91" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K91" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K91" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -4659,31 +4659,31 @@
         <v>500</v>
       </c>
       <c r="F92" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G92" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H92" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J92" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K92" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K92" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -4705,31 +4705,31 @@
         <v>500</v>
       </c>
       <c r="F93" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G93" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H93" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J93" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K93" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K93" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -4751,31 +4751,31 @@
         <v>500</v>
       </c>
       <c r="F94" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G94" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H94" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I94" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J94" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K94" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K94" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -4797,31 +4797,31 @@
         <v>500</v>
       </c>
       <c r="F95" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G95" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H95" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J95" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K95" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K95" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -4843,31 +4843,31 @@
         <v>500</v>
       </c>
       <c r="F96" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G96" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H96" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I96" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J96" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K96" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K96" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -4889,31 +4889,31 @@
         <v>500</v>
       </c>
       <c r="F97" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G97" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H97" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J97" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K97" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K97" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -4935,31 +4935,31 @@
         <v>500</v>
       </c>
       <c r="F98" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G98" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H98" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I98" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J98" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K98" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K98" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -4981,31 +4981,31 @@
         <v>500</v>
       </c>
       <c r="F99" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G99" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H99" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I99" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J99" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K99" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K99" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -5027,31 +5027,31 @@
         <v>500</v>
       </c>
       <c r="F100" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G100" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H100" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J100" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K100" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K100" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -5073,31 +5073,31 @@
         <v>500</v>
       </c>
       <c r="F101" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G101" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H101" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I101" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J101" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K101" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K101" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -5119,31 +5119,31 @@
         <v>500</v>
       </c>
       <c r="F102" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G102" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H102" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I102" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J102" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K102" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K102" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -5165,31 +5165,31 @@
         <v>500</v>
       </c>
       <c r="F103" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G103" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H103" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I103" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J103" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K103" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K103" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -5211,31 +5211,31 @@
         <v>500</v>
       </c>
       <c r="F104" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G104" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I104" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J104" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K104" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K104" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -5257,31 +5257,31 @@
         <v>500</v>
       </c>
       <c r="F105" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G105" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H105" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I105" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J105" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K105" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K105" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -5303,31 +5303,31 @@
         <v>500</v>
       </c>
       <c r="F106" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G106" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H106" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I106" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J106" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K106" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K106" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -5349,31 +5349,31 @@
         <v>500</v>
       </c>
       <c r="F107" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G107" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H107" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I107" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J107" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K107" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K107" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -5395,31 +5395,31 @@
         <v>500</v>
       </c>
       <c r="F108" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G108" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H108" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I108" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J108" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K108" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K108" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -5441,31 +5441,31 @@
         <v>500</v>
       </c>
       <c r="F109" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G109" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H109" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I109" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J109" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K109" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K109" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -5487,31 +5487,31 @@
         <v>500</v>
       </c>
       <c r="F110" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G110" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H110" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I110" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J110" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K110" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K110" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -5533,31 +5533,31 @@
         <v>500</v>
       </c>
       <c r="F111" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G111" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H111" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I111" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J111" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K111" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K111" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -5579,31 +5579,31 @@
         <v>500</v>
       </c>
       <c r="F112" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G112" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J112" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K112" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -5625,31 +5625,31 @@
         <v>500</v>
       </c>
       <c r="F113" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G113" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J113" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K113" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -5671,31 +5671,31 @@
         <v>500</v>
       </c>
       <c r="F114" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G114" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J114" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K114" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -5717,31 +5717,31 @@
         <v>500</v>
       </c>
       <c r="F115" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G115" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J115" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K115" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -5763,31 +5763,31 @@
         <v>500</v>
       </c>
       <c r="F116" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G116" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J116" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K116" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -5809,31 +5809,31 @@
         <v>500</v>
       </c>
       <c r="F117" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G117" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H117" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J117" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K117" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -5855,31 +5855,31 @@
         <v>500</v>
       </c>
       <c r="F118" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G118" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H118" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J118" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K118" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -5901,31 +5901,31 @@
         <v>500</v>
       </c>
       <c r="F119" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G119" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J119" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K119" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -5947,31 +5947,31 @@
         <v>500</v>
       </c>
       <c r="F120" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G120" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J120" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K120" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -5993,31 +5993,31 @@
         <v>500</v>
       </c>
       <c r="F121" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G121" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J121" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K121" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -6039,31 +6039,31 @@
         <v>500</v>
       </c>
       <c r="F122" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G122" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J122" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K122" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -6085,31 +6085,31 @@
         <v>500</v>
       </c>
       <c r="F123" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G123" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J123" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K123" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -6131,31 +6131,31 @@
         <v>500</v>
       </c>
       <c r="F124" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G124" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J124" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K124" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -6177,31 +6177,31 @@
         <v>500</v>
       </c>
       <c r="F125" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G125" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H125" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J125" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K125" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -6223,31 +6223,31 @@
         <v>500</v>
       </c>
       <c r="F126" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G126" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J126" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K126" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -6269,31 +6269,31 @@
         <v>500</v>
       </c>
       <c r="F127" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G127" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H127" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J127" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K127" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -6315,31 +6315,31 @@
         <v>500</v>
       </c>
       <c r="F128" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G128" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J128" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K128" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -6361,31 +6361,31 @@
         <v>500</v>
       </c>
       <c r="F129" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G129" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J129" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K129" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -6407,31 +6407,31 @@
         <v>500</v>
       </c>
       <c r="F130" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G130" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H130" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J130" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K130" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -6453,31 +6453,31 @@
         <v>500</v>
       </c>
       <c r="F131" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G131" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J131" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K131" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -6499,31 +6499,31 @@
         <v>500</v>
       </c>
       <c r="F132" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G132" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H132" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J132" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K132" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -6545,31 +6545,31 @@
         <v>500</v>
       </c>
       <c r="F133" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G133" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J133" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K133" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -6591,31 +6591,31 @@
         <v>500</v>
       </c>
       <c r="F134" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G134" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H134" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J134" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K134" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -6637,31 +6637,31 @@
         <v>500</v>
       </c>
       <c r="F135" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G135" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H135" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J135" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K135" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -6683,31 +6683,31 @@
         <v>500</v>
       </c>
       <c r="F136" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G136" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H136" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J136" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K136" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -6729,31 +6729,31 @@
         <v>500</v>
       </c>
       <c r="F137" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G137" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H137" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J137" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K137" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -6775,31 +6775,31 @@
         <v>500</v>
       </c>
       <c r="F138" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G138" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H138" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J138" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K138" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -6821,31 +6821,31 @@
         <v>500</v>
       </c>
       <c r="F139" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G139" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H139" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J139" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K139" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -6867,31 +6867,31 @@
         <v>500</v>
       </c>
       <c r="F140" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G140" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H140" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J140" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K140" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -6913,31 +6913,31 @@
         <v>500</v>
       </c>
       <c r="F141" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G141" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H141" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J141" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K141" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -6959,31 +6959,31 @@
         <v>500</v>
       </c>
       <c r="F142" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G142" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H142" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J142" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K142" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -7005,31 +7005,31 @@
         <v>500</v>
       </c>
       <c r="F143" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G143" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H143" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J143" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K143" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -7051,31 +7051,31 @@
         <v>500</v>
       </c>
       <c r="F144" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G144" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H144" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J144" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K144" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -7097,31 +7097,31 @@
         <v>500</v>
       </c>
       <c r="F145" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G145" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H145" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J145" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K145" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -7143,31 +7143,31 @@
         <v>500</v>
       </c>
       <c r="F146" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G146" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J146" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K146" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -7189,31 +7189,31 @@
         <v>500</v>
       </c>
       <c r="F147" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G147" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H147" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J147" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K147" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -7235,31 +7235,31 @@
         <v>500</v>
       </c>
       <c r="F148" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G148" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H148" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J148" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K148" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -7281,31 +7281,31 @@
         <v>500</v>
       </c>
       <c r="F149" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G149" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H149" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J149" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K149" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -7327,31 +7327,31 @@
         <v>500</v>
       </c>
       <c r="F150" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G150" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H150" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J150" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K150" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -7373,31 +7373,31 @@
         <v>500</v>
       </c>
       <c r="F151" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G151" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H151" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J151" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K151" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -7419,31 +7419,31 @@
         <v>500</v>
       </c>
       <c r="F152" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G152" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H152" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J152" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K152" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -7465,31 +7465,31 @@
         <v>500</v>
       </c>
       <c r="F153" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G153" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H153" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J153" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K153" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -7511,31 +7511,31 @@
         <v>500</v>
       </c>
       <c r="F154" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G154" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H154" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J154" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K154" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -7557,31 +7557,31 @@
         <v>500</v>
       </c>
       <c r="F155" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G155" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H155" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J155" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K155" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -7603,31 +7603,31 @@
         <v>500</v>
       </c>
       <c r="F156" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G156" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J156" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K156" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -7649,31 +7649,31 @@
         <v>500</v>
       </c>
       <c r="F157" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G157" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J157" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K157" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -7695,31 +7695,31 @@
         <v>500</v>
       </c>
       <c r="F158" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G158" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H158" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J158" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K158" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -7741,31 +7741,31 @@
         <v>500</v>
       </c>
       <c r="F159" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G159" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J159" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K159" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -7787,31 +7787,31 @@
         <v>500</v>
       </c>
       <c r="F160" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G160" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H160" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I160" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J160" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K160" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -7833,31 +7833,31 @@
         <v>500</v>
       </c>
       <c r="F161" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G161" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H161" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J161" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K161" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -7879,31 +7879,31 @@
         <v>500</v>
       </c>
       <c r="F162" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G162" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J162" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K162" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -7925,31 +7925,31 @@
         <v>500</v>
       </c>
       <c r="F163" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G163" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H163" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J163" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K163" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -7971,31 +7971,31 @@
         <v>500</v>
       </c>
       <c r="F164" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G164" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H164" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J164" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K164" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -8017,31 +8017,31 @@
         <v>500</v>
       </c>
       <c r="F165" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G165" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H165" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J165" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K165" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -8063,31 +8063,31 @@
         <v>500</v>
       </c>
       <c r="F166" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G166" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H166" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J166" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K166" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -8109,31 +8109,31 @@
         <v>500</v>
       </c>
       <c r="F167" t="n">
-        <v>1.01</v>
+        <v>0.26</v>
       </c>
       <c r="G167" t="n">
-        <v>16.94</v>
+        <v>10.21</v>
       </c>
       <c r="H167" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I167" t="n">
-        <v>115.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J167" t="n">
-        <v>74.8</v>
+        <v>65.8</v>
       </c>
       <c r="K167" t="n">
-        <v>87.7</v>
+        <v>88.3</v>
       </c>
       <c r="L167" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
         <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168">
@@ -8155,31 +8155,31 @@
         <v>500</v>
       </c>
       <c r="F168" t="n">
-        <v>1.04</v>
+        <v>0.26</v>
       </c>
       <c r="G168" t="n">
-        <v>6.76</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H168" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>101.9</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J168" t="n">
-        <v>85.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="K168" t="n">
-        <v>90.2</v>
+        <v>87.8</v>
       </c>
       <c r="L168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -8201,31 +8201,31 @@
         <v>500</v>
       </c>
       <c r="F169" t="n">
-        <v>1.04</v>
+        <v>0.26</v>
       </c>
       <c r="G169" t="n">
-        <v>6.76</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H169" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>101.9</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J169" t="n">
-        <v>85.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="K169" t="n">
-        <v>90.2</v>
+        <v>87.8</v>
       </c>
       <c r="L169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -8247,31 +8247,31 @@
         <v>500</v>
       </c>
       <c r="F170" t="n">
-        <v>1.04</v>
+        <v>0.26</v>
       </c>
       <c r="G170" t="n">
-        <v>6.76</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H170" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>101.9</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J170" t="n">
-        <v>85.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="K170" t="n">
-        <v>90.2</v>
+        <v>87.8</v>
       </c>
       <c r="L170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -8293,31 +8293,31 @@
         <v>500</v>
       </c>
       <c r="F171" t="n">
-        <v>1.04</v>
+        <v>0.26</v>
       </c>
       <c r="G171" t="n">
-        <v>6.76</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H171" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>101.9</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J171" t="n">
-        <v>85.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="K171" t="n">
-        <v>90.2</v>
+        <v>87.8</v>
       </c>
       <c r="L171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -8339,31 +8339,31 @@
         <v>500</v>
       </c>
       <c r="F172" t="n">
-        <v>1.01</v>
+        <v>0.26</v>
       </c>
       <c r="G172" t="n">
-        <v>0.34</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="H172" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I172" t="n">
-        <v>92.3</v>
+        <v>67.8</v>
       </c>
       <c r="J172" t="n">
-        <v>92.5</v>
+        <v>66</v>
       </c>
       <c r="K172" t="n">
-        <v>93.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="L172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173">
@@ -8385,31 +8385,31 @@
         <v>500</v>
       </c>
       <c r="F173" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G173" t="n">
-        <v>0.43</v>
+        <v>9.59</v>
       </c>
       <c r="H173" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I173" t="n">
-        <v>92.2</v>
+        <v>68.3</v>
       </c>
       <c r="J173" t="n">
-        <v>92.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="K173" t="n">
-        <v>93.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -8431,31 +8431,31 @@
         <v>500</v>
       </c>
       <c r="F174" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G174" t="n">
-        <v>0.43</v>
+        <v>9.59</v>
       </c>
       <c r="H174" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>92.2</v>
+        <v>68.3</v>
       </c>
       <c r="J174" t="n">
-        <v>92.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="K174" t="n">
-        <v>93.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -8477,31 +8477,31 @@
         <v>500</v>
       </c>
       <c r="F175" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G175" t="n">
-        <v>0.43</v>
+        <v>9.59</v>
       </c>
       <c r="H175" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I175" t="n">
-        <v>92.2</v>
+        <v>68.3</v>
       </c>
       <c r="J175" t="n">
-        <v>92.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="K175" t="n">
-        <v>93.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -8523,31 +8523,31 @@
         <v>500</v>
       </c>
       <c r="F176" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G176" t="n">
-        <v>0.43</v>
+        <v>9.59</v>
       </c>
       <c r="H176" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I176" t="n">
-        <v>92.2</v>
+        <v>68.3</v>
       </c>
       <c r="J176" t="n">
-        <v>92.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="K176" t="n">
-        <v>93.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -8569,31 +8569,31 @@
         <v>500</v>
       </c>
       <c r="F177" t="n">
-        <v>1.01</v>
+        <v>0.26</v>
       </c>
       <c r="G177" t="n">
-        <v>0.4</v>
+        <v>9.23</v>
       </c>
       <c r="H177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I177" t="n">
-        <v>92.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J177" t="n">
-        <v>92.40000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K177" t="n">
-        <v>93.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="L177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -8615,31 +8615,31 @@
         <v>500</v>
       </c>
       <c r="F178" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G178" t="n">
-        <v>0.43</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H178" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I178" t="n">
-        <v>92.2</v>
+        <v>68.7</v>
       </c>
       <c r="J178" t="n">
-        <v>92.40000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K178" t="n">
-        <v>93.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="L178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -8661,31 +8661,31 @@
         <v>500</v>
       </c>
       <c r="F179" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G179" t="n">
-        <v>0.43</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H179" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I179" t="n">
-        <v>92.2</v>
+        <v>68.7</v>
       </c>
       <c r="J179" t="n">
-        <v>92.40000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K179" t="n">
-        <v>93.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="L179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -8707,31 +8707,31 @@
         <v>500</v>
       </c>
       <c r="F180" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G180" t="n">
-        <v>0.43</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H180" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I180" t="n">
-        <v>92.2</v>
+        <v>68.7</v>
       </c>
       <c r="J180" t="n">
-        <v>92.40000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K180" t="n">
-        <v>93.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="L180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -8753,31 +8753,31 @@
         <v>500</v>
       </c>
       <c r="F181" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G181" t="n">
-        <v>0.43</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>92.2</v>
+        <v>68.7</v>
       </c>
       <c r="J181" t="n">
-        <v>92.40000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K181" t="n">
-        <v>93.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="L181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -8799,31 +8799,31 @@
         <v>500</v>
       </c>
       <c r="F182" t="n">
-        <v>1.01</v>
+        <v>0.26</v>
       </c>
       <c r="G182" t="n">
-        <v>0.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H182" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I182" t="n">
-        <v>92.3</v>
+        <v>69.2</v>
       </c>
       <c r="J182" t="n">
-        <v>92.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K182" t="n">
-        <v>93.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -8845,31 +8845,31 @@
         <v>500</v>
       </c>
       <c r="F183" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G183" t="n">
-        <v>0.43</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H183" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I183" t="n">
-        <v>92.2</v>
+        <v>69.2</v>
       </c>
       <c r="J183" t="n">
-        <v>92.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K183" t="n">
-        <v>93.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -8891,31 +8891,31 @@
         <v>500</v>
       </c>
       <c r="F184" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G184" t="n">
-        <v>0.43</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>92.2</v>
+        <v>69.2</v>
       </c>
       <c r="J184" t="n">
-        <v>92.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K184" t="n">
-        <v>93.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -8937,31 +8937,31 @@
         <v>500</v>
       </c>
       <c r="F185" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G185" t="n">
-        <v>0.43</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H185" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I185" t="n">
-        <v>92.2</v>
+        <v>69.2</v>
       </c>
       <c r="J185" t="n">
-        <v>92.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K185" t="n">
-        <v>93.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -8983,31 +8983,31 @@
         <v>500</v>
       </c>
       <c r="F186" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G186" t="n">
-        <v>0.43</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H186" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>92.2</v>
+        <v>69.2</v>
       </c>
       <c r="J186" t="n">
-        <v>92.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K186" t="n">
-        <v>93.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -9029,31 +9029,31 @@
         <v>500</v>
       </c>
       <c r="F187" t="n">
-        <v>1.01</v>
+        <v>0.26</v>
       </c>
       <c r="G187" t="n">
-        <v>0.33</v>
+        <v>7.66</v>
       </c>
       <c r="H187" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I187" t="n">
-        <v>92.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="J187" t="n">
-        <v>92.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K187" t="n">
-        <v>93.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -9075,31 +9075,31 @@
         <v>500</v>
       </c>
       <c r="F188" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G188" t="n">
-        <v>0.34</v>
+        <v>7.66</v>
       </c>
       <c r="H188" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>92.3</v>
+        <v>70</v>
       </c>
       <c r="J188" t="n">
-        <v>92.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K188" t="n">
-        <v>93.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -9121,31 +9121,31 @@
         <v>500</v>
       </c>
       <c r="F189" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G189" t="n">
-        <v>0.34</v>
+        <v>7.66</v>
       </c>
       <c r="H189" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>92.3</v>
+        <v>70</v>
       </c>
       <c r="J189" t="n">
-        <v>92.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K189" t="n">
-        <v>93.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -9167,31 +9167,31 @@
         <v>500</v>
       </c>
       <c r="F190" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G190" t="n">
-        <v>0.34</v>
+        <v>7.66</v>
       </c>
       <c r="H190" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>92.3</v>
+        <v>70</v>
       </c>
       <c r="J190" t="n">
-        <v>92.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K190" t="n">
-        <v>93.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -9213,31 +9213,31 @@
         <v>500</v>
       </c>
       <c r="F191" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G191" t="n">
-        <v>0.34</v>
+        <v>7.66</v>
       </c>
       <c r="H191" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>92.3</v>
+        <v>70</v>
       </c>
       <c r="J191" t="n">
-        <v>92.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K191" t="n">
-        <v>93.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -9259,31 +9259,31 @@
         <v>500</v>
       </c>
       <c r="F192" t="n">
-        <v>1.02</v>
+        <v>0.27</v>
       </c>
       <c r="G192" t="n">
-        <v>0.31</v>
+        <v>7.11</v>
       </c>
       <c r="H192" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>92.2</v>
+        <v>70.5</v>
       </c>
       <c r="J192" t="n">
-        <v>92.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K192" t="n">
-        <v>92.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="L192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -9305,31 +9305,31 @@
         <v>500</v>
       </c>
       <c r="F193" t="n">
-        <v>1.03</v>
+        <v>0.27</v>
       </c>
       <c r="G193" t="n">
-        <v>0.37</v>
+        <v>7.11</v>
       </c>
       <c r="H193" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>92.2</v>
+        <v>70.5</v>
       </c>
       <c r="J193" t="n">
-        <v>92.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K193" t="n">
-        <v>93.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="L193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -9351,31 +9351,31 @@
         <v>500</v>
       </c>
       <c r="F194" t="n">
-        <v>1.03</v>
+        <v>0.27</v>
       </c>
       <c r="G194" t="n">
-        <v>0.37</v>
+        <v>7.11</v>
       </c>
       <c r="H194" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>92.2</v>
+        <v>70.5</v>
       </c>
       <c r="J194" t="n">
-        <v>92.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K194" t="n">
-        <v>93.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="L194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -9397,31 +9397,31 @@
         <v>500</v>
       </c>
       <c r="F195" t="n">
-        <v>1.03</v>
+        <v>0.27</v>
       </c>
       <c r="G195" t="n">
-        <v>0.37</v>
+        <v>7.11</v>
       </c>
       <c r="H195" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I195" t="n">
-        <v>92.2</v>
+        <v>70.5</v>
       </c>
       <c r="J195" t="n">
-        <v>92.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K195" t="n">
-        <v>93.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="L195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -9443,31 +9443,31 @@
         <v>500</v>
       </c>
       <c r="F196" t="n">
-        <v>1.03</v>
+        <v>0.27</v>
       </c>
       <c r="G196" t="n">
-        <v>0.37</v>
+        <v>7.11</v>
       </c>
       <c r="H196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>92.2</v>
+        <v>70.5</v>
       </c>
       <c r="J196" t="n">
-        <v>92.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K196" t="n">
-        <v>93.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="L196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -9489,31 +9489,31 @@
         <v>500</v>
       </c>
       <c r="F197" t="n">
-        <v>1.02</v>
+        <v>0.27</v>
       </c>
       <c r="G197" t="n">
-        <v>0.24</v>
+        <v>6.02</v>
       </c>
       <c r="H197" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>92.3</v>
+        <v>71.2</v>
       </c>
       <c r="J197" t="n">
-        <v>92.8</v>
+        <v>68.2</v>
       </c>
       <c r="K197" t="n">
-        <v>92.8</v>
+        <v>82.2</v>
       </c>
       <c r="L197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -9535,31 +9535,31 @@
         <v>500</v>
       </c>
       <c r="F198" t="n">
-        <v>1.04</v>
+        <v>0.27</v>
       </c>
       <c r="G198" t="n">
-        <v>0.31</v>
+        <v>6.02</v>
       </c>
       <c r="H198" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>92.2</v>
+        <v>71.2</v>
       </c>
       <c r="J198" t="n">
-        <v>92.8</v>
+        <v>68.2</v>
       </c>
       <c r="K198" t="n">
-        <v>92.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="L198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -9581,31 +9581,31 @@
         <v>500</v>
       </c>
       <c r="F199" t="n">
-        <v>1.04</v>
+        <v>0.27</v>
       </c>
       <c r="G199" t="n">
-        <v>0.31</v>
+        <v>6.02</v>
       </c>
       <c r="H199" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>92.2</v>
+        <v>71.2</v>
       </c>
       <c r="J199" t="n">
-        <v>92.8</v>
+        <v>68.2</v>
       </c>
       <c r="K199" t="n">
-        <v>92.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="L199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -9627,31 +9627,31 @@
         <v>500</v>
       </c>
       <c r="F200" t="n">
-        <v>1.04</v>
+        <v>0.27</v>
       </c>
       <c r="G200" t="n">
-        <v>0.31</v>
+        <v>6.02</v>
       </c>
       <c r="H200" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I200" t="n">
-        <v>92.2</v>
+        <v>71.2</v>
       </c>
       <c r="J200" t="n">
-        <v>92.8</v>
+        <v>68.2</v>
       </c>
       <c r="K200" t="n">
-        <v>92.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="L200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -9673,31 +9673,31 @@
         <v>500</v>
       </c>
       <c r="F201" t="n">
-        <v>1.04</v>
+        <v>0.27</v>
       </c>
       <c r="G201" t="n">
-        <v>0.31</v>
+        <v>6.02</v>
       </c>
       <c r="H201" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>92.2</v>
+        <v>71.2</v>
       </c>
       <c r="J201" t="n">
-        <v>92.8</v>
+        <v>68.2</v>
       </c>
       <c r="K201" t="n">
-        <v>92.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="L201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -9719,31 +9719,31 @@
         <v>500</v>
       </c>
       <c r="F202" t="n">
-        <v>1.02</v>
+        <v>0.29</v>
       </c>
       <c r="G202" t="n">
-        <v>0.17</v>
+        <v>4.76</v>
       </c>
       <c r="H202" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I202" t="n">
-        <v>92.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="J202" t="n">
-        <v>92.7</v>
+        <v>69.2</v>
       </c>
       <c r="K202" t="n">
-        <v>92.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="L202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -9765,31 +9765,31 @@
         <v>500</v>
       </c>
       <c r="F203" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="G203" t="n">
-        <v>0.25</v>
+        <v>4.76</v>
       </c>
       <c r="H203" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>92.3</v>
+        <v>72</v>
       </c>
       <c r="J203" t="n">
-        <v>92.7</v>
+        <v>69.2</v>
       </c>
       <c r="K203" t="n">
-        <v>92.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="L203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -9811,31 +9811,31 @@
         <v>500</v>
       </c>
       <c r="F204" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="G204" t="n">
-        <v>0.25</v>
+        <v>4.76</v>
       </c>
       <c r="H204" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>92.3</v>
+        <v>72</v>
       </c>
       <c r="J204" t="n">
-        <v>92.7</v>
+        <v>69.2</v>
       </c>
       <c r="K204" t="n">
-        <v>92.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="L204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -9857,31 +9857,31 @@
         <v>500</v>
       </c>
       <c r="F205" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="G205" t="n">
-        <v>0.25</v>
+        <v>4.76</v>
       </c>
       <c r="H205" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>92.3</v>
+        <v>72</v>
       </c>
       <c r="J205" t="n">
-        <v>92.7</v>
+        <v>69.2</v>
       </c>
       <c r="K205" t="n">
-        <v>92.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="L205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -9903,31 +9903,31 @@
         <v>500</v>
       </c>
       <c r="F206" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="G206" t="n">
-        <v>0.25</v>
+        <v>4.76</v>
       </c>
       <c r="H206" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>92.3</v>
+        <v>72</v>
       </c>
       <c r="J206" t="n">
-        <v>92.7</v>
+        <v>69.2</v>
       </c>
       <c r="K206" t="n">
-        <v>92.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="L206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -9949,31 +9949,31 @@
         <v>500</v>
       </c>
       <c r="F207" t="n">
-        <v>1.03</v>
+        <v>0.3</v>
       </c>
       <c r="G207" t="n">
-        <v>0.17</v>
+        <v>3.05</v>
       </c>
       <c r="H207" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I207" t="n">
-        <v>92.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="J207" t="n">
-        <v>92.7</v>
+        <v>70.7</v>
       </c>
       <c r="K207" t="n">
-        <v>92.8</v>
+        <v>78</v>
       </c>
       <c r="L207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -9995,31 +9995,31 @@
         <v>500</v>
       </c>
       <c r="F208" t="n">
-        <v>1.04</v>
+        <v>0.3</v>
       </c>
       <c r="G208" t="n">
-        <v>0.25</v>
+        <v>3.05</v>
       </c>
       <c r="H208" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>92.3</v>
+        <v>73</v>
       </c>
       <c r="J208" t="n">
-        <v>92.7</v>
+        <v>70.7</v>
       </c>
       <c r="K208" t="n">
-        <v>92.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="L208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -10041,31 +10041,31 @@
         <v>500</v>
       </c>
       <c r="F209" t="n">
-        <v>1.04</v>
+        <v>0.3</v>
       </c>
       <c r="G209" t="n">
-        <v>0.25</v>
+        <v>3.05</v>
       </c>
       <c r="H209" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I209" t="n">
-        <v>92.3</v>
+        <v>73</v>
       </c>
       <c r="J209" t="n">
-        <v>92.7</v>
+        <v>70.7</v>
       </c>
       <c r="K209" t="n">
-        <v>92.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="L209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -10087,31 +10087,31 @@
         <v>500</v>
       </c>
       <c r="F210" t="n">
-        <v>1.04</v>
+        <v>0.3</v>
       </c>
       <c r="G210" t="n">
-        <v>0.25</v>
+        <v>3.05</v>
       </c>
       <c r="H210" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I210" t="n">
-        <v>92.3</v>
+        <v>73</v>
       </c>
       <c r="J210" t="n">
-        <v>92.7</v>
+        <v>70.7</v>
       </c>
       <c r="K210" t="n">
-        <v>92.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="L210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -10133,31 +10133,31 @@
         <v>500</v>
       </c>
       <c r="F211" t="n">
-        <v>1.04</v>
+        <v>0.3</v>
       </c>
       <c r="G211" t="n">
-        <v>0.25</v>
+        <v>3.05</v>
       </c>
       <c r="H211" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I211" t="n">
-        <v>92.3</v>
+        <v>73</v>
       </c>
       <c r="J211" t="n">
-        <v>92.7</v>
+        <v>70.7</v>
       </c>
       <c r="K211" t="n">
-        <v>92.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="L211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -10179,31 +10179,31 @@
         <v>500</v>
       </c>
       <c r="F212" t="n">
-        <v>1.02</v>
+        <v>0.33</v>
       </c>
       <c r="G212" t="n">
-        <v>0.25</v>
+        <v>1.52</v>
       </c>
       <c r="H212" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I212" t="n">
-        <v>92.3</v>
+        <v>73.7</v>
       </c>
       <c r="J212" t="n">
-        <v>92.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="K212" t="n">
-        <v>92.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="L212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -10225,31 +10225,31 @@
         <v>500</v>
       </c>
       <c r="F213" t="n">
-        <v>1.04</v>
+        <v>0.33</v>
       </c>
       <c r="G213" t="n">
-        <v>0.24</v>
+        <v>1.52</v>
       </c>
       <c r="H213" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I213" t="n">
-        <v>92.3</v>
+        <v>73.7</v>
       </c>
       <c r="J213" t="n">
-        <v>92.8</v>
+        <v>72.2</v>
       </c>
       <c r="K213" t="n">
-        <v>92.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="L213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -10271,31 +10271,31 @@
         <v>500</v>
       </c>
       <c r="F214" t="n">
-        <v>1.04</v>
+        <v>0.33</v>
       </c>
       <c r="G214" t="n">
-        <v>0.24</v>
+        <v>1.52</v>
       </c>
       <c r="H214" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>92.3</v>
+        <v>73.7</v>
       </c>
       <c r="J214" t="n">
-        <v>92.8</v>
+        <v>72.2</v>
       </c>
       <c r="K214" t="n">
-        <v>92.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="L214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -10317,31 +10317,31 @@
         <v>500</v>
       </c>
       <c r="F215" t="n">
-        <v>1.04</v>
+        <v>0.33</v>
       </c>
       <c r="G215" t="n">
-        <v>0.24</v>
+        <v>1.52</v>
       </c>
       <c r="H215" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I215" t="n">
-        <v>92.3</v>
+        <v>73.7</v>
       </c>
       <c r="J215" t="n">
-        <v>92.8</v>
+        <v>72.2</v>
       </c>
       <c r="K215" t="n">
-        <v>92.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="L215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -10363,31 +10363,31 @@
         <v>500</v>
       </c>
       <c r="F216" t="n">
-        <v>1.04</v>
+        <v>0.33</v>
       </c>
       <c r="G216" t="n">
-        <v>0.24</v>
+        <v>1.52</v>
       </c>
       <c r="H216" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I216" t="n">
-        <v>92.3</v>
+        <v>73.7</v>
       </c>
       <c r="J216" t="n">
-        <v>92.8</v>
+        <v>72.2</v>
       </c>
       <c r="K216" t="n">
-        <v>92.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="L216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -10409,31 +10409,31 @@
         <v>500</v>
       </c>
       <c r="F217" t="n">
-        <v>1.17</v>
+        <v>0.53</v>
       </c>
       <c r="G217" t="n">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="H217" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I217" t="n">
-        <v>92.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J217" t="n">
-        <v>92.3</v>
+        <v>73.8</v>
       </c>
       <c r="K217" t="n">
-        <v>92.8</v>
+        <v>74</v>
       </c>
       <c r="L217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -10455,31 +10455,31 @@
         <v>500</v>
       </c>
       <c r="F218" t="n">
-        <v>1.17</v>
+        <v>0.53</v>
       </c>
       <c r="G218" t="n">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="H218" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>92.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J218" t="n">
-        <v>92.3</v>
+        <v>73.8</v>
       </c>
       <c r="K218" t="n">
-        <v>92.8</v>
+        <v>74</v>
       </c>
       <c r="L218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -10501,31 +10501,31 @@
         <v>500</v>
       </c>
       <c r="F219" t="n">
-        <v>1.17</v>
+        <v>0.53</v>
       </c>
       <c r="G219" t="n">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="H219" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>92.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J219" t="n">
-        <v>92.3</v>
+        <v>73.8</v>
       </c>
       <c r="K219" t="n">
-        <v>92.8</v>
+        <v>74</v>
       </c>
       <c r="L219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -10547,31 +10547,31 @@
         <v>500</v>
       </c>
       <c r="F220" t="n">
-        <v>1.17</v>
+        <v>0.53</v>
       </c>
       <c r="G220" t="n">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="H220" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I220" t="n">
-        <v>92.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J220" t="n">
-        <v>92.3</v>
+        <v>73.8</v>
       </c>
       <c r="K220" t="n">
-        <v>92.8</v>
+        <v>74</v>
       </c>
       <c r="L220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -10593,31 +10593,31 @@
         <v>500</v>
       </c>
       <c r="F221" t="n">
-        <v>1.17</v>
+        <v>0.53</v>
       </c>
       <c r="G221" t="n">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="H221" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I221" t="n">
-        <v>92.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J221" t="n">
-        <v>92.3</v>
+        <v>73.8</v>
       </c>
       <c r="K221" t="n">
-        <v>92.8</v>
+        <v>74</v>
       </c>
       <c r="L221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Sensitivity_Output/Sensitivity_Analysis_Full.xlsx
+++ b/Sensitivity_Output/Sensitivity_Analysis_Full.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,72 +417,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>alpha</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>lookahead_days</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>total_assigned</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>avg_travel_hours</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>HomecareA_avg_utilization</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>HomecareB_avg_utilization</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>HomecareC_avg_utilization</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>HomecareA_overcap_weeks</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>HomecareB_overcap_weeks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>HomecareC_overcap_weeks</t>
         </is>
@@ -522,19 +510,19 @@
         <v>0.26</v>
       </c>
       <c r="G2" t="n">
-        <v>10.21</v>
+        <v>10.77</v>
       </c>
       <c r="H2" t="n">
         <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>67.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="J2" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="K2" t="n">
-        <v>88.3</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -568,19 +556,19 @@
         <v>0.26</v>
       </c>
       <c r="G3" t="n">
-        <v>9.869999999999999</v>
+        <v>10.42</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>68.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="K3" t="n">
-        <v>87.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -614,19 +602,19 @@
         <v>0.26</v>
       </c>
       <c r="G4" t="n">
-        <v>9.869999999999999</v>
+        <v>10.42</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>68.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="K4" t="n">
-        <v>87.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -660,19 +648,19 @@
         <v>0.26</v>
       </c>
       <c r="G5" t="n">
-        <v>9.869999999999999</v>
+        <v>10.42</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>68.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="K5" t="n">
-        <v>87.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -706,19 +694,19 @@
         <v>0.26</v>
       </c>
       <c r="G6" t="n">
-        <v>9.869999999999999</v>
+        <v>10.42</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>68.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="K6" t="n">
-        <v>87.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -752,19 +740,19 @@
         <v>0.26</v>
       </c>
       <c r="G7" t="n">
-        <v>9.970000000000001</v>
+        <v>10.49</v>
       </c>
       <c r="H7" t="n">
         <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>67.8</v>
+        <v>68.2</v>
       </c>
       <c r="J7" t="n">
-        <v>66</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>88</v>
+        <v>89.5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -798,19 +786,19 @@
         <v>0.26</v>
       </c>
       <c r="G8" t="n">
-        <v>9.640000000000001</v>
+        <v>10.16</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>68.3</v>
+        <v>68.7</v>
       </c>
       <c r="J8" t="n">
-        <v>66</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>87.5</v>
+        <v>89</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -844,19 +832,19 @@
         <v>0.26</v>
       </c>
       <c r="G9" t="n">
-        <v>9.640000000000001</v>
+        <v>10.16</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>68.3</v>
+        <v>68.7</v>
       </c>
       <c r="J9" t="n">
-        <v>66</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>87.5</v>
+        <v>89</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -890,19 +878,19 @@
         <v>0.26</v>
       </c>
       <c r="G10" t="n">
-        <v>9.640000000000001</v>
+        <v>10.16</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>68.3</v>
+        <v>68.7</v>
       </c>
       <c r="J10" t="n">
-        <v>66</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>87.5</v>
+        <v>89</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -936,19 +924,19 @@
         <v>0.26</v>
       </c>
       <c r="G11" t="n">
-        <v>9.640000000000001</v>
+        <v>10.16</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>68.3</v>
+        <v>68.7</v>
       </c>
       <c r="J11" t="n">
-        <v>66</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>87.5</v>
+        <v>89</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -982,19 +970,19 @@
         <v>0.26</v>
       </c>
       <c r="G12" t="n">
-        <v>9.16</v>
+        <v>9.73</v>
       </c>
       <c r="H12" t="n">
         <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>68.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="K12" t="n">
-        <v>86.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1028,19 +1016,19 @@
         <v>0.26</v>
       </c>
       <c r="G13" t="n">
-        <v>9.01</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="J13" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="K13" t="n">
-        <v>86.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1074,19 +1062,19 @@
         <v>0.26</v>
       </c>
       <c r="G14" t="n">
-        <v>9.01</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="J14" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="K14" t="n">
-        <v>86.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1120,19 +1108,19 @@
         <v>0.26</v>
       </c>
       <c r="G15" t="n">
-        <v>9.01</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="J15" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="K15" t="n">
-        <v>86.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1166,19 +1154,19 @@
         <v>0.26</v>
       </c>
       <c r="G16" t="n">
-        <v>9.01</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="J16" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="K16" t="n">
-        <v>86.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1212,19 +1200,19 @@
         <v>0.26</v>
       </c>
       <c r="G17" t="n">
-        <v>8.619999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>69.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="K17" t="n">
-        <v>86</v>
+        <v>87.5</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1258,19 +1246,19 @@
         <v>0.26</v>
       </c>
       <c r="G18" t="n">
-        <v>8.550000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>69.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="K18" t="n">
-        <v>85.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1304,19 +1292,19 @@
         <v>0.26</v>
       </c>
       <c r="G19" t="n">
-        <v>8.550000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>69.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="K19" t="n">
-        <v>85.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1350,19 +1338,19 @@
         <v>0.26</v>
       </c>
       <c r="G20" t="n">
-        <v>8.550000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>69.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="K20" t="n">
-        <v>85.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1396,19 +1384,19 @@
         <v>0.26</v>
       </c>
       <c r="G21" t="n">
-        <v>8.550000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>69.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="K21" t="n">
-        <v>85.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1442,19 +1430,19 @@
         <v>0.26</v>
       </c>
       <c r="G22" t="n">
-        <v>7.71</v>
+        <v>8.19</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>69.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>67.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>84.7</v>
+        <v>86.2</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1488,19 +1476,19 @@
         <v>0.26</v>
       </c>
       <c r="G23" t="n">
-        <v>7.71</v>
+        <v>8.19</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>69.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>67.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>84.7</v>
+        <v>86.2</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1534,19 +1522,19 @@
         <v>0.26</v>
       </c>
       <c r="G24" t="n">
-        <v>7.71</v>
+        <v>8.19</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>69.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>67.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>84.7</v>
+        <v>86.2</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1580,19 +1568,19 @@
         <v>0.26</v>
       </c>
       <c r="G25" t="n">
-        <v>7.71</v>
+        <v>8.19</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>69.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>67.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>84.7</v>
+        <v>86.2</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1626,19 +1614,19 @@
         <v>0.26</v>
       </c>
       <c r="G26" t="n">
-        <v>7.71</v>
+        <v>8.19</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>69.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>67.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>84.7</v>
+        <v>86.2</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1672,19 +1660,19 @@
         <v>0.27</v>
       </c>
       <c r="G27" t="n">
-        <v>7.02</v>
+        <v>7.58</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>70.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="J27" t="n">
-        <v>67.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="K27" t="n">
-        <v>83.7</v>
+        <v>85.3</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1718,19 +1706,19 @@
         <v>0.27</v>
       </c>
       <c r="G28" t="n">
-        <v>7.02</v>
+        <v>7.58</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>70.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="J28" t="n">
-        <v>67.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="K28" t="n">
-        <v>83.7</v>
+        <v>85.3</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1764,19 +1752,19 @@
         <v>0.27</v>
       </c>
       <c r="G29" t="n">
-        <v>7.02</v>
+        <v>7.58</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>70.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="J29" t="n">
-        <v>67.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="K29" t="n">
-        <v>83.7</v>
+        <v>85.3</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1810,19 +1798,19 @@
         <v>0.27</v>
       </c>
       <c r="G30" t="n">
-        <v>7.02</v>
+        <v>7.58</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>70.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="J30" t="n">
-        <v>67.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="K30" t="n">
-        <v>83.7</v>
+        <v>85.3</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1856,19 +1844,19 @@
         <v>0.27</v>
       </c>
       <c r="G31" t="n">
-        <v>7.02</v>
+        <v>7.58</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>70.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="J31" t="n">
-        <v>67.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="K31" t="n">
-        <v>83.7</v>
+        <v>85.3</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1902,19 +1890,19 @@
         <v>0.28</v>
       </c>
       <c r="G32" t="n">
-        <v>5.99</v>
+        <v>6.4</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>71.2</v>
+        <v>71.7</v>
       </c>
       <c r="J32" t="n">
-        <v>68.3</v>
+        <v>68.8</v>
       </c>
       <c r="K32" t="n">
-        <v>82.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1948,19 +1936,19 @@
         <v>0.28</v>
       </c>
       <c r="G33" t="n">
-        <v>5.99</v>
+        <v>6.4</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>71.2</v>
+        <v>71.7</v>
       </c>
       <c r="J33" t="n">
-        <v>68.3</v>
+        <v>68.8</v>
       </c>
       <c r="K33" t="n">
-        <v>82.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -1994,19 +1982,19 @@
         <v>0.28</v>
       </c>
       <c r="G34" t="n">
-        <v>5.99</v>
+        <v>6.4</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>71.2</v>
+        <v>71.7</v>
       </c>
       <c r="J34" t="n">
-        <v>68.3</v>
+        <v>68.8</v>
       </c>
       <c r="K34" t="n">
-        <v>82.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2040,19 +2028,19 @@
         <v>0.28</v>
       </c>
       <c r="G35" t="n">
-        <v>5.99</v>
+        <v>6.4</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>71.2</v>
+        <v>71.7</v>
       </c>
       <c r="J35" t="n">
-        <v>68.3</v>
+        <v>68.8</v>
       </c>
       <c r="K35" t="n">
-        <v>82.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2086,19 +2074,19 @@
         <v>0.28</v>
       </c>
       <c r="G36" t="n">
-        <v>5.99</v>
+        <v>6.4</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>71.2</v>
+        <v>71.7</v>
       </c>
       <c r="J36" t="n">
-        <v>68.3</v>
+        <v>68.8</v>
       </c>
       <c r="K36" t="n">
-        <v>82.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2132,19 +2120,19 @@
         <v>0.29</v>
       </c>
       <c r="G37" t="n">
-        <v>4.67</v>
+        <v>4.92</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>69.3</v>
+        <v>70</v>
       </c>
       <c r="K37" t="n">
-        <v>80.3</v>
+        <v>81.5</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2178,19 +2166,19 @@
         <v>0.29</v>
       </c>
       <c r="G38" t="n">
-        <v>4.67</v>
+        <v>4.92</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>69.3</v>
+        <v>70</v>
       </c>
       <c r="K38" t="n">
-        <v>80.3</v>
+        <v>81.5</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2224,19 +2212,19 @@
         <v>0.29</v>
       </c>
       <c r="G39" t="n">
-        <v>4.67</v>
+        <v>4.92</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>69.3</v>
+        <v>70</v>
       </c>
       <c r="K39" t="n">
-        <v>80.3</v>
+        <v>81.5</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2270,19 +2258,19 @@
         <v>0.29</v>
       </c>
       <c r="G40" t="n">
-        <v>4.67</v>
+        <v>4.92</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>69.3</v>
+        <v>70</v>
       </c>
       <c r="K40" t="n">
-        <v>80.3</v>
+        <v>81.5</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2316,19 +2304,19 @@
         <v>0.29</v>
       </c>
       <c r="G41" t="n">
-        <v>4.67</v>
+        <v>4.92</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>69.3</v>
+        <v>70</v>
       </c>
       <c r="K41" t="n">
-        <v>80.3</v>
+        <v>81.5</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2362,19 +2350,19 @@
         <v>0.3</v>
       </c>
       <c r="G42" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>72.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="J42" t="n">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>78.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2408,19 +2396,19 @@
         <v>0.3</v>
       </c>
       <c r="G43" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>72.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="J43" t="n">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>78.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2454,19 +2442,19 @@
         <v>0.3</v>
       </c>
       <c r="G44" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>72.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="J44" t="n">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>78.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -2500,19 +2488,19 @@
         <v>0.3</v>
       </c>
       <c r="G45" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>72.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="J45" t="n">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>78.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2546,19 +2534,19 @@
         <v>0.3</v>
       </c>
       <c r="G46" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>72.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="J46" t="n">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>78.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2592,19 +2580,19 @@
         <v>0.34</v>
       </c>
       <c r="G47" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>73.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>72.3</v>
+        <v>73</v>
       </c>
       <c r="K47" t="n">
-        <v>76.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2638,19 +2626,19 @@
         <v>0.34</v>
       </c>
       <c r="G48" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>73.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>72.3</v>
+        <v>73</v>
       </c>
       <c r="K48" t="n">
-        <v>76.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2684,19 +2672,19 @@
         <v>0.34</v>
       </c>
       <c r="G49" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>73.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>72.3</v>
+        <v>73</v>
       </c>
       <c r="K49" t="n">
-        <v>76.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2730,19 +2718,19 @@
         <v>0.34</v>
       </c>
       <c r="G50" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>73.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>72.3</v>
+        <v>73</v>
       </c>
       <c r="K50" t="n">
-        <v>76.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2776,19 +2764,19 @@
         <v>0.34</v>
       </c>
       <c r="G51" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>73.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>72.3</v>
+        <v>73</v>
       </c>
       <c r="K51" t="n">
-        <v>76.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2828,13 +2816,13 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>73.8</v>
+        <v>74.8</v>
       </c>
       <c r="J52" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="K52" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2874,13 +2862,13 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>73.8</v>
+        <v>74.8</v>
       </c>
       <c r="J53" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="K53" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -2920,13 +2908,13 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>73.8</v>
+        <v>74.8</v>
       </c>
       <c r="J54" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="K54" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -2966,13 +2954,13 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>73.8</v>
+        <v>74.8</v>
       </c>
       <c r="J55" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="K55" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -3012,13 +3000,13 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>73.8</v>
+        <v>74.8</v>
       </c>
       <c r="J56" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="K56" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -3052,19 +3040,19 @@
         <v>0.26</v>
       </c>
       <c r="G57" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H57" t="n">
         <v>2</v>
       </c>
       <c r="I57" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K57" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3098,19 +3086,19 @@
         <v>0.26</v>
       </c>
       <c r="G58" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H58" t="n">
         <v>2</v>
       </c>
       <c r="I58" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K58" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -3144,19 +3132,19 @@
         <v>0.26</v>
       </c>
       <c r="G59" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H59" t="n">
         <v>2</v>
       </c>
       <c r="I59" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K59" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -3190,19 +3178,19 @@
         <v>0.26</v>
       </c>
       <c r="G60" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K60" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -3236,19 +3224,19 @@
         <v>0.26</v>
       </c>
       <c r="G61" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H61" t="n">
         <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K61" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -3282,19 +3270,19 @@
         <v>0.26</v>
       </c>
       <c r="G62" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H62" t="n">
         <v>2</v>
       </c>
       <c r="I62" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J62" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K62" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3328,19 +3316,19 @@
         <v>0.26</v>
       </c>
       <c r="G63" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H63" t="n">
         <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J63" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K63" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3374,19 +3362,19 @@
         <v>0.26</v>
       </c>
       <c r="G64" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H64" t="n">
         <v>2</v>
       </c>
       <c r="I64" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K64" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3420,19 +3408,19 @@
         <v>0.26</v>
       </c>
       <c r="G65" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H65" t="n">
         <v>2</v>
       </c>
       <c r="I65" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K65" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3466,19 +3454,19 @@
         <v>0.26</v>
       </c>
       <c r="G66" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H66" t="n">
         <v>2</v>
       </c>
       <c r="I66" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K66" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3512,19 +3500,19 @@
         <v>0.26</v>
       </c>
       <c r="G67" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
       </c>
       <c r="I67" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J67" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K67" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -3558,19 +3546,19 @@
         <v>0.26</v>
       </c>
       <c r="G68" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H68" t="n">
         <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J68" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K68" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3604,19 +3592,19 @@
         <v>0.26</v>
       </c>
       <c r="G69" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H69" t="n">
         <v>2</v>
       </c>
       <c r="I69" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K69" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3650,19 +3638,19 @@
         <v>0.26</v>
       </c>
       <c r="G70" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H70" t="n">
         <v>2</v>
       </c>
       <c r="I70" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J70" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K70" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -3696,19 +3684,19 @@
         <v>0.26</v>
       </c>
       <c r="G71" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H71" t="n">
         <v>2</v>
       </c>
       <c r="I71" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K71" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -3742,19 +3730,19 @@
         <v>0.26</v>
       </c>
       <c r="G72" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H72" t="n">
         <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J72" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K72" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -3788,19 +3776,19 @@
         <v>0.26</v>
       </c>
       <c r="G73" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H73" t="n">
         <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K73" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -3834,19 +3822,19 @@
         <v>0.26</v>
       </c>
       <c r="G74" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H74" t="n">
         <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K74" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -3880,19 +3868,19 @@
         <v>0.26</v>
       </c>
       <c r="G75" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H75" t="n">
         <v>2</v>
       </c>
       <c r="I75" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K75" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -3926,19 +3914,19 @@
         <v>0.26</v>
       </c>
       <c r="G76" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H76" t="n">
         <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K76" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -3972,19 +3960,19 @@
         <v>0.26</v>
       </c>
       <c r="G77" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H77" t="n">
         <v>2</v>
       </c>
       <c r="I77" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K77" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -4018,19 +4006,19 @@
         <v>0.26</v>
       </c>
       <c r="G78" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H78" t="n">
         <v>2</v>
       </c>
       <c r="I78" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K78" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -4064,19 +4052,19 @@
         <v>0.26</v>
       </c>
       <c r="G79" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J79" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K79" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -4110,19 +4098,19 @@
         <v>0.26</v>
       </c>
       <c r="G80" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H80" t="n">
         <v>2</v>
       </c>
       <c r="I80" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J80" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K80" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -4156,19 +4144,19 @@
         <v>0.26</v>
       </c>
       <c r="G81" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H81" t="n">
         <v>2</v>
       </c>
       <c r="I81" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K81" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -4202,19 +4190,19 @@
         <v>0.26</v>
       </c>
       <c r="G82" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H82" t="n">
         <v>2</v>
       </c>
       <c r="I82" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K82" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -4248,19 +4236,19 @@
         <v>0.26</v>
       </c>
       <c r="G83" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H83" t="n">
         <v>2</v>
       </c>
       <c r="I83" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K83" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -4294,19 +4282,19 @@
         <v>0.26</v>
       </c>
       <c r="G84" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H84" t="n">
         <v>2</v>
       </c>
       <c r="I84" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J84" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K84" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -4340,19 +4328,19 @@
         <v>0.26</v>
       </c>
       <c r="G85" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H85" t="n">
         <v>2</v>
       </c>
       <c r="I85" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J85" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K85" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -4386,19 +4374,19 @@
         <v>0.26</v>
       </c>
       <c r="G86" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H86" t="n">
         <v>2</v>
       </c>
       <c r="I86" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K86" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -4432,19 +4420,19 @@
         <v>0.26</v>
       </c>
       <c r="G87" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H87" t="n">
         <v>2</v>
       </c>
       <c r="I87" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K87" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4478,19 +4466,19 @@
         <v>0.26</v>
       </c>
       <c r="G88" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H88" t="n">
         <v>2</v>
       </c>
       <c r="I88" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J88" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K88" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4524,19 +4512,19 @@
         <v>0.26</v>
       </c>
       <c r="G89" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H89" t="n">
         <v>2</v>
       </c>
       <c r="I89" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K89" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4570,19 +4558,19 @@
         <v>0.26</v>
       </c>
       <c r="G90" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H90" t="n">
         <v>2</v>
       </c>
       <c r="I90" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J90" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K90" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -4616,19 +4604,19 @@
         <v>0.26</v>
       </c>
       <c r="G91" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H91" t="n">
         <v>2</v>
       </c>
       <c r="I91" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K91" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -4662,19 +4650,19 @@
         <v>0.26</v>
       </c>
       <c r="G92" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H92" t="n">
         <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J92" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K92" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -4708,19 +4696,19 @@
         <v>0.26</v>
       </c>
       <c r="G93" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H93" t="n">
         <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J93" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K93" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -4754,19 +4742,19 @@
         <v>0.26</v>
       </c>
       <c r="G94" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H94" t="n">
         <v>2</v>
       </c>
       <c r="I94" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J94" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K94" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -4800,19 +4788,19 @@
         <v>0.26</v>
       </c>
       <c r="G95" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H95" t="n">
         <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J95" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K95" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -4846,19 +4834,19 @@
         <v>0.26</v>
       </c>
       <c r="G96" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H96" t="n">
         <v>2</v>
       </c>
       <c r="I96" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J96" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K96" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -4892,19 +4880,19 @@
         <v>0.26</v>
       </c>
       <c r="G97" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H97" t="n">
         <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J97" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K97" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -4938,19 +4926,19 @@
         <v>0.26</v>
       </c>
       <c r="G98" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H98" t="n">
         <v>2</v>
       </c>
       <c r="I98" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K98" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -4984,19 +4972,19 @@
         <v>0.26</v>
       </c>
       <c r="G99" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H99" t="n">
         <v>2</v>
       </c>
       <c r="I99" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J99" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K99" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -5030,19 +5018,19 @@
         <v>0.26</v>
       </c>
       <c r="G100" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J100" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K100" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -5076,19 +5064,19 @@
         <v>0.26</v>
       </c>
       <c r="G101" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H101" t="n">
         <v>2</v>
       </c>
       <c r="I101" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J101" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K101" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -5122,19 +5110,19 @@
         <v>0.26</v>
       </c>
       <c r="G102" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H102" t="n">
         <v>2</v>
       </c>
       <c r="I102" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J102" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K102" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -5168,19 +5156,19 @@
         <v>0.26</v>
       </c>
       <c r="G103" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H103" t="n">
         <v>2</v>
       </c>
       <c r="I103" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J103" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K103" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -5214,19 +5202,19 @@
         <v>0.26</v>
       </c>
       <c r="G104" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H104" t="n">
         <v>2</v>
       </c>
       <c r="I104" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J104" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K104" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -5260,19 +5248,19 @@
         <v>0.26</v>
       </c>
       <c r="G105" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H105" t="n">
         <v>2</v>
       </c>
       <c r="I105" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J105" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K105" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -5306,19 +5294,19 @@
         <v>0.26</v>
       </c>
       <c r="G106" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H106" t="n">
         <v>2</v>
       </c>
       <c r="I106" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J106" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K106" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -5352,19 +5340,19 @@
         <v>0.26</v>
       </c>
       <c r="G107" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H107" t="n">
         <v>2</v>
       </c>
       <c r="I107" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J107" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K107" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -5398,19 +5386,19 @@
         <v>0.26</v>
       </c>
       <c r="G108" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H108" t="n">
         <v>2</v>
       </c>
       <c r="I108" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J108" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K108" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -5444,19 +5432,19 @@
         <v>0.26</v>
       </c>
       <c r="G109" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H109" t="n">
         <v>2</v>
       </c>
       <c r="I109" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J109" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K109" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -5490,19 +5478,19 @@
         <v>0.26</v>
       </c>
       <c r="G110" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H110" t="n">
         <v>2</v>
       </c>
       <c r="I110" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J110" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K110" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -5536,19 +5524,19 @@
         <v>0.26</v>
       </c>
       <c r="G111" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H111" t="n">
         <v>2</v>
       </c>
       <c r="I111" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K111" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -5588,13 +5576,13 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J112" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K112" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -5634,13 +5622,13 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J113" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K113" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -5680,13 +5668,13 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J114" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K114" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -5726,13 +5714,13 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J115" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K115" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -5772,13 +5760,13 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J116" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K116" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -5818,13 +5806,13 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J117" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K117" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -5864,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J118" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K118" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -5910,13 +5898,13 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J119" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K119" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -5956,13 +5944,13 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J120" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K120" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -6002,13 +5990,13 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J121" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K121" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -6048,13 +6036,13 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J122" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K122" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -6094,13 +6082,13 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J123" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K123" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -6140,13 +6128,13 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J124" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K124" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -6186,13 +6174,13 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J125" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K125" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -6232,13 +6220,13 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J126" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K126" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -6278,13 +6266,13 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J127" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K127" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -6324,13 +6312,13 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J128" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K128" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -6370,13 +6358,13 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J129" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K129" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -6416,13 +6404,13 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J130" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K130" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -6462,13 +6450,13 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J131" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K131" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -6508,13 +6496,13 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J132" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K132" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -6554,13 +6542,13 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J133" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K133" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -6600,13 +6588,13 @@
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J134" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K134" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -6646,13 +6634,13 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J135" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K135" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -6692,13 +6680,13 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J136" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K136" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -6738,13 +6726,13 @@
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J137" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K137" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -6784,13 +6772,13 @@
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J138" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K138" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -6830,13 +6818,13 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J139" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K139" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -6876,13 +6864,13 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J140" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K140" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -6922,13 +6910,13 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J141" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K141" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -6968,13 +6956,13 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J142" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K142" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -7014,13 +7002,13 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J143" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K143" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -7060,13 +7048,13 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J144" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K144" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -7106,13 +7094,13 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J145" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K145" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -7152,13 +7140,13 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J146" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K146" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -7198,13 +7186,13 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J147" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K147" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -7244,13 +7232,13 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J148" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K148" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -7290,13 +7278,13 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J149" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K149" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -7336,13 +7324,13 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J150" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K150" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -7382,13 +7370,13 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J151" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K151" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -7428,13 +7416,13 @@
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J152" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K152" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -7474,13 +7462,13 @@
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J153" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K153" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -7520,13 +7508,13 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J154" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K154" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -7566,13 +7554,13 @@
         <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J155" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K155" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -7612,13 +7600,13 @@
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J156" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K156" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -7658,13 +7646,13 @@
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J157" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K157" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -7704,13 +7692,13 @@
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J158" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K158" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -7750,13 +7738,13 @@
         <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J159" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K159" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -7796,13 +7784,13 @@
         <v>0</v>
       </c>
       <c r="I160" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J160" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K160" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -7842,13 +7830,13 @@
         <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J161" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K161" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -7888,13 +7876,13 @@
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J162" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K162" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -7934,13 +7922,13 @@
         <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J163" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K163" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -7980,13 +7968,13 @@
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J164" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K164" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -8026,13 +8014,13 @@
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J165" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K165" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -8072,13 +8060,13 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J166" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K166" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -8112,19 +8100,19 @@
         <v>0.26</v>
       </c>
       <c r="G167" t="n">
-        <v>10.21</v>
+        <v>10.77</v>
       </c>
       <c r="H167" t="n">
         <v>6</v>
       </c>
       <c r="I167" t="n">
-        <v>67.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="J167" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="K167" t="n">
-        <v>88.3</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -8158,19 +8146,19 @@
         <v>0.26</v>
       </c>
       <c r="G168" t="n">
-        <v>9.869999999999999</v>
+        <v>10.42</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>68.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="J168" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="K168" t="n">
-        <v>87.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -8204,19 +8192,19 @@
         <v>0.26</v>
       </c>
       <c r="G169" t="n">
-        <v>9.869999999999999</v>
+        <v>10.42</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>68.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="J169" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="K169" t="n">
-        <v>87.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -8250,19 +8238,19 @@
         <v>0.26</v>
       </c>
       <c r="G170" t="n">
-        <v>9.869999999999999</v>
+        <v>10.42</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>68.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="J170" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="K170" t="n">
-        <v>87.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -8296,19 +8284,19 @@
         <v>0.26</v>
       </c>
       <c r="G171" t="n">
-        <v>9.869999999999999</v>
+        <v>10.42</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>68.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="J171" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="K171" t="n">
-        <v>87.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -8342,19 +8330,19 @@
         <v>0.26</v>
       </c>
       <c r="G172" t="n">
-        <v>9.970000000000001</v>
+        <v>10.49</v>
       </c>
       <c r="H172" t="n">
         <v>5</v>
       </c>
       <c r="I172" t="n">
-        <v>67.8</v>
+        <v>68.2</v>
       </c>
       <c r="J172" t="n">
-        <v>66</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K172" t="n">
-        <v>88</v>
+        <v>89.5</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -8388,19 +8376,19 @@
         <v>0.26</v>
       </c>
       <c r="G173" t="n">
-        <v>9.59</v>
+        <v>10.16</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
       </c>
       <c r="I173" t="n">
-        <v>68.3</v>
+        <v>68.7</v>
       </c>
       <c r="J173" t="n">
-        <v>66</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K173" t="n">
-        <v>87.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -8434,19 +8422,19 @@
         <v>0.26</v>
       </c>
       <c r="G174" t="n">
-        <v>9.59</v>
+        <v>10.16</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>68.3</v>
+        <v>68.7</v>
       </c>
       <c r="J174" t="n">
-        <v>66</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K174" t="n">
-        <v>87.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -8480,19 +8468,19 @@
         <v>0.26</v>
       </c>
       <c r="G175" t="n">
-        <v>9.59</v>
+        <v>10.16</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
       </c>
       <c r="I175" t="n">
-        <v>68.3</v>
+        <v>68.7</v>
       </c>
       <c r="J175" t="n">
-        <v>66</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K175" t="n">
-        <v>87.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -8526,19 +8514,19 @@
         <v>0.26</v>
       </c>
       <c r="G176" t="n">
-        <v>9.59</v>
+        <v>10.16</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
       </c>
       <c r="I176" t="n">
-        <v>68.3</v>
+        <v>68.7</v>
       </c>
       <c r="J176" t="n">
-        <v>66</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K176" t="n">
-        <v>87.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -8572,19 +8560,19 @@
         <v>0.26</v>
       </c>
       <c r="G177" t="n">
-        <v>9.23</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="H177" t="n">
         <v>2</v>
       </c>
       <c r="I177" t="n">
-        <v>68.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="J177" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="K177" t="n">
-        <v>86.90000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -8618,19 +8606,19 @@
         <v>0.26</v>
       </c>
       <c r="G178" t="n">
-        <v>9.029999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
       </c>
       <c r="I178" t="n">
-        <v>68.7</v>
+        <v>69.2</v>
       </c>
       <c r="J178" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="K178" t="n">
-        <v>86.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -8664,19 +8652,19 @@
         <v>0.26</v>
       </c>
       <c r="G179" t="n">
-        <v>9.029999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
       </c>
       <c r="I179" t="n">
-        <v>68.7</v>
+        <v>69.2</v>
       </c>
       <c r="J179" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="K179" t="n">
-        <v>86.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -8710,19 +8698,19 @@
         <v>0.26</v>
       </c>
       <c r="G180" t="n">
-        <v>9.029999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
       </c>
       <c r="I180" t="n">
-        <v>68.7</v>
+        <v>69.2</v>
       </c>
       <c r="J180" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="K180" t="n">
-        <v>86.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -8756,19 +8744,19 @@
         <v>0.26</v>
       </c>
       <c r="G181" t="n">
-        <v>9.029999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>68.7</v>
+        <v>69.2</v>
       </c>
       <c r="J181" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="K181" t="n">
-        <v>86.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -8802,19 +8790,19 @@
         <v>0.26</v>
       </c>
       <c r="G182" t="n">
-        <v>8.550000000000001</v>
+        <v>9</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
       </c>
       <c r="I182" t="n">
-        <v>69.2</v>
+        <v>69.7</v>
       </c>
       <c r="J182" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="K182" t="n">
-        <v>85.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -8848,19 +8836,19 @@
         <v>0.26</v>
       </c>
       <c r="G183" t="n">
-        <v>8.550000000000001</v>
+        <v>9</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
       </c>
       <c r="I183" t="n">
-        <v>69.2</v>
+        <v>69.7</v>
       </c>
       <c r="J183" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="K183" t="n">
-        <v>85.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -8894,19 +8882,19 @@
         <v>0.26</v>
       </c>
       <c r="G184" t="n">
-        <v>8.550000000000001</v>
+        <v>9</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>69.2</v>
+        <v>69.7</v>
       </c>
       <c r="J184" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="K184" t="n">
-        <v>85.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -8940,19 +8928,19 @@
         <v>0.26</v>
       </c>
       <c r="G185" t="n">
-        <v>8.550000000000001</v>
+        <v>9</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
       </c>
       <c r="I185" t="n">
-        <v>69.2</v>
+        <v>69.7</v>
       </c>
       <c r="J185" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="K185" t="n">
-        <v>85.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -8986,19 +8974,19 @@
         <v>0.26</v>
       </c>
       <c r="G186" t="n">
-        <v>8.550000000000001</v>
+        <v>9</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>69.2</v>
+        <v>69.7</v>
       </c>
       <c r="J186" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="K186" t="n">
-        <v>85.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -9032,19 +9020,19 @@
         <v>0.26</v>
       </c>
       <c r="G187" t="n">
-        <v>7.66</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
       </c>
       <c r="I187" t="n">
-        <v>70</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J187" t="n">
-        <v>67.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="K187" t="n">
-        <v>84.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -9078,19 +9066,19 @@
         <v>0.26</v>
       </c>
       <c r="G188" t="n">
-        <v>7.66</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>70</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J188" t="n">
-        <v>67.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="K188" t="n">
-        <v>84.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -9124,19 +9112,19 @@
         <v>0.26</v>
       </c>
       <c r="G189" t="n">
-        <v>7.66</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>70</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J189" t="n">
-        <v>67.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="K189" t="n">
-        <v>84.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -9170,19 +9158,19 @@
         <v>0.26</v>
       </c>
       <c r="G190" t="n">
-        <v>7.66</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>70</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J190" t="n">
-        <v>67.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="K190" t="n">
-        <v>84.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -9216,19 +9204,19 @@
         <v>0.26</v>
       </c>
       <c r="G191" t="n">
-        <v>7.66</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>70</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J191" t="n">
-        <v>67.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="K191" t="n">
-        <v>84.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -9262,19 +9250,19 @@
         <v>0.27</v>
       </c>
       <c r="G192" t="n">
-        <v>7.11</v>
+        <v>7.64</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>70.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="J192" t="n">
-        <v>67.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K192" t="n">
-        <v>83.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -9308,19 +9296,19 @@
         <v>0.27</v>
       </c>
       <c r="G193" t="n">
-        <v>7.11</v>
+        <v>7.64</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>70.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="J193" t="n">
-        <v>67.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K193" t="n">
-        <v>83.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -9354,19 +9342,19 @@
         <v>0.27</v>
       </c>
       <c r="G194" t="n">
-        <v>7.11</v>
+        <v>7.64</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>70.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="J194" t="n">
-        <v>67.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K194" t="n">
-        <v>83.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -9400,19 +9388,19 @@
         <v>0.27</v>
       </c>
       <c r="G195" t="n">
-        <v>7.11</v>
+        <v>7.64</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
       </c>
       <c r="I195" t="n">
-        <v>70.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="J195" t="n">
-        <v>67.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K195" t="n">
-        <v>83.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -9446,19 +9434,19 @@
         <v>0.27</v>
       </c>
       <c r="G196" t="n">
-        <v>7.11</v>
+        <v>7.64</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>70.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="J196" t="n">
-        <v>67.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K196" t="n">
-        <v>83.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -9492,19 +9480,19 @@
         <v>0.27</v>
       </c>
       <c r="G197" t="n">
-        <v>6.02</v>
+        <v>6.4</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>71.2</v>
+        <v>71.7</v>
       </c>
       <c r="J197" t="n">
-        <v>68.2</v>
+        <v>68.8</v>
       </c>
       <c r="K197" t="n">
-        <v>82.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="L197" t="n">
         <v>0</v>
@@ -9538,19 +9526,19 @@
         <v>0.27</v>
       </c>
       <c r="G198" t="n">
-        <v>6.02</v>
+        <v>6.4</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>71.2</v>
+        <v>71.7</v>
       </c>
       <c r="J198" t="n">
-        <v>68.2</v>
+        <v>68.8</v>
       </c>
       <c r="K198" t="n">
-        <v>82.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -9584,19 +9572,19 @@
         <v>0.27</v>
       </c>
       <c r="G199" t="n">
-        <v>6.02</v>
+        <v>6.4</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>71.2</v>
+        <v>71.7</v>
       </c>
       <c r="J199" t="n">
-        <v>68.2</v>
+        <v>68.8</v>
       </c>
       <c r="K199" t="n">
-        <v>82.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -9630,19 +9618,19 @@
         <v>0.27</v>
       </c>
       <c r="G200" t="n">
-        <v>6.02</v>
+        <v>6.4</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
       </c>
       <c r="I200" t="n">
-        <v>71.2</v>
+        <v>71.7</v>
       </c>
       <c r="J200" t="n">
-        <v>68.2</v>
+        <v>68.8</v>
       </c>
       <c r="K200" t="n">
-        <v>82.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -9676,19 +9664,19 @@
         <v>0.27</v>
       </c>
       <c r="G201" t="n">
-        <v>6.02</v>
+        <v>6.4</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>71.2</v>
+        <v>71.7</v>
       </c>
       <c r="J201" t="n">
-        <v>68.2</v>
+        <v>68.8</v>
       </c>
       <c r="K201" t="n">
-        <v>82.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -9722,19 +9710,19 @@
         <v>0.29</v>
       </c>
       <c r="G202" t="n">
-        <v>4.76</v>
+        <v>5.08</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
       </c>
       <c r="I202" t="n">
-        <v>72</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J202" t="n">
-        <v>69.2</v>
+        <v>69.8</v>
       </c>
       <c r="K202" t="n">
-        <v>80.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -9768,19 +9756,19 @@
         <v>0.29</v>
       </c>
       <c r="G203" t="n">
-        <v>4.76</v>
+        <v>5.08</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>72</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J203" t="n">
-        <v>69.2</v>
+        <v>69.8</v>
       </c>
       <c r="K203" t="n">
-        <v>80.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -9814,19 +9802,19 @@
         <v>0.29</v>
       </c>
       <c r="G204" t="n">
-        <v>4.76</v>
+        <v>5.08</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>72</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J204" t="n">
-        <v>69.2</v>
+        <v>69.8</v>
       </c>
       <c r="K204" t="n">
-        <v>80.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -9860,19 +9848,19 @@
         <v>0.29</v>
       </c>
       <c r="G205" t="n">
-        <v>4.76</v>
+        <v>5.08</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>72</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J205" t="n">
-        <v>69.2</v>
+        <v>69.8</v>
       </c>
       <c r="K205" t="n">
-        <v>80.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -9906,19 +9894,19 @@
         <v>0.29</v>
       </c>
       <c r="G206" t="n">
-        <v>4.76</v>
+        <v>5.08</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>72</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>69.2</v>
+        <v>69.8</v>
       </c>
       <c r="K206" t="n">
-        <v>80.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="L206" t="n">
         <v>0</v>
@@ -9952,19 +9940,19 @@
         <v>0.3</v>
       </c>
       <c r="G207" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
       </c>
       <c r="I207" t="n">
-        <v>73</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J207" t="n">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K207" t="n">
-        <v>78</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
@@ -9998,19 +9986,19 @@
         <v>0.3</v>
       </c>
       <c r="G208" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>73</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J208" t="n">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K208" t="n">
-        <v>78</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
@@ -10044,19 +10032,19 @@
         <v>0.3</v>
       </c>
       <c r="G209" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
       </c>
       <c r="I209" t="n">
-        <v>73</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K209" t="n">
-        <v>78</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -10090,19 +10078,19 @@
         <v>0.3</v>
       </c>
       <c r="G210" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
       </c>
       <c r="I210" t="n">
-        <v>73</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J210" t="n">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K210" t="n">
-        <v>78</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L210" t="n">
         <v>0</v>
@@ -10136,19 +10124,19 @@
         <v>0.3</v>
       </c>
       <c r="G211" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
       </c>
       <c r="I211" t="n">
-        <v>73</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J211" t="n">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K211" t="n">
-        <v>78</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -10182,19 +10170,19 @@
         <v>0.33</v>
       </c>
       <c r="G212" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
       </c>
       <c r="I212" t="n">
-        <v>73.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J212" t="n">
-        <v>72.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K212" t="n">
-        <v>75.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="L212" t="n">
         <v>0</v>
@@ -10228,19 +10216,19 @@
         <v>0.33</v>
       </c>
       <c r="G213" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
       </c>
       <c r="I213" t="n">
-        <v>73.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J213" t="n">
-        <v>72.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K213" t="n">
-        <v>75.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="L213" t="n">
         <v>0</v>
@@ -10274,19 +10262,19 @@
         <v>0.33</v>
       </c>
       <c r="G214" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>73.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J214" t="n">
-        <v>72.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K214" t="n">
-        <v>75.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="L214" t="n">
         <v>0</v>
@@ -10320,19 +10308,19 @@
         <v>0.33</v>
       </c>
       <c r="G215" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
       </c>
       <c r="I215" t="n">
-        <v>73.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J215" t="n">
-        <v>72.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K215" t="n">
-        <v>75.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="L215" t="n">
         <v>0</v>
@@ -10366,19 +10354,19 @@
         <v>0.33</v>
       </c>
       <c r="G216" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
       </c>
       <c r="I216" t="n">
-        <v>73.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J216" t="n">
-        <v>72.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K216" t="n">
-        <v>75.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -10418,13 +10406,13 @@
         <v>0</v>
       </c>
       <c r="I217" t="n">
-        <v>73.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="J217" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K217" t="n">
-        <v>74</v>
+        <v>74.7</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
@@ -10464,13 +10452,13 @@
         <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>73.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="J218" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K218" t="n">
-        <v>74</v>
+        <v>74.7</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -10510,13 +10498,13 @@
         <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>73.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="J219" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K219" t="n">
-        <v>74</v>
+        <v>74.7</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -10556,13 +10544,13 @@
         <v>0</v>
       </c>
       <c r="I220" t="n">
-        <v>73.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="J220" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K220" t="n">
-        <v>74</v>
+        <v>74.7</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -10602,13 +10590,13 @@
         <v>0</v>
       </c>
       <c r="I221" t="n">
-        <v>73.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="J221" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K221" t="n">
-        <v>74</v>
+        <v>74.7</v>
       </c>
       <c r="L221" t="n">
         <v>0</v>

--- a/Sensitivity_Output/Sensitivity_Analysis_Full.xlsx
+++ b/Sensitivity_Output/Sensitivity_Analysis_Full.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>alpha</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>lookahead_days</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total_assigned</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>avg_travel_hours</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_avg_utilization</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_avg_utilization</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_avg_utilization</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_overcap_weeks</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_overcap_weeks</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_overcap_weeks</t>
         </is>
